--- a/FIFAScheduleResults.xlsx
+++ b/FIFAScheduleResults.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World Cup Betting/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World Cup Betting/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AED77603-FF1F-4C24-8770-FC66820C71EF}"/>
+  <xr:revisionPtr revIDLastSave="171" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB30738B-8EA8-4390-BF48-70975A310CF3}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA World Cup 2026" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5893" uniqueCount="2521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5897" uniqueCount="2525">
   <si>
     <t>Match</t>
   </si>
@@ -7434,12 +7434,6 @@
     <t>game104</t>
   </si>
   <si>
-    <t>Scorer (player code, comma separated, OG = Own Goal)</t>
-  </si>
-  <si>
-    <t>Result (order compliant, "-" separated)</t>
-  </si>
-  <si>
     <t>Resultcode</t>
   </si>
   <si>
@@ -7452,9 +7446,6 @@
     <t>Curaçao vs Ivory Coast</t>
   </si>
   <si>
-    <t>ScorerRealName</t>
-  </si>
-  <si>
     <t>game01</t>
   </si>
   <si>
@@ -7624,6 +7615,27 @@
   </si>
   <si>
     <t>Time</t>
+  </si>
+  <si>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>MEX9, MEX16</t>
+  </si>
+  <si>
+    <t>CZE7, KOR6, KOR18</t>
+  </si>
+  <si>
+    <t>ResultGame</t>
+  </si>
+  <si>
+    <t>ScorerGame</t>
+  </si>
+  <si>
+    <t>DiffGame</t>
   </si>
 </sst>
 </file>
@@ -7938,7 +7950,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -7972,11 +7984,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8414,9 +8435,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -8425,6 +8443,12 @@
     </xf>
     <xf numFmtId="20" fontId="5" fillId="53" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8736,8 +8760,9 @@
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="15.81640625" customWidth="1"/>
     <col min="7" max="7" width="27.6328125" customWidth="1"/>
-    <col min="8" max="9" width="26.6328125" customWidth="1"/>
-    <col min="10" max="10" width="14.36328125" customWidth="1"/>
+    <col min="8" max="8" width="26.6328125" customWidth="1"/>
+    <col min="9" max="9" width="14.36328125" customWidth="1"/>
+    <col min="10" max="10" width="13.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.35">
@@ -8751,7 +8776,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2520</v>
+        <v>2517</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -8760,16 +8785,16 @@
         <v>2361</v>
       </c>
       <c r="G1" s="144" t="s">
-        <v>2458</v>
+        <v>2522</v>
       </c>
       <c r="H1" s="144" t="s">
+        <v>2523</v>
+      </c>
+      <c r="I1" s="144" t="s">
         <v>2457</v>
       </c>
-      <c r="I1" s="144" t="s">
-        <v>2463</v>
-      </c>
       <c r="J1" s="144" t="s">
-        <v>2459</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -8783,18 +8808,27 @@
         <v>6</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="127" t="s">
-        <v>2464</v>
-      </c>
-      <c r="G2" s="146"/>
-      <c r="J2" t="e" cm="1">
-        <f t="array" ref="J2">_xlfn.IFS(LEFT(G2,1)-RIGHT(G2,1) &gt; 0, "W1",LEFT(G2,1)-RIGHT(G2,1) = 0, "D",LEFT(G2,1)-RIGHT(G2,1) &lt; 0, "W2")</f>
-        <v>#VALUE!</v>
+        <v>2461</v>
+      </c>
+      <c r="G2" s="146" t="s">
+        <v>2518</v>
+      </c>
+      <c r="H2" s="150" t="s">
+        <v>2520</v>
+      </c>
+      <c r="I2" t="str" cm="1">
+        <f t="array" ref="I2">_xlfn.IFS(LEFT(G2,1)-RIGHT(G2,1) &gt; 0, "W1",LEFT(G2,1)-RIGHT(G2,1) = 0, "D",LEFT(G2,1)-RIGHT(G2,1) &lt; 0, "W2", ISBLANK(G2), "")</f>
+        <v>W1</v>
+      </c>
+      <c r="J2" s="146">
+        <f>LEFT(G2,1)-RIGHT(G2,1)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -8808,13 +8842,27 @@
         <v>6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2508</v>
+        <v>2505</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F3" s="127" t="s">
-        <v>2465</v>
+        <v>2462</v>
+      </c>
+      <c r="G3" s="146" t="s">
+        <v>2519</v>
+      </c>
+      <c r="H3" s="150" t="s">
+        <v>2521</v>
+      </c>
+      <c r="I3" t="str" cm="1">
+        <f t="array" ref="I3">_xlfn.IFS(LEFT(G3,1)-RIGHT(G3,1) &gt; 0, "W1",LEFT(G3,1)-RIGHT(G3,1) = 0, "D",LEFT(G3,1)-RIGHT(G3,1) &lt; 0, "W2", ISBLANK(G3), "")</f>
+        <v>W1</v>
+      </c>
+      <c r="J3" s="146">
+        <f>LEFT(G3,1)-RIGHT(G3,1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -8828,13 +8876,21 @@
         <v>12</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2513</v>
+        <v>2510</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="127" t="s">
         <v>2362</v>
+      </c>
+      <c r="I4" t="e" cm="1">
+        <f t="array" ref="I4">_xlfn.IFS(LEFT(G4,1)-RIGHT(G4,1)&gt;0,"W1",LEFT(G4,1)-RIGHT(G4,1)=0,"D",LEFT(G4,1)-RIGHT(G4,1)&lt;0,"W2",ISBLANK(G4),"")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J4" s="146" t="e">
+        <f t="shared" ref="J4:J67" si="0">LEFT(G4,1)-RIGHT(G4,1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -8848,13 +8904,21 @@
         <v>12</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="127" t="s">
         <v>2363</v>
+      </c>
+      <c r="I5" t="e" cm="1">
+        <f t="array" ref="I5">_xlfn.IFS(LEFT(G5,1)-RIGHT(G5,1) &gt; 0, "W1",LEFT(G5,1)-RIGHT(G5,1) = 0, "D",LEFT(G5,1)-RIGHT(G5,1) &lt; 0, "W2", ISBLANK(G5), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J5" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -8868,13 +8932,21 @@
         <v>18</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F6" s="127" t="s">
         <v>2364</v>
+      </c>
+      <c r="I6" t="e" cm="1">
+        <f t="array" ref="I6">_xlfn.IFS(LEFT(G6,1)-RIGHT(G6,1) &gt; 0, "W1",LEFT(G6,1)-RIGHT(G6,1) = 0, "D",LEFT(G6,1)-RIGHT(G6,1) &lt; 0, "W2", ISBLANK(G6), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J6" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -8888,13 +8960,21 @@
         <v>18</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="127" t="s">
         <v>2365</v>
+      </c>
+      <c r="I7" t="e" cm="1">
+        <f t="array" ref="I7">_xlfn.IFS(LEFT(G7,1)-RIGHT(G7,1) &gt; 0, "W1",LEFT(G7,1)-RIGHT(G7,1) = 0, "D",LEFT(G7,1)-RIGHT(G7,1) &lt; 0, "W2", ISBLANK(G7), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J7" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -8908,13 +8988,21 @@
         <v>24</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>2509</v>
+        <v>2506</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="128" t="s">
-        <v>2466</v>
+        <v>2463</v>
+      </c>
+      <c r="I8" t="e" cm="1">
+        <f t="array" ref="I8">_xlfn.IFS(LEFT(G8,1)-RIGHT(G8,1) &gt; 0, "W1",LEFT(G8,1)-RIGHT(G8,1) = 0, "D",LEFT(G8,1)-RIGHT(G8,1) &lt; 0, "W2", ISBLANK(G8), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J8" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -8928,13 +9016,21 @@
         <v>28</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F9" s="128" t="s">
-        <v>2467</v>
+        <v>2464</v>
+      </c>
+      <c r="I9" t="e" cm="1">
+        <f t="array" ref="I9">_xlfn.IFS(LEFT(G9,1)-RIGHT(G9,1) &gt; 0, "W1",LEFT(G9,1)-RIGHT(G9,1) = 0, "D",LEFT(G9,1)-RIGHT(G9,1) &lt; 0, "W2", ISBLANK(G9), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J9" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -8948,13 +9044,21 @@
         <v>12</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F10" s="128" t="s">
         <v>2366</v>
+      </c>
+      <c r="I10" t="e" cm="1">
+        <f t="array" ref="I10">_xlfn.IFS(LEFT(G10,1)-RIGHT(G10,1) &gt; 0, "W1",LEFT(G10,1)-RIGHT(G10,1) = 0, "D",LEFT(G10,1)-RIGHT(G10,1) &lt; 0, "W2", ISBLANK(G10), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J10" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -8968,13 +9072,21 @@
         <v>12</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F11" s="128" t="s">
         <v>2367</v>
+      </c>
+      <c r="I11" t="e" cm="1">
+        <f t="array" ref="I11">_xlfn.IFS(LEFT(G11,1)-RIGHT(G11,1) &gt; 0, "W1",LEFT(G11,1)-RIGHT(G11,1) = 0, "D",LEFT(G11,1)-RIGHT(G11,1) &lt; 0, "W2", ISBLANK(G11), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J11" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -8988,13 +9100,21 @@
         <v>18</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>36</v>
       </c>
       <c r="F12" s="128" t="s">
         <v>2368</v>
+      </c>
+      <c r="I12" t="e" cm="1">
+        <f t="array" ref="I12">_xlfn.IFS(LEFT(G12,1)-RIGHT(G12,1) &gt; 0, "W1",LEFT(G12,1)-RIGHT(G12,1) = 0, "D",LEFT(G12,1)-RIGHT(G12,1) &lt; 0, "W2", ISBLANK(G12), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J12" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -9008,13 +9128,21 @@
         <v>18</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>36</v>
       </c>
       <c r="F13" s="128" t="s">
         <v>2369</v>
+      </c>
+      <c r="I13" t="e" cm="1">
+        <f t="array" ref="I13">_xlfn.IFS(LEFT(G13,1)-RIGHT(G13,1) &gt; 0, "W1",LEFT(G13,1)-RIGHT(G13,1) = 0, "D",LEFT(G13,1)-RIGHT(G13,1) &lt; 0, "W2", ISBLANK(G13), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J13" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -9028,13 +9156,21 @@
         <v>28</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>2512</v>
+        <v>2509</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>41</v>
       </c>
       <c r="F14" s="129" t="s">
-        <v>2468</v>
+        <v>2465</v>
+      </c>
+      <c r="I14" t="e" cm="1">
+        <f t="array" ref="I14">_xlfn.IFS(LEFT(G14,1)-RIGHT(G14,1) &gt; 0, "W1",LEFT(G14,1)-RIGHT(G14,1) = 0, "D",LEFT(G14,1)-RIGHT(G14,1) &lt; 0, "W2", ISBLANK(G14), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J14" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -9048,13 +9184,21 @@
         <v>28</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>41</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>2469</v>
+        <v>2466</v>
+      </c>
+      <c r="I15" t="e" cm="1">
+        <f t="array" ref="I15">_xlfn.IFS(LEFT(G15,1)-RIGHT(G15,1) &gt; 0, "W1",LEFT(G15,1)-RIGHT(G15,1) = 0, "D",LEFT(G15,1)-RIGHT(G15,1) &lt; 0, "W2", ISBLANK(G15), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J15" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -9068,7 +9212,7 @@
         <v>46</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>47</v>
@@ -9076,8 +9220,16 @@
       <c r="F16" s="129" t="s">
         <v>2370</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I16" t="e" cm="1">
+        <f t="array" ref="I16">_xlfn.IFS(LEFT(G16,1)-RIGHT(G16,1) &gt; 0, "W1",LEFT(G16,1)-RIGHT(G16,1) = 0, "D",LEFT(G16,1)-RIGHT(G16,1) &lt; 0, "W2", ISBLANK(G16), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J16" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>48</v>
       </c>
@@ -9088,7 +9240,7 @@
         <v>46</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>47</v>
@@ -9096,8 +9248,16 @@
       <c r="F17" s="129" t="s">
         <v>2371</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I17" t="e" cm="1">
+        <f t="array" ref="I17">_xlfn.IFS(LEFT(G17,1)-RIGHT(G17,1) &gt; 0, "W1",LEFT(G17,1)-RIGHT(G17,1) = 0, "D",LEFT(G17,1)-RIGHT(G17,1) &lt; 0, "W2", ISBLANK(G17), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J17" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>50</v>
       </c>
@@ -9108,7 +9268,7 @@
         <v>18</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>52</v>
@@ -9116,8 +9276,16 @@
       <c r="F18" s="129" t="s">
         <v>2372</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I18" t="e" cm="1">
+        <f t="array" ref="I18">_xlfn.IFS(LEFT(G18,1)-RIGHT(G18,1) &gt; 0, "W1",LEFT(G18,1)-RIGHT(G18,1) = 0, "D",LEFT(G18,1)-RIGHT(G18,1) &lt; 0, "W2", ISBLANK(G18), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J18" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>53</v>
       </c>
@@ -9128,7 +9296,7 @@
         <v>18</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>52</v>
@@ -9136,8 +9304,16 @@
       <c r="F19" s="129" t="s">
         <v>2373</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I19" t="e" cm="1">
+        <f t="array" ref="I19">_xlfn.IFS(LEFT(G19,1)-RIGHT(G19,1) &gt; 0, "W1",LEFT(G19,1)-RIGHT(G19,1) = 0, "D",LEFT(G19,1)-RIGHT(G19,1) &lt; 0, "W2", ISBLANK(G19), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J19" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>55</v>
       </c>
@@ -9148,16 +9324,24 @@
         <v>24</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>57</v>
       </c>
       <c r="F20" s="130" t="s">
-        <v>2470</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+        <v>2467</v>
+      </c>
+      <c r="I20" t="e" cm="1">
+        <f t="array" ref="I20">_xlfn.IFS(LEFT(G20,1)-RIGHT(G20,1) &gt; 0, "W1",LEFT(G20,1)-RIGHT(G20,1) = 0, "D",LEFT(G20,1)-RIGHT(G20,1) &lt; 0, "W2", ISBLANK(G20), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J20" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>58</v>
       </c>
@@ -9168,16 +9352,24 @@
         <v>28</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>2511</v>
+        <v>2508</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>57</v>
       </c>
       <c r="F21" s="130" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+        <v>2468</v>
+      </c>
+      <c r="I21" t="e" cm="1">
+        <f t="array" ref="I21">_xlfn.IFS(LEFT(G21,1)-RIGHT(G21,1) &gt; 0, "W1",LEFT(G21,1)-RIGHT(G21,1) = 0, "D",LEFT(G21,1)-RIGHT(G21,1) &lt; 0, "W2", ISBLANK(G21), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J21" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
         <v>60</v>
       </c>
@@ -9188,7 +9380,7 @@
         <v>46</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>2511</v>
+        <v>2508</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>62</v>
@@ -9196,8 +9388,16 @@
       <c r="F22" s="130" t="s">
         <v>2374</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I22" t="e" cm="1">
+        <f t="array" ref="I22">_xlfn.IFS(LEFT(G22,1)-RIGHT(G22,1) &gt; 0, "W1",LEFT(G22,1)-RIGHT(G22,1) = 0, "D",LEFT(G22,1)-RIGHT(G22,1) &lt; 0, "W2", ISBLANK(G22), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J22" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>63</v>
       </c>
@@ -9208,7 +9408,7 @@
         <v>46</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>62</v>
@@ -9216,8 +9416,16 @@
       <c r="F23" s="130" t="s">
         <v>2375</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I23" t="e" cm="1">
+        <f t="array" ref="I23">_xlfn.IFS(LEFT(G23,1)-RIGHT(G23,1) &gt; 0, "W1",LEFT(G23,1)-RIGHT(G23,1) = 0, "D",LEFT(G23,1)-RIGHT(G23,1) &lt; 0, "W2", ISBLANK(G23), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J23" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
         <v>65</v>
       </c>
@@ -9228,7 +9436,7 @@
         <v>67</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>68</v>
@@ -9236,8 +9444,16 @@
       <c r="F24" s="130" t="s">
         <v>2376</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I24" t="e" cm="1">
+        <f t="array" ref="I24">_xlfn.IFS(LEFT(G24,1)-RIGHT(G24,1) &gt; 0, "W1",LEFT(G24,1)-RIGHT(G24,1) = 0, "D",LEFT(G24,1)-RIGHT(G24,1) &lt; 0, "W2", ISBLANK(G24), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J24" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>69</v>
       </c>
@@ -9248,7 +9464,7 @@
         <v>67</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>68</v>
@@ -9256,8 +9472,16 @@
       <c r="F25" s="130" t="s">
         <v>2377</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I25" t="e" cm="1">
+        <f t="array" ref="I25">_xlfn.IFS(LEFT(G25,1)-RIGHT(G25,1) &gt; 0, "W1",LEFT(G25,1)-RIGHT(G25,1) = 0, "D",LEFT(G25,1)-RIGHT(G25,1) &lt; 0, "W2", ISBLANK(G25), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J25" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
         <v>71</v>
       </c>
@@ -9268,7 +9492,7 @@
         <v>73</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>2513</v>
+        <v>2510</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>74</v>
@@ -9276,10 +9500,18 @@
       <c r="F26" s="131" t="s">
         <v>2378</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I26" t="e" cm="1">
+        <f t="array" ref="I26">_xlfn.IFS(LEFT(G26,1)-RIGHT(G26,1) &gt; 0, "W1",LEFT(G26,1)-RIGHT(G26,1) = 0, "D",LEFT(G26,1)-RIGHT(G26,1) &lt; 0, "W2", ISBLANK(G26), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J26" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>75</v>
@@ -9288,18 +9520,26 @@
         <v>73</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>74</v>
       </c>
       <c r="F27" s="131" t="s">
-        <v>2472</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+        <v>2469</v>
+      </c>
+      <c r="I27" t="e" cm="1">
+        <f t="array" ref="I27">_xlfn.IFS(LEFT(G27,1)-RIGHT(G27,1) &gt; 0, "W1",LEFT(G27,1)-RIGHT(G27,1) = 0, "D",LEFT(G27,1)-RIGHT(G27,1) &lt; 0, "W2", ISBLANK(G27), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J27" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>76</v>
@@ -9308,7 +9548,7 @@
         <v>77</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>2517</v>
+        <v>2514</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>78</v>
@@ -9316,8 +9556,16 @@
       <c r="F28" s="131" t="s">
         <v>2379</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I28" t="e" cm="1">
+        <f t="array" ref="I28">_xlfn.IFS(LEFT(G28,1)-RIGHT(G28,1) &gt; 0, "W1",LEFT(G28,1)-RIGHT(G28,1) = 0, "D",LEFT(G28,1)-RIGHT(G28,1) &lt; 0, "W2", ISBLANK(G28), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J28" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="10" t="s">
         <v>79</v>
       </c>
@@ -9328,7 +9576,7 @@
         <v>77</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>78</v>
@@ -9336,8 +9584,16 @@
       <c r="F29" s="131" t="s">
         <v>2380</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I29" t="e" cm="1">
+        <f t="array" ref="I29">_xlfn.IFS(LEFT(G29,1)-RIGHT(G29,1) &gt; 0, "W1",LEFT(G29,1)-RIGHT(G29,1) = 0, "D",LEFT(G29,1)-RIGHT(G29,1) &lt; 0, "W2", ISBLANK(G29), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J29" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
         <v>81</v>
       </c>
@@ -9348,7 +9604,7 @@
         <v>67</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>83</v>
@@ -9356,10 +9612,18 @@
       <c r="F30" s="131" t="s">
         <v>2381</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I30" t="e" cm="1">
+        <f t="array" ref="I30">_xlfn.IFS(LEFT(G30,1)-RIGHT(G30,1) &gt; 0, "W1",LEFT(G30,1)-RIGHT(G30,1) = 0, "D",LEFT(G30,1)-RIGHT(G30,1) &lt; 0, "W2", ISBLANK(G30), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J30" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>84</v>
@@ -9368,7 +9632,7 @@
         <v>67</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>83</v>
@@ -9376,8 +9640,16 @@
       <c r="F31" s="131" t="s">
         <v>2382</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I31" t="e" cm="1">
+        <f t="array" ref="I31">_xlfn.IFS(LEFT(G31,1)-RIGHT(G31,1) &gt; 0, "W1",LEFT(G31,1)-RIGHT(G31,1) = 0, "D",LEFT(G31,1)-RIGHT(G31,1) &lt; 0, "W2", ISBLANK(G31), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J31" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
         <v>85</v>
       </c>
@@ -9388,7 +9660,7 @@
         <v>73</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="E32" s="13" t="s">
         <v>87</v>
@@ -9396,8 +9668,16 @@
       <c r="F32" s="132" t="s">
         <v>2383</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I32" t="e" cm="1">
+        <f t="array" ref="I32">_xlfn.IFS(LEFT(G32,1)-RIGHT(G32,1) &gt; 0, "W1",LEFT(G32,1)-RIGHT(G32,1) = 0, "D",LEFT(G32,1)-RIGHT(G32,1) &lt; 0, "W2", ISBLANK(G32), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J32" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
         <v>88</v>
       </c>
@@ -9408,7 +9688,7 @@
         <v>73</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="E33" s="13" t="s">
         <v>87</v>
@@ -9416,8 +9696,16 @@
       <c r="F33" s="132" t="s">
         <v>2384</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I33" t="e" cm="1">
+        <f t="array" ref="I33">_xlfn.IFS(LEFT(G33,1)-RIGHT(G33,1) &gt; 0, "W1",LEFT(G33,1)-RIGHT(G33,1) = 0, "D",LEFT(G33,1)-RIGHT(G33,1) &lt; 0, "W2", ISBLANK(G33), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J33" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
         <v>90</v>
       </c>
@@ -9428,7 +9716,7 @@
         <v>77</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>2509</v>
+        <v>2506</v>
       </c>
       <c r="E34" s="13" t="s">
         <v>92</v>
@@ -9436,8 +9724,16 @@
       <c r="F34" s="132" t="s">
         <v>2385</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I34" t="e" cm="1">
+        <f t="array" ref="I34">_xlfn.IFS(LEFT(G34,1)-RIGHT(G34,1) &gt; 0, "W1",LEFT(G34,1)-RIGHT(G34,1) = 0, "D",LEFT(G34,1)-RIGHT(G34,1) &lt; 0, "W2", ISBLANK(G34), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J34" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
         <v>93</v>
       </c>
@@ -9448,7 +9744,7 @@
         <v>77</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>2508</v>
+        <v>2505</v>
       </c>
       <c r="E35" s="13" t="s">
         <v>92</v>
@@ -9456,8 +9752,16 @@
       <c r="F35" s="132" t="s">
         <v>2386</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I35" t="e" cm="1">
+        <f t="array" ref="I35">_xlfn.IFS(LEFT(G35,1)-RIGHT(G35,1) &gt; 0, "W1",LEFT(G35,1)-RIGHT(G35,1) = 0, "D",LEFT(G35,1)-RIGHT(G35,1) &lt; 0, "W2", ISBLANK(G35), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J35" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="12" t="s">
         <v>95</v>
       </c>
@@ -9468,7 +9772,7 @@
         <v>67</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="E36" s="13" t="s">
         <v>97</v>
@@ -9476,8 +9780,16 @@
       <c r="F36" s="132" t="s">
         <v>2387</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I36" t="e" cm="1">
+        <f t="array" ref="I36">_xlfn.IFS(LEFT(G36,1)-RIGHT(G36,1) &gt; 0, "W1",LEFT(G36,1)-RIGHT(G36,1) = 0, "D",LEFT(G36,1)-RIGHT(G36,1) &lt; 0, "W2", ISBLANK(G36), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J36" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="12" t="s">
         <v>98</v>
       </c>
@@ -9488,7 +9800,7 @@
         <v>67</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="E37" s="13" t="s">
         <v>97</v>
@@ -9496,8 +9808,16 @@
       <c r="F37" s="132" t="s">
         <v>2388</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I37" t="e" cm="1">
+        <f t="array" ref="I37">_xlfn.IFS(LEFT(G37,1)-RIGHT(G37,1) &gt; 0, "W1",LEFT(G37,1)-RIGHT(G37,1) = 0, "D",LEFT(G37,1)-RIGHT(G37,1) &lt; 0, "W2", ISBLANK(G37), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J37" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="14" t="s">
         <v>100</v>
       </c>
@@ -9508,7 +9828,7 @@
         <v>102</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="E38" s="15" t="s">
         <v>103</v>
@@ -9516,8 +9836,16 @@
       <c r="F38" s="133" t="s">
         <v>2389</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I38" t="e" cm="1">
+        <f t="array" ref="I38">_xlfn.IFS(LEFT(G38,1)-RIGHT(G38,1) &gt; 0, "W1",LEFT(G38,1)-RIGHT(G38,1) = 0, "D",LEFT(G38,1)-RIGHT(G38,1) &lt; 0, "W2", ISBLANK(G38), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J38" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="14" t="s">
         <v>104</v>
       </c>
@@ -9528,7 +9856,7 @@
         <v>102</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="E39" s="15" t="s">
         <v>103</v>
@@ -9536,8 +9864,16 @@
       <c r="F39" s="133" t="s">
         <v>2390</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I39" t="e" cm="1">
+        <f t="array" ref="I39">_xlfn.IFS(LEFT(G39,1)-RIGHT(G39,1) &gt; 0, "W1",LEFT(G39,1)-RIGHT(G39,1) = 0, "D",LEFT(G39,1)-RIGHT(G39,1) &lt; 0, "W2", ISBLANK(G39), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J39" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="14" t="s">
         <v>106</v>
       </c>
@@ -9548,7 +9884,7 @@
         <v>108</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>109</v>
@@ -9556,8 +9892,16 @@
       <c r="F40" s="133" t="s">
         <v>2391</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I40" t="e" cm="1">
+        <f t="array" ref="I40">_xlfn.IFS(LEFT(G40,1)-RIGHT(G40,1) &gt; 0, "W1",LEFT(G40,1)-RIGHT(G40,1) = 0, "D",LEFT(G40,1)-RIGHT(G40,1) &lt; 0, "W2", ISBLANK(G40), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J40" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="14" t="s">
         <v>110</v>
       </c>
@@ -9568,7 +9912,7 @@
         <v>108</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>109</v>
@@ -9576,8 +9920,16 @@
       <c r="F41" s="133" t="s">
         <v>2392</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I41" t="e" cm="1">
+        <f t="array" ref="I41">_xlfn.IFS(LEFT(G41,1)-RIGHT(G41,1) &gt; 0, "W1",LEFT(G41,1)-RIGHT(G41,1) = 0, "D",LEFT(G41,1)-RIGHT(G41,1) &lt; 0, "W2", ISBLANK(G41), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J41" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="14" t="s">
         <v>112</v>
       </c>
@@ -9588,7 +9940,7 @@
         <v>114</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>115</v>
@@ -9596,8 +9948,16 @@
       <c r="F42" s="133" t="s">
         <v>2393</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I42" t="e" cm="1">
+        <f t="array" ref="I42">_xlfn.IFS(LEFT(G42,1)-RIGHT(G42,1) &gt; 0, "W1",LEFT(G42,1)-RIGHT(G42,1) = 0, "D",LEFT(G42,1)-RIGHT(G42,1) &lt; 0, "W2", ISBLANK(G42), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J42" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="14" t="s">
         <v>116</v>
       </c>
@@ -9608,7 +9968,7 @@
         <v>114</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>115</v>
@@ -9616,8 +9976,16 @@
       <c r="F43" s="133" t="s">
         <v>2394</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I43" t="e" cm="1">
+        <f t="array" ref="I43">_xlfn.IFS(LEFT(G43,1)-RIGHT(G43,1) &gt; 0, "W1",LEFT(G43,1)-RIGHT(G43,1) = 0, "D",LEFT(G43,1)-RIGHT(G43,1) &lt; 0, "W2", ISBLANK(G43), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J43" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="16" t="s">
         <v>118</v>
       </c>
@@ -9628,7 +9996,7 @@
         <v>102</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>2513</v>
+        <v>2510</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>120</v>
@@ -9636,8 +10004,16 @@
       <c r="F44" s="134" t="s">
         <v>2395</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I44" t="e" cm="1">
+        <f t="array" ref="I44">_xlfn.IFS(LEFT(G44,1)-RIGHT(G44,1) &gt; 0, "W1",LEFT(G44,1)-RIGHT(G44,1) = 0, "D",LEFT(G44,1)-RIGHT(G44,1) &lt; 0, "W2", ISBLANK(G44), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J44" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="16" t="s">
         <v>121</v>
       </c>
@@ -9648,7 +10024,7 @@
         <v>102</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>120</v>
@@ -9656,8 +10032,16 @@
       <c r="F45" s="134" t="s">
         <v>2396</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I45" t="e" cm="1">
+        <f t="array" ref="I45">_xlfn.IFS(LEFT(G45,1)-RIGHT(G45,1) &gt; 0, "W1",LEFT(G45,1)-RIGHT(G45,1) = 0, "D",LEFT(G45,1)-RIGHT(G45,1) &lt; 0, "W2", ISBLANK(G45), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J45" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="16" t="s">
         <v>123</v>
       </c>
@@ -9668,7 +10052,7 @@
         <v>108</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>2513</v>
+        <v>2510</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>125</v>
@@ -9676,8 +10060,16 @@
       <c r="F46" s="134" t="s">
         <v>2397</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I46" t="e" cm="1">
+        <f t="array" ref="I46">_xlfn.IFS(LEFT(G46,1)-RIGHT(G46,1) &gt; 0, "W1",LEFT(G46,1)-RIGHT(G46,1) = 0, "D",LEFT(G46,1)-RIGHT(G46,1) &lt; 0, "W2", ISBLANK(G46), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J46" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="16" t="s">
         <v>126</v>
       </c>
@@ -9688,7 +10080,7 @@
         <v>108</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>125</v>
@@ -9696,8 +10088,16 @@
       <c r="F47" s="134" t="s">
         <v>2398</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I47" t="e" cm="1">
+        <f t="array" ref="I47">_xlfn.IFS(LEFT(G47,1)-RIGHT(G47,1) &gt; 0, "W1",LEFT(G47,1)-RIGHT(G47,1) = 0, "D",LEFT(G47,1)-RIGHT(G47,1) &lt; 0, "W2", ISBLANK(G47), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J47" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="16" t="s">
         <v>128</v>
       </c>
@@ -9708,7 +10108,7 @@
         <v>114</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="E48" s="17" t="s">
         <v>130</v>
@@ -9716,8 +10116,16 @@
       <c r="F48" s="134" t="s">
         <v>2399</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I48" t="e" cm="1">
+        <f t="array" ref="I48">_xlfn.IFS(LEFT(G48,1)-RIGHT(G48,1) &gt; 0, "W1",LEFT(G48,1)-RIGHT(G48,1) = 0, "D",LEFT(G48,1)-RIGHT(G48,1) &lt; 0, "W2", ISBLANK(G48), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J48" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="16" t="s">
         <v>131</v>
       </c>
@@ -9728,7 +10136,7 @@
         <v>114</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="E49" s="17" t="s">
         <v>130</v>
@@ -9736,8 +10144,16 @@
       <c r="F49" s="134" t="s">
         <v>2400</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I49" t="e" cm="1">
+        <f t="array" ref="I49">_xlfn.IFS(LEFT(G49,1)-RIGHT(G49,1) &gt; 0, "W1",LEFT(G49,1)-RIGHT(G49,1) = 0, "D",LEFT(G49,1)-RIGHT(G49,1) &lt; 0, "W2", ISBLANK(G49), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J49" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="18" t="s">
         <v>133</v>
       </c>
@@ -9748,7 +10164,7 @@
         <v>135</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="E50" s="19" t="s">
         <v>136</v>
@@ -9756,8 +10172,16 @@
       <c r="F50" s="135" t="s">
         <v>2401</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I50" t="e" cm="1">
+        <f t="array" ref="I50">_xlfn.IFS(LEFT(G50,1)-RIGHT(G50,1) &gt; 0, "W1",LEFT(G50,1)-RIGHT(G50,1) = 0, "D",LEFT(G50,1)-RIGHT(G50,1) &lt; 0, "W2", ISBLANK(G50), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J50" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="18" t="s">
         <v>137</v>
       </c>
@@ -9768,7 +10192,7 @@
         <v>135</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="E51" s="19" t="s">
         <v>136</v>
@@ -9776,8 +10200,16 @@
       <c r="F51" s="135" t="s">
         <v>2402</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I51" t="e" cm="1">
+        <f t="array" ref="I51">_xlfn.IFS(LEFT(G51,1)-RIGHT(G51,1) &gt; 0, "W1",LEFT(G51,1)-RIGHT(G51,1) = 0, "D",LEFT(G51,1)-RIGHT(G51,1) &lt; 0, "W2", ISBLANK(G51), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J51" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="18" t="s">
         <v>139</v>
       </c>
@@ -9788,7 +10220,7 @@
         <v>141</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>2512</v>
+        <v>2509</v>
       </c>
       <c r="E52" s="19" t="s">
         <v>142</v>
@@ -9796,8 +10228,16 @@
       <c r="F52" s="135" t="s">
         <v>2403</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I52" t="e" cm="1">
+        <f t="array" ref="I52">_xlfn.IFS(LEFT(G52,1)-RIGHT(G52,1) &gt; 0, "W1",LEFT(G52,1)-RIGHT(G52,1) = 0, "D",LEFT(G52,1)-RIGHT(G52,1) &lt; 0, "W2", ISBLANK(G52), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J52" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="18" t="s">
         <v>143</v>
       </c>
@@ -9808,7 +10248,7 @@
         <v>141</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="E53" s="19" t="s">
         <v>142</v>
@@ -9816,8 +10256,16 @@
       <c r="F53" s="135" t="s">
         <v>2404</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I53" t="e" cm="1">
+        <f t="array" ref="I53">_xlfn.IFS(LEFT(G53,1)-RIGHT(G53,1) &gt; 0, "W1",LEFT(G53,1)-RIGHT(G53,1) = 0, "D",LEFT(G53,1)-RIGHT(G53,1) &lt; 0, "W2", ISBLANK(G53), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J53" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="18" t="s">
         <v>145</v>
       </c>
@@ -9828,7 +10276,7 @@
         <v>114</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="E54" s="19" t="s">
         <v>147</v>
@@ -9836,8 +10284,16 @@
       <c r="F54" s="135" t="s">
         <v>2405</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I54" t="e" cm="1">
+        <f t="array" ref="I54">_xlfn.IFS(LEFT(G54,1)-RIGHT(G54,1) &gt; 0, "W1",LEFT(G54,1)-RIGHT(G54,1) = 0, "D",LEFT(G54,1)-RIGHT(G54,1) &lt; 0, "W2", ISBLANK(G54), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J54" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="18" t="s">
         <v>148</v>
       </c>
@@ -9848,7 +10304,7 @@
         <v>114</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="E55" s="19" t="s">
         <v>147</v>
@@ -9856,8 +10312,16 @@
       <c r="F55" s="135" t="s">
         <v>2406</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I55" t="e" cm="1">
+        <f t="array" ref="I55">_xlfn.IFS(LEFT(G55,1)-RIGHT(G55,1) &gt; 0, "W1",LEFT(G55,1)-RIGHT(G55,1) = 0, "D",LEFT(G55,1)-RIGHT(G55,1) &lt; 0, "W2", ISBLANK(G55), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J55" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="20" t="s">
         <v>150</v>
       </c>
@@ -9868,7 +10332,7 @@
         <v>135</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="E56" s="21" t="s">
         <v>152</v>
@@ -9876,8 +10340,16 @@
       <c r="F56" s="136" t="s">
         <v>2407</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I56" t="e" cm="1">
+        <f t="array" ref="I56">_xlfn.IFS(LEFT(G56,1)-RIGHT(G56,1) &gt; 0, "W1",LEFT(G56,1)-RIGHT(G56,1) = 0, "D",LEFT(G56,1)-RIGHT(G56,1) &lt; 0, "W2", ISBLANK(G56), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J56" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="20" t="s">
         <v>153</v>
       </c>
@@ -9888,7 +10360,7 @@
         <v>135</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>2511</v>
+        <v>2508</v>
       </c>
       <c r="E57" s="21" t="s">
         <v>152</v>
@@ -9896,8 +10368,16 @@
       <c r="F57" s="136" t="s">
         <v>2408</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I57" t="e" cm="1">
+        <f t="array" ref="I57">_xlfn.IFS(LEFT(G57,1)-RIGHT(G57,1) &gt; 0, "W1",LEFT(G57,1)-RIGHT(G57,1) = 0, "D",LEFT(G57,1)-RIGHT(G57,1) &lt; 0, "W2", ISBLANK(G57), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J57" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="20" t="s">
         <v>155</v>
       </c>
@@ -9908,7 +10388,7 @@
         <v>141</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>2509</v>
+        <v>2506</v>
       </c>
       <c r="E58" s="21" t="s">
         <v>157</v>
@@ -9916,8 +10396,16 @@
       <c r="F58" s="136" t="s">
         <v>2409</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I58" t="e" cm="1">
+        <f t="array" ref="I58">_xlfn.IFS(LEFT(G58,1)-RIGHT(G58,1) &gt; 0, "W1",LEFT(G58,1)-RIGHT(G58,1) = 0, "D",LEFT(G58,1)-RIGHT(G58,1) &lt; 0, "W2", ISBLANK(G58), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J58" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="20" t="s">
         <v>158</v>
       </c>
@@ -9928,7 +10416,7 @@
         <v>141</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>2519</v>
+        <v>2516</v>
       </c>
       <c r="E59" s="21" t="s">
         <v>157</v>
@@ -9936,8 +10424,16 @@
       <c r="F59" s="136" t="s">
         <v>2410</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I59" t="e" cm="1">
+        <f t="array" ref="I59">_xlfn.IFS(LEFT(G59,1)-RIGHT(G59,1) &gt; 0, "W1",LEFT(G59,1)-RIGHT(G59,1) = 0, "D",LEFT(G59,1)-RIGHT(G59,1) &lt; 0, "W2", ISBLANK(G59), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J59" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="20" t="s">
         <v>160</v>
       </c>
@@ -9948,7 +10444,7 @@
         <v>162</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="E60" s="21" t="s">
         <v>163</v>
@@ -9956,8 +10452,16 @@
       <c r="F60" s="136" t="s">
         <v>2411</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I60" t="e" cm="1">
+        <f t="array" ref="I60">_xlfn.IFS(LEFT(G60,1)-RIGHT(G60,1) &gt; 0, "W1",LEFT(G60,1)-RIGHT(G60,1) = 0, "D",LEFT(G60,1)-RIGHT(G60,1) &lt; 0, "W2", ISBLANK(G60), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J60" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="20" t="s">
         <v>164</v>
       </c>
@@ -9968,7 +10472,7 @@
         <v>162</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="E61" s="21" t="s">
         <v>163</v>
@@ -9976,8 +10480,16 @@
       <c r="F61" s="136" t="s">
         <v>2412</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I61" t="e" cm="1">
+        <f t="array" ref="I61">_xlfn.IFS(LEFT(G61,1)-RIGHT(G61,1) &gt; 0, "W1",LEFT(G61,1)-RIGHT(G61,1) = 0, "D",LEFT(G61,1)-RIGHT(G61,1) &lt; 0, "W2", ISBLANK(G61), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J61" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="22" t="s">
         <v>166</v>
       </c>
@@ -9988,7 +10500,7 @@
         <v>168</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>2509</v>
+        <v>2506</v>
       </c>
       <c r="E62" s="23" t="s">
         <v>169</v>
@@ -9996,8 +10508,16 @@
       <c r="F62" s="137" t="s">
         <v>2413</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I62" t="e" cm="1">
+        <f t="array" ref="I62">_xlfn.IFS(LEFT(G62,1)-RIGHT(G62,1) &gt; 0, "W1",LEFT(G62,1)-RIGHT(G62,1) = 0, "D",LEFT(G62,1)-RIGHT(G62,1) &lt; 0, "W2", ISBLANK(G62), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J62" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="22" t="s">
         <v>170</v>
       </c>
@@ -10008,7 +10528,7 @@
         <v>168</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>2518</v>
+        <v>2515</v>
       </c>
       <c r="E63" s="23" t="s">
         <v>169</v>
@@ -10016,8 +10536,16 @@
       <c r="F63" s="137" t="s">
         <v>2414</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I63" t="e" cm="1">
+        <f t="array" ref="I63">_xlfn.IFS(LEFT(G63,1)-RIGHT(G63,1) &gt; 0, "W1",LEFT(G63,1)-RIGHT(G63,1) = 0, "D",LEFT(G63,1)-RIGHT(G63,1) &lt; 0, "W2", ISBLANK(G63), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J63" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="22" t="s">
         <v>172</v>
       </c>
@@ -10028,7 +10556,7 @@
         <v>174</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>2509</v>
+        <v>2506</v>
       </c>
       <c r="E64" s="23" t="s">
         <v>175</v>
@@ -10036,8 +10564,16 @@
       <c r="F64" s="137" t="s">
         <v>2415</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I64" t="e" cm="1">
+        <f t="array" ref="I64">_xlfn.IFS(LEFT(G64,1)-RIGHT(G64,1) &gt; 0, "W1",LEFT(G64,1)-RIGHT(G64,1) = 0, "D",LEFT(G64,1)-RIGHT(G64,1) &lt; 0, "W2", ISBLANK(G64), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J64" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="22" t="s">
         <v>176</v>
       </c>
@@ -10048,7 +10584,7 @@
         <v>174</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>2518</v>
+        <v>2515</v>
       </c>
       <c r="E65" s="23" t="s">
         <v>175</v>
@@ -10056,8 +10592,16 @@
       <c r="F65" s="137" t="s">
         <v>2416</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I65" t="e" cm="1">
+        <f t="array" ref="I65">_xlfn.IFS(LEFT(G65,1)-RIGHT(G65,1) &gt; 0, "W1",LEFT(G65,1)-RIGHT(G65,1) = 0, "D",LEFT(G65,1)-RIGHT(G65,1) &lt; 0, "W2", ISBLANK(G65), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J65" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="22" t="s">
         <v>178</v>
       </c>
@@ -10068,7 +10612,7 @@
         <v>162</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="E66" s="23" t="s">
         <v>180</v>
@@ -10076,8 +10620,16 @@
       <c r="F66" s="137" t="s">
         <v>2417</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I66" t="e" cm="1">
+        <f t="array" ref="I66">_xlfn.IFS(LEFT(G66,1)-RIGHT(G66,1) &gt; 0, "W1",LEFT(G66,1)-RIGHT(G66,1) = 0, "D",LEFT(G66,1)-RIGHT(G66,1) &lt; 0, "W2", ISBLANK(G66), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J66" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="22" t="s">
         <v>181</v>
       </c>
@@ -10088,7 +10640,7 @@
         <v>162</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="E67" s="23" t="s">
         <v>180</v>
@@ -10096,8 +10648,16 @@
       <c r="F67" s="137" t="s">
         <v>2418</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I67" t="e" cm="1">
+        <f t="array" ref="I67">_xlfn.IFS(LEFT(G67,1)-RIGHT(G67,1) &gt; 0, "W1",LEFT(G67,1)-RIGHT(G67,1) = 0, "D",LEFT(G67,1)-RIGHT(G67,1) &lt; 0, "W2", ISBLANK(G67), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J67" s="146" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="24" t="s">
         <v>183</v>
       </c>
@@ -10108,7 +10668,7 @@
         <v>168</v>
       </c>
       <c r="D68" s="25" t="s">
-        <v>2517</v>
+        <v>2514</v>
       </c>
       <c r="E68" s="25" t="s">
         <v>185</v>
@@ -10116,8 +10676,16 @@
       <c r="F68" s="138" t="s">
         <v>2419</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I68" t="e" cm="1">
+        <f t="array" ref="I68">_xlfn.IFS(LEFT(G68,1)-RIGHT(G68,1) &gt; 0, "W1",LEFT(G68,1)-RIGHT(G68,1) = 0, "D",LEFT(G68,1)-RIGHT(G68,1) &lt; 0, "W2", ISBLANK(G68), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J68" s="146" t="e">
+        <f t="shared" ref="J68:J105" si="1">LEFT(G68,1)-RIGHT(G68,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="24" t="s">
         <v>186</v>
       </c>
@@ -10128,7 +10696,7 @@
         <v>168</v>
       </c>
       <c r="D69" s="25" t="s">
-        <v>2508</v>
+        <v>2505</v>
       </c>
       <c r="E69" s="25" t="s">
         <v>185</v>
@@ -10136,8 +10704,16 @@
       <c r="F69" s="138" t="s">
         <v>2420</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I69" t="e" cm="1">
+        <f t="array" ref="I69">_xlfn.IFS(LEFT(G69,1)-RIGHT(G69,1) &gt; 0, "W1",LEFT(G69,1)-RIGHT(G69,1) = 0, "D",LEFT(G69,1)-RIGHT(G69,1) &lt; 0, "W2", ISBLANK(G69), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J69" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="24" t="s">
         <v>188</v>
       </c>
@@ -10148,7 +10724,7 @@
         <v>174</v>
       </c>
       <c r="D70" s="25" t="s">
-        <v>2517</v>
+        <v>2514</v>
       </c>
       <c r="E70" s="25" t="s">
         <v>190</v>
@@ -10156,8 +10732,16 @@
       <c r="F70" s="138" t="s">
         <v>2421</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I70" t="e" cm="1">
+        <f t="array" ref="I70">_xlfn.IFS(LEFT(G70,1)-RIGHT(G70,1) &gt; 0, "W1",LEFT(G70,1)-RIGHT(G70,1) = 0, "D",LEFT(G70,1)-RIGHT(G70,1) &lt; 0, "W2", ISBLANK(G70), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J70" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="24" t="s">
         <v>191</v>
       </c>
@@ -10168,7 +10752,7 @@
         <v>174</v>
       </c>
       <c r="D71" s="25" t="s">
-        <v>2508</v>
+        <v>2505</v>
       </c>
       <c r="E71" s="25" t="s">
         <v>190</v>
@@ -10176,8 +10760,16 @@
       <c r="F71" s="138" t="s">
         <v>2422</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I71" t="e" cm="1">
+        <f t="array" ref="I71">_xlfn.IFS(LEFT(G71,1)-RIGHT(G71,1) &gt; 0, "W1",LEFT(G71,1)-RIGHT(G71,1) = 0, "D",LEFT(G71,1)-RIGHT(G71,1) &lt; 0, "W2", ISBLANK(G71), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J71" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="24" t="s">
         <v>193</v>
       </c>
@@ -10188,7 +10780,7 @@
         <v>162</v>
       </c>
       <c r="D72" s="25" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="E72" s="25" t="s">
         <v>195</v>
@@ -10196,8 +10788,16 @@
       <c r="F72" s="138" t="s">
         <v>2423</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I72" t="e" cm="1">
+        <f t="array" ref="I72">_xlfn.IFS(LEFT(G72,1)-RIGHT(G72,1) &gt; 0, "W1",LEFT(G72,1)-RIGHT(G72,1) = 0, "D",LEFT(G72,1)-RIGHT(G72,1) &lt; 0, "W2", ISBLANK(G72), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J72" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="24" t="s">
         <v>196</v>
       </c>
@@ -10208,7 +10808,7 @@
         <v>162</v>
       </c>
       <c r="D73" s="25" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="E73" s="25" t="s">
         <v>195</v>
@@ -10216,8 +10816,16 @@
       <c r="F73" s="138" t="s">
         <v>2424</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I73" t="e" cm="1">
+        <f t="array" ref="I73">_xlfn.IFS(LEFT(G73,1)-RIGHT(G73,1) &gt; 0, "W1",LEFT(G73,1)-RIGHT(G73,1) = 0, "D",LEFT(G73,1)-RIGHT(G73,1) &lt; 0, "W2", ISBLANK(G73), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J73" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="26" t="s">
         <v>198</v>
       </c>
@@ -10234,8 +10842,16 @@
       <c r="F74" s="139" t="s">
         <v>2425</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I74" t="e" cm="1">
+        <f t="array" ref="I74">_xlfn.IFS(LEFT(G74,1)-RIGHT(G74,1) &gt; 0, "W1",LEFT(G74,1)-RIGHT(G74,1) = 0, "D",LEFT(G74,1)-RIGHT(G74,1) &lt; 0, "W2", ISBLANK(G74), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J74" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="26" t="s">
         <v>202</v>
       </c>
@@ -10252,8 +10868,16 @@
       <c r="F75" s="139" t="s">
         <v>2426</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I75" t="e" cm="1">
+        <f t="array" ref="I75">_xlfn.IFS(LEFT(G75,1)-RIGHT(G75,1) &gt; 0, "W1",LEFT(G75,1)-RIGHT(G75,1) = 0, "D",LEFT(G75,1)-RIGHT(G75,1) &lt; 0, "W2", ISBLANK(G75), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J75" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="26" t="s">
         <v>204</v>
       </c>
@@ -10270,8 +10894,16 @@
       <c r="F76" s="139" t="s">
         <v>2427</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I76" t="e" cm="1">
+        <f t="array" ref="I76">_xlfn.IFS(LEFT(G76,1)-RIGHT(G76,1) &gt; 0, "W1",LEFT(G76,1)-RIGHT(G76,1) = 0, "D",LEFT(G76,1)-RIGHT(G76,1) &lt; 0, "W2", ISBLANK(G76), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J76" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="26" t="s">
         <v>206</v>
       </c>
@@ -10288,8 +10920,16 @@
       <c r="F77" s="139" t="s">
         <v>2428</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I77" t="e" cm="1">
+        <f t="array" ref="I77">_xlfn.IFS(LEFT(G77,1)-RIGHT(G77,1) &gt; 0, "W1",LEFT(G77,1)-RIGHT(G77,1) = 0, "D",LEFT(G77,1)-RIGHT(G77,1) &lt; 0, "W2", ISBLANK(G77), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J77" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="26" t="s">
         <v>207</v>
       </c>
@@ -10306,8 +10946,16 @@
       <c r="F78" s="139" t="s">
         <v>2429</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I78" t="e" cm="1">
+        <f t="array" ref="I78">_xlfn.IFS(LEFT(G78,1)-RIGHT(G78,1) &gt; 0, "W1",LEFT(G78,1)-RIGHT(G78,1) = 0, "D",LEFT(G78,1)-RIGHT(G78,1) &lt; 0, "W2", ISBLANK(G78), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J78" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="26" t="s">
         <v>210</v>
       </c>
@@ -10324,8 +10972,16 @@
       <c r="F79" s="139" t="s">
         <v>2430</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I79" t="e" cm="1">
+        <f t="array" ref="I79">_xlfn.IFS(LEFT(G79,1)-RIGHT(G79,1) &gt; 0, "W1",LEFT(G79,1)-RIGHT(G79,1) = 0, "D",LEFT(G79,1)-RIGHT(G79,1) &lt; 0, "W2", ISBLANK(G79), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J79" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="26" t="s">
         <v>211</v>
       </c>
@@ -10342,8 +10998,16 @@
       <c r="F80" s="139" t="s">
         <v>2431</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I80" t="e" cm="1">
+        <f t="array" ref="I80">_xlfn.IFS(LEFT(G80,1)-RIGHT(G80,1) &gt; 0, "W1",LEFT(G80,1)-RIGHT(G80,1) = 0, "D",LEFT(G80,1)-RIGHT(G80,1) &lt; 0, "W2", ISBLANK(G80), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J80" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="26" t="s">
         <v>213</v>
       </c>
@@ -10360,8 +11024,16 @@
       <c r="F81" s="139" t="s">
         <v>2432</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I81" t="e" cm="1">
+        <f t="array" ref="I81">_xlfn.IFS(LEFT(G81,1)-RIGHT(G81,1) &gt; 0, "W1",LEFT(G81,1)-RIGHT(G81,1) = 0, "D",LEFT(G81,1)-RIGHT(G81,1) &lt; 0, "W2", ISBLANK(G81), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J81" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="26" t="s">
         <v>216</v>
       </c>
@@ -10378,8 +11050,16 @@
       <c r="F82" s="139" t="s">
         <v>2433</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I82" t="e" cm="1">
+        <f t="array" ref="I82">_xlfn.IFS(LEFT(G82,1)-RIGHT(G82,1) &gt; 0, "W1",LEFT(G82,1)-RIGHT(G82,1) = 0, "D",LEFT(G82,1)-RIGHT(G82,1) &lt; 0, "W2", ISBLANK(G82), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J82" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="26" t="s">
         <v>218</v>
       </c>
@@ -10396,8 +11076,16 @@
       <c r="F83" s="139" t="s">
         <v>2434</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I83" t="e" cm="1">
+        <f t="array" ref="I83">_xlfn.IFS(LEFT(G83,1)-RIGHT(G83,1) &gt; 0, "W1",LEFT(G83,1)-RIGHT(G83,1) = 0, "D",LEFT(G83,1)-RIGHT(G83,1) &lt; 0, "W2", ISBLANK(G83), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J83" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="26" t="s">
         <v>219</v>
       </c>
@@ -10414,8 +11102,16 @@
       <c r="F84" s="139" t="s">
         <v>2435</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I84" t="e" cm="1">
+        <f t="array" ref="I84">_xlfn.IFS(LEFT(G84,1)-RIGHT(G84,1) &gt; 0, "W1",LEFT(G84,1)-RIGHT(G84,1) = 0, "D",LEFT(G84,1)-RIGHT(G84,1) &lt; 0, "W2", ISBLANK(G84), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J84" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="26" t="s">
         <v>221</v>
       </c>
@@ -10432,8 +11128,16 @@
       <c r="F85" s="139" t="s">
         <v>2436</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I85" t="e" cm="1">
+        <f t="array" ref="I85">_xlfn.IFS(LEFT(G85,1)-RIGHT(G85,1) &gt; 0, "W1",LEFT(G85,1)-RIGHT(G85,1) = 0, "D",LEFT(G85,1)-RIGHT(G85,1) &lt; 0, "W2", ISBLANK(G85), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J85" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="26" t="s">
         <v>222</v>
       </c>
@@ -10450,8 +11154,16 @@
       <c r="F86" s="139" t="s">
         <v>2437</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I86" t="e" cm="1">
+        <f t="array" ref="I86">_xlfn.IFS(LEFT(G86,1)-RIGHT(G86,1) &gt; 0, "W1",LEFT(G86,1)-RIGHT(G86,1) = 0, "D",LEFT(G86,1)-RIGHT(G86,1) &lt; 0, "W2", ISBLANK(G86), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J86" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="26" t="s">
         <v>223</v>
       </c>
@@ -10468,8 +11180,16 @@
       <c r="F87" s="139" t="s">
         <v>2438</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I87" t="e" cm="1">
+        <f t="array" ref="I87">_xlfn.IFS(LEFT(G87,1)-RIGHT(G87,1) &gt; 0, "W1",LEFT(G87,1)-RIGHT(G87,1) = 0, "D",LEFT(G87,1)-RIGHT(G87,1) &lt; 0, "W2", ISBLANK(G87), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J87" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="26" t="s">
         <v>225</v>
       </c>
@@ -10486,8 +11206,16 @@
       <c r="F88" s="139" t="s">
         <v>2439</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I88" t="e" cm="1">
+        <f t="array" ref="I88">_xlfn.IFS(LEFT(G88,1)-RIGHT(G88,1) &gt; 0, "W1",LEFT(G88,1)-RIGHT(G88,1) = 0, "D",LEFT(G88,1)-RIGHT(G88,1) &lt; 0, "W2", ISBLANK(G88), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J88" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="26" t="s">
         <v>226</v>
       </c>
@@ -10504,8 +11232,16 @@
       <c r="F89" s="139" t="s">
         <v>2440</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I89" t="e" cm="1">
+        <f t="array" ref="I89">_xlfn.IFS(LEFT(G89,1)-RIGHT(G89,1) &gt; 0, "W1",LEFT(G89,1)-RIGHT(G89,1) = 0, "D",LEFT(G89,1)-RIGHT(G89,1) &lt; 0, "W2", ISBLANK(G89), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J89" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="28" t="s">
         <v>227</v>
       </c>
@@ -10522,8 +11258,16 @@
       <c r="F90" s="140" t="s">
         <v>2441</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I90" t="e" cm="1">
+        <f t="array" ref="I90">_xlfn.IFS(LEFT(G90,1)-RIGHT(G90,1) &gt; 0, "W1",LEFT(G90,1)-RIGHT(G90,1) = 0, "D",LEFT(G90,1)-RIGHT(G90,1) &lt; 0, "W2", ISBLANK(G90), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J90" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="28" t="s">
         <v>230</v>
       </c>
@@ -10540,8 +11284,16 @@
       <c r="F91" s="140" t="s">
         <v>2442</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I91" t="e" cm="1">
+        <f t="array" ref="I91">_xlfn.IFS(LEFT(G91,1)-RIGHT(G91,1) &gt; 0, "W1",LEFT(G91,1)-RIGHT(G91,1) = 0, "D",LEFT(G91,1)-RIGHT(G91,1) &lt; 0, "W2", ISBLANK(G91), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J91" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="28" t="s">
         <v>231</v>
       </c>
@@ -10558,8 +11310,16 @@
       <c r="F92" s="140" t="s">
         <v>2443</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I92" t="e" cm="1">
+        <f t="array" ref="I92">_xlfn.IFS(LEFT(G92,1)-RIGHT(G92,1) &gt; 0, "W1",LEFT(G92,1)-RIGHT(G92,1) = 0, "D",LEFT(G92,1)-RIGHT(G92,1) &lt; 0, "W2", ISBLANK(G92), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J92" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="28" t="s">
         <v>234</v>
       </c>
@@ -10576,8 +11336,16 @@
       <c r="F93" s="140" t="s">
         <v>2444</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I93" t="e" cm="1">
+        <f t="array" ref="I93">_xlfn.IFS(LEFT(G93,1)-RIGHT(G93,1) &gt; 0, "W1",LEFT(G93,1)-RIGHT(G93,1) = 0, "D",LEFT(G93,1)-RIGHT(G93,1) &lt; 0, "W2", ISBLANK(G93), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J93" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="28" t="s">
         <v>235</v>
       </c>
@@ -10594,8 +11362,16 @@
       <c r="F94" s="140" t="s">
         <v>2445</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I94" t="e" cm="1">
+        <f t="array" ref="I94">_xlfn.IFS(LEFT(G94,1)-RIGHT(G94,1) &gt; 0, "W1",LEFT(G94,1)-RIGHT(G94,1) = 0, "D",LEFT(G94,1)-RIGHT(G94,1) &lt; 0, "W2", ISBLANK(G94), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J94" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="28" t="s">
         <v>238</v>
       </c>
@@ -10612,8 +11388,16 @@
       <c r="F95" s="140" t="s">
         <v>2446</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I95" t="e" cm="1">
+        <f t="array" ref="I95">_xlfn.IFS(LEFT(G95,1)-RIGHT(G95,1) &gt; 0, "W1",LEFT(G95,1)-RIGHT(G95,1) = 0, "D",LEFT(G95,1)-RIGHT(G95,1) &lt; 0, "W2", ISBLANK(G95), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J95" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="28" t="s">
         <v>239</v>
       </c>
@@ -10630,8 +11414,16 @@
       <c r="F96" s="140" t="s">
         <v>2447</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I96" t="e" cm="1">
+        <f t="array" ref="I96">_xlfn.IFS(LEFT(G96,1)-RIGHT(G96,1) &gt; 0, "W1",LEFT(G96,1)-RIGHT(G96,1) = 0, "D",LEFT(G96,1)-RIGHT(G96,1) &lt; 0, "W2", ISBLANK(G96), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J96" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="28" t="s">
         <v>242</v>
       </c>
@@ -10648,8 +11440,16 @@
       <c r="F97" s="140" t="s">
         <v>2448</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I97" t="e" cm="1">
+        <f t="array" ref="I97">_xlfn.IFS(LEFT(G97,1)-RIGHT(G97,1) &gt; 0, "W1",LEFT(G97,1)-RIGHT(G97,1) = 0, "D",LEFT(G97,1)-RIGHT(G97,1) &lt; 0, "W2", ISBLANK(G97), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J97" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="30" t="s">
         <v>244</v>
       </c>
@@ -10666,8 +11466,16 @@
       <c r="F98" s="141" t="s">
         <v>2449</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I98" t="e" cm="1">
+        <f t="array" ref="I98">_xlfn.IFS(LEFT(G98,1)-RIGHT(G98,1) &gt; 0, "W1",LEFT(G98,1)-RIGHT(G98,1) = 0, "D",LEFT(G98,1)-RIGHT(G98,1) &lt; 0, "W2", ISBLANK(G98), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J98" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="30" t="s">
         <v>247</v>
       </c>
@@ -10684,8 +11492,16 @@
       <c r="F99" s="141" t="s">
         <v>2450</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I99" t="e" cm="1">
+        <f t="array" ref="I99">_xlfn.IFS(LEFT(G99,1)-RIGHT(G99,1) &gt; 0, "W1",LEFT(G99,1)-RIGHT(G99,1) = 0, "D",LEFT(G99,1)-RIGHT(G99,1) &lt; 0, "W2", ISBLANK(G99), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J99" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="30" t="s">
         <v>249</v>
       </c>
@@ -10702,8 +11518,16 @@
       <c r="F100" s="141" t="s">
         <v>2451</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I100" t="e" cm="1">
+        <f t="array" ref="I100">_xlfn.IFS(LEFT(G100,1)-RIGHT(G100,1) &gt; 0, "W1",LEFT(G100,1)-RIGHT(G100,1) = 0, "D",LEFT(G100,1)-RIGHT(G100,1) &lt; 0, "W2", ISBLANK(G100), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J100" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="30" t="s">
         <v>252</v>
       </c>
@@ -10720,8 +11544,16 @@
       <c r="F101" s="141" t="s">
         <v>2452</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I101" t="e" cm="1">
+        <f t="array" ref="I101">_xlfn.IFS(LEFT(G101,1)-RIGHT(G101,1) &gt; 0, "W1",LEFT(G101,1)-RIGHT(G101,1) = 0, "D",LEFT(G101,1)-RIGHT(G101,1) &lt; 0, "W2", ISBLANK(G101), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J101" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="32" t="s">
         <v>253</v>
       </c>
@@ -10738,8 +11570,16 @@
       <c r="F102" s="142" t="s">
         <v>2453</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I102" t="e" cm="1">
+        <f t="array" ref="I102">_xlfn.IFS(LEFT(G102,1)-RIGHT(G102,1) &gt; 0, "W1",LEFT(G102,1)-RIGHT(G102,1) = 0, "D",LEFT(G102,1)-RIGHT(G102,1) &lt; 0, "W2", ISBLANK(G102), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J102" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="32" t="s">
         <v>256</v>
       </c>
@@ -10756,8 +11596,16 @@
       <c r="F103" s="142" t="s">
         <v>2454</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I103" t="e" cm="1">
+        <f t="array" ref="I103">_xlfn.IFS(LEFT(G103,1)-RIGHT(G103,1) &gt; 0, "W1",LEFT(G103,1)-RIGHT(G103,1) = 0, "D",LEFT(G103,1)-RIGHT(G103,1) &lt; 0, "W2", ISBLANK(G103), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J103" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="34" t="s">
         <v>258</v>
       </c>
@@ -10774,8 +11622,16 @@
       <c r="F104" s="143" t="s">
         <v>2455</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I104" t="e" cm="1">
+        <f t="array" ref="I104">_xlfn.IFS(LEFT(G104,1)-RIGHT(G104,1) &gt; 0, "W1",LEFT(G104,1)-RIGHT(G104,1) = 0, "D",LEFT(G104,1)-RIGHT(G104,1) &lt; 0, "W2", ISBLANK(G104), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J104" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="26" t="s">
         <v>261</v>
       </c>
@@ -10791,6 +11647,14 @@
       </c>
       <c r="F105" s="139" t="s">
         <v>2456</v>
+      </c>
+      <c r="I105" t="e" cm="1">
+        <f t="array" ref="I105">_xlfn.IFS(LEFT(G105,1)-RIGHT(G105,1) &gt; 0, "W1",LEFT(G105,1)-RIGHT(G105,1) = 0, "D",LEFT(G105,1)-RIGHT(G105,1) &lt; 0, "W2", ISBLANK(G105), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J105" s="146" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -42057,1035 +42921,1035 @@
   <sheetData>
     <row r="1" spans="5:14" x14ac:dyDescent="0.35">
       <c r="F1" s="145"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
     </row>
     <row r="3" spans="5:14" ht="34.5" x14ac:dyDescent="0.35">
-      <c r="E3" s="148" t="s">
+      <c r="E3" s="147" t="s">
+        <v>2470</v>
+      </c>
+      <c r="F3" s="147" t="s">
+        <v>2471</v>
+      </c>
+      <c r="G3" s="147" t="s">
+        <v>2472</v>
+      </c>
+      <c r="H3" s="147" t="s">
         <v>2473</v>
       </c>
-      <c r="F3" s="148" t="s">
+    </row>
+    <row r="4" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E4" s="148" t="s">
         <v>2474</v>
       </c>
-      <c r="G3" s="148" t="s">
+      <c r="F4" s="148" t="s">
         <v>2475</v>
       </c>
-      <c r="H3" s="148" t="s">
+      <c r="G4" s="148" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="149" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="5" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E5" s="148" t="s">
         <v>2476</v>
       </c>
-    </row>
-    <row r="4" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E4" s="149" t="s">
+      <c r="F5" s="148" t="s">
+        <v>2475</v>
+      </c>
+      <c r="G5" s="148" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="149" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="6" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E6" s="148" t="s">
+        <v>2476</v>
+      </c>
+      <c r="F6" s="148" t="s">
         <v>2477</v>
       </c>
-      <c r="F4" s="149" t="s">
+      <c r="G6" s="148" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="149" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="7" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E7" s="148" t="s">
         <v>2478</v>
       </c>
-      <c r="G4" s="149" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="150" t="s">
+      <c r="F7" s="148" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G7" s="148" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" s="149" t="s">
         <v>2507</v>
       </c>
     </row>
-    <row r="5" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E5" s="149" t="s">
+    <row r="8" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E8" s="148" t="s">
+        <v>2478</v>
+      </c>
+      <c r="F8" s="148" t="s">
         <v>2479</v>
       </c>
-      <c r="F5" s="149" t="s">
+      <c r="G8" s="148" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="149" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="9" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E9" s="148" t="s">
         <v>2478</v>
       </c>
-      <c r="G5" s="149" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="150" t="s">
+      <c r="F9" s="148" t="s">
+        <v>2477</v>
+      </c>
+      <c r="G9" s="148" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="149" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="10" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E10" s="148" t="s">
+        <v>2478</v>
+      </c>
+      <c r="F10" s="148" t="s">
+        <v>2480</v>
+      </c>
+      <c r="G10" s="148" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="149" t="s">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="11" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E11" s="148" t="s">
+        <v>2481</v>
+      </c>
+      <c r="F11" s="148" t="s">
+        <v>2480</v>
+      </c>
+      <c r="G11" s="148" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="149" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="12" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E12" s="148" t="s">
+        <v>2481</v>
+      </c>
+      <c r="F12" s="148" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G12" s="148" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" s="149" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="13" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E13" s="148" t="s">
+        <v>2481</v>
+      </c>
+      <c r="F13" s="148" t="s">
+        <v>2483</v>
+      </c>
+      <c r="G13" s="148" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="149" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="14" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E14" s="148" t="s">
+        <v>2484</v>
+      </c>
+      <c r="F14" s="148" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G14" s="148" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="149" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="15" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E15" s="148" t="s">
+        <v>2484</v>
+      </c>
+      <c r="F15" s="148" t="s">
+        <v>2483</v>
+      </c>
+      <c r="G15" s="148" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="149" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="16" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E16" s="148" t="s">
+        <v>2484</v>
+      </c>
+      <c r="F16" s="148" t="s">
+        <v>2485</v>
+      </c>
+      <c r="G16" s="148" t="s">
+        <v>119</v>
+      </c>
+      <c r="H16" s="149" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="17" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E17" s="148" t="s">
+        <v>2484</v>
+      </c>
+      <c r="F17" s="148" t="s">
+        <v>2486</v>
+      </c>
+      <c r="G17" s="148" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" s="149" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="18" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E18" s="148" t="s">
+        <v>2487</v>
+      </c>
+      <c r="F18" s="148" t="s">
+        <v>2485</v>
+      </c>
+      <c r="G18" s="148" t="s">
+        <v>122</v>
+      </c>
+      <c r="H18" s="149" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="19" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E19" s="148" t="s">
+        <v>2487</v>
+      </c>
+      <c r="F19" s="148" t="s">
+        <v>2486</v>
+      </c>
+      <c r="G19" s="148" t="s">
+        <v>105</v>
+      </c>
+      <c r="H19" s="149" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="20" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E20" s="148" t="s">
+        <v>2487</v>
+      </c>
+      <c r="F20" s="148" t="s">
+        <v>2488</v>
+      </c>
+      <c r="G20" s="148" t="s">
+        <v>134</v>
+      </c>
+      <c r="H20" s="149" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="21" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E21" s="148" t="s">
+        <v>2489</v>
+      </c>
+      <c r="F21" s="148" t="s">
+        <v>2488</v>
+      </c>
+      <c r="G21" s="148" t="s">
+        <v>138</v>
+      </c>
+      <c r="H21" s="149" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="22" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E22" s="148" t="s">
+        <v>2489</v>
+      </c>
+      <c r="F22" s="148" t="s">
+        <v>2490</v>
+      </c>
+      <c r="G22" s="148" t="s">
+        <v>151</v>
+      </c>
+      <c r="H22" s="149" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="23" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E23" s="148" t="s">
+        <v>2489</v>
+      </c>
+      <c r="F23" s="148" t="s">
+        <v>2490</v>
+      </c>
+      <c r="G23" s="148" t="s">
+        <v>154</v>
+      </c>
+      <c r="H23" s="149" t="s">
         <v>2508</v>
       </c>
     </row>
-    <row r="6" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E6" s="149" t="s">
+    <row r="24" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E24" s="148" t="s">
+        <v>2489</v>
+      </c>
+      <c r="F24" s="148" t="s">
+        <v>2491</v>
+      </c>
+      <c r="G24" s="148" t="s">
+        <v>167</v>
+      </c>
+      <c r="H24" s="149" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="25" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E25" s="148" t="s">
+        <v>2492</v>
+      </c>
+      <c r="F25" s="148" t="s">
+        <v>2493</v>
+      </c>
+      <c r="G25" s="148" t="s">
+        <v>184</v>
+      </c>
+      <c r="H25" s="149" t="s">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="26" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E26" s="148" t="s">
+        <v>2492</v>
+      </c>
+      <c r="F26" s="148" t="s">
+        <v>2493</v>
+      </c>
+      <c r="G26" s="148" t="s">
+        <v>187</v>
+      </c>
+      <c r="H26" s="149" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="27" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E27" s="148" t="s">
+        <v>2492</v>
+      </c>
+      <c r="F27" s="148" t="s">
+        <v>2491</v>
+      </c>
+      <c r="G27" s="148" t="s">
+        <v>171</v>
+      </c>
+      <c r="H27" s="149" t="s">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="28" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E28" s="148" t="s">
+        <v>2492</v>
+      </c>
+      <c r="F28" s="148" t="s">
+        <v>2475</v>
+      </c>
+      <c r="G28" s="148" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="149" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="29" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E29" s="148" t="s">
+        <v>2492</v>
+      </c>
+      <c r="F29" s="148" t="s">
+        <v>2477</v>
+      </c>
+      <c r="G29" s="148" t="s">
+        <v>30</v>
+      </c>
+      <c r="H29" s="149" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="30" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E30" s="148" t="s">
+        <v>2494</v>
+      </c>
+      <c r="F30" s="148" t="s">
+        <v>2477</v>
+      </c>
+      <c r="G30" s="148" t="s">
+        <v>33</v>
+      </c>
+      <c r="H30" s="149" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="31" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E31" s="148" t="s">
+        <v>2494</v>
+      </c>
+      <c r="F31" s="148" t="s">
+        <v>2475</v>
+      </c>
+      <c r="G31" s="148" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="149" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="32" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E32" s="148" t="s">
+        <v>2494</v>
+      </c>
+      <c r="F32" s="148" t="s">
         <v>2479</v>
       </c>
-      <c r="F6" s="149" t="s">
+      <c r="G32" s="148" t="s">
+        <v>61</v>
+      </c>
+      <c r="H32" s="149" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="33" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E33" s="148" t="s">
+        <v>2494</v>
+      </c>
+      <c r="F33" s="148" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G33" s="148" t="s">
+        <v>64</v>
+      </c>
+      <c r="H33" s="149" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="34" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E34" s="148" t="s">
+        <v>2495</v>
+      </c>
+      <c r="F34" s="148" t="s">
         <v>2480</v>
       </c>
-      <c r="G6" s="149" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="150" t="s">
+      <c r="G34" s="148" t="s">
+        <v>45</v>
+      </c>
+      <c r="H34" s="149" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="35" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E35" s="148" t="s">
+        <v>2495</v>
+      </c>
+      <c r="F35" s="148" t="s">
+        <v>2480</v>
+      </c>
+      <c r="G35" s="148" t="s">
+        <v>49</v>
+      </c>
+      <c r="H35" s="149" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="36" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E36" s="148" t="s">
+        <v>2495</v>
+      </c>
+      <c r="F36" s="148" t="s">
+        <v>2483</v>
+      </c>
+      <c r="G36" s="148" t="s">
+        <v>91</v>
+      </c>
+      <c r="H36" s="149" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="37" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E37" s="148" t="s">
+        <v>2496</v>
+      </c>
+      <c r="F37" s="148" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G37" s="148" t="s">
+        <v>76</v>
+      </c>
+      <c r="H37" s="149" t="s">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="38" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E38" s="148" t="s">
+        <v>2496</v>
+      </c>
+      <c r="F38" s="148" t="s">
+        <v>2483</v>
+      </c>
+      <c r="G38" s="148" t="s">
+        <v>94</v>
+      </c>
+      <c r="H38" s="149" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="39" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E39" s="148" t="s">
+        <v>2496</v>
+      </c>
+      <c r="F39" s="148" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G39" s="148" t="s">
+        <v>80</v>
+      </c>
+      <c r="H39" s="149" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="40" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E40" s="148" t="s">
+        <v>2496</v>
+      </c>
+      <c r="F40" s="148" t="s">
+        <v>2485</v>
+      </c>
+      <c r="G40" s="148" t="s">
+        <v>124</v>
+      </c>
+      <c r="H40" s="149" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="41" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E41" s="148" t="s">
+        <v>2496</v>
+      </c>
+      <c r="F41" s="148" t="s">
+        <v>2486</v>
+      </c>
+      <c r="G41" s="148" t="s">
+        <v>107</v>
+      </c>
+      <c r="H41" s="149" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="42" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E42" s="148" t="s">
+        <v>2497</v>
+      </c>
+      <c r="F42" s="148" t="s">
+        <v>2485</v>
+      </c>
+      <c r="G42" s="148" t="s">
+        <v>127</v>
+      </c>
+      <c r="H42" s="149" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="43" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E43" s="148" t="s">
+        <v>2497</v>
+      </c>
+      <c r="F43" s="148" t="s">
+        <v>2486</v>
+      </c>
+      <c r="G43" s="148" t="s">
+        <v>111</v>
+      </c>
+      <c r="H43" s="149" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="44" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E44" s="148" t="s">
+        <v>2497</v>
+      </c>
+      <c r="F44" s="148" t="s">
+        <v>2490</v>
+      </c>
+      <c r="G44" s="148" t="s">
+        <v>156</v>
+      </c>
+      <c r="H44" s="149" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="45" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E45" s="148" t="s">
+        <v>2498</v>
+      </c>
+      <c r="F45" s="148" t="s">
+        <v>2488</v>
+      </c>
+      <c r="G45" s="148" t="s">
+        <v>140</v>
+      </c>
+      <c r="H45" s="149" t="s">
         <v>2509</v>
       </c>
     </row>
-    <row r="7" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E7" s="149" t="s">
-        <v>2481</v>
-      </c>
-      <c r="F7" s="149" t="s">
+    <row r="46" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E46" s="148" t="s">
+        <v>2498</v>
+      </c>
+      <c r="F46" s="148" t="s">
+        <v>2488</v>
+      </c>
+      <c r="G46" s="148" t="s">
+        <v>144</v>
+      </c>
+      <c r="H46" s="149" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="47" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E47" s="148" t="s">
+        <v>2498</v>
+      </c>
+      <c r="F47" s="148" t="s">
+        <v>2490</v>
+      </c>
+      <c r="G47" s="148" t="s">
+        <v>159</v>
+      </c>
+      <c r="H47" s="149" t="s">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="48" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E48" s="148" t="s">
+        <v>2498</v>
+      </c>
+      <c r="F48" s="148" t="s">
+        <v>2491</v>
+      </c>
+      <c r="G48" s="148" t="s">
+        <v>173</v>
+      </c>
+      <c r="H48" s="149" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="49" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E49" s="148" t="s">
+        <v>2499</v>
+      </c>
+      <c r="F49" s="148" t="s">
+        <v>2493</v>
+      </c>
+      <c r="G49" s="148" t="s">
+        <v>189</v>
+      </c>
+      <c r="H49" s="149" t="s">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="50" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E50" s="148" t="s">
+        <v>2499</v>
+      </c>
+      <c r="F50" s="148" t="s">
+        <v>2493</v>
+      </c>
+      <c r="G50" s="148" t="s">
+        <v>192</v>
+      </c>
+      <c r="H50" s="149" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="51" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E51" s="148" t="s">
+        <v>2499</v>
+      </c>
+      <c r="F51" s="148" t="s">
+        <v>2491</v>
+      </c>
+      <c r="G51" s="148" t="s">
+        <v>177</v>
+      </c>
+      <c r="H51" s="149" t="s">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="52" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E52" s="148" t="s">
+        <v>2499</v>
+      </c>
+      <c r="F52" s="148" t="s">
+        <v>2477</v>
+      </c>
+      <c r="G52" s="148" t="s">
+        <v>35</v>
+      </c>
+      <c r="H52" s="149" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="53" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E53" s="148" t="s">
+        <v>2499</v>
+      </c>
+      <c r="F53" s="148" t="s">
+        <v>2477</v>
+      </c>
+      <c r="G53" s="148" t="s">
+        <v>38</v>
+      </c>
+      <c r="H53" s="149" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="54" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E54" s="148" t="s">
+        <v>2500</v>
+      </c>
+      <c r="F54" s="148" t="s">
+        <v>2480</v>
+      </c>
+      <c r="G54" s="148" t="s">
+        <v>51</v>
+      </c>
+      <c r="H54" s="149" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="55" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E55" s="148" t="s">
+        <v>2500</v>
+      </c>
+      <c r="F55" s="148" t="s">
+        <v>2480</v>
+      </c>
+      <c r="G55" s="148" t="s">
+        <v>54</v>
+      </c>
+      <c r="H55" s="149" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="56" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E56" s="148" t="s">
+        <v>2500</v>
+      </c>
+      <c r="F56" s="148" t="s">
+        <v>2475</v>
+      </c>
+      <c r="G56" s="148" t="s">
+        <v>21</v>
+      </c>
+      <c r="H56" s="149" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="57" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E57" s="148" t="s">
+        <v>2500</v>
+      </c>
+      <c r="F57" s="148" t="s">
+        <v>2475</v>
+      </c>
+      <c r="G57" s="148" t="s">
+        <v>17</v>
+      </c>
+      <c r="H57" s="149" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="58" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E58" s="148" t="s">
+        <v>2500</v>
+      </c>
+      <c r="F58" s="148" t="s">
         <v>2482</v>
       </c>
-      <c r="G7" s="149" t="s">
-        <v>56</v>
-      </c>
-      <c r="H7" s="150" t="s">
-        <v>2510</v>
-      </c>
-    </row>
-    <row r="8" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E8" s="149" t="s">
-        <v>2481</v>
-      </c>
-      <c r="F8" s="149" t="s">
+      <c r="G58" s="148" t="s">
+        <v>82</v>
+      </c>
+      <c r="H58" s="149" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="59" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E59" s="148" t="s">
+        <v>2500</v>
+      </c>
+      <c r="F59" s="148" t="s">
         <v>2482</v>
       </c>
-      <c r="G8" s="149" t="s">
-        <v>59</v>
-      </c>
-      <c r="H8" s="150" t="s">
+      <c r="G59" s="148" t="s">
+        <v>84</v>
+      </c>
+      <c r="H59" s="149" t="s">
         <v>2511</v>
       </c>
     </row>
-    <row r="9" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E9" s="149" t="s">
-        <v>2481</v>
-      </c>
-      <c r="F9" s="149" t="s">
-        <v>2480</v>
-      </c>
-      <c r="G9" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="150" t="s">
-        <v>2507</v>
-      </c>
-    </row>
-    <row r="10" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E10" s="149" t="s">
-        <v>2481</v>
-      </c>
-      <c r="F10" s="149" t="s">
+    <row r="60" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E60" s="148" t="s">
+        <v>2501</v>
+      </c>
+      <c r="F60" s="148" t="s">
         <v>2483</v>
       </c>
-      <c r="G10" s="149" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="150" t="s">
+      <c r="G60" s="148" t="s">
+        <v>99</v>
+      </c>
+      <c r="H60" s="149" t="s">
         <v>2512</v>
       </c>
     </row>
-    <row r="11" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E11" s="149" t="s">
-        <v>2484</v>
-      </c>
-      <c r="F11" s="149" t="s">
+    <row r="61" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E61" s="148" t="s">
+        <v>2501</v>
+      </c>
+      <c r="F61" s="148" t="s">
         <v>2483</v>
       </c>
-      <c r="G11" s="149" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="150" t="s">
-        <v>2510</v>
-      </c>
-    </row>
-    <row r="12" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E12" s="149" t="s">
-        <v>2484</v>
-      </c>
-      <c r="F12" s="149" t="s">
+      <c r="G61" s="148" t="s">
+        <v>96</v>
+      </c>
+      <c r="H61" s="149" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="62" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E62" s="148" t="s">
+        <v>2501</v>
+      </c>
+      <c r="F62" s="148" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G62" s="148" t="s">
+        <v>66</v>
+      </c>
+      <c r="H62" s="149" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="63" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E63" s="148" t="s">
+        <v>2501</v>
+      </c>
+      <c r="F63" s="148" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G63" s="148" t="s">
+        <v>70</v>
+      </c>
+      <c r="H63" s="149" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="64" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E64" s="148" t="s">
+        <v>2501</v>
+      </c>
+      <c r="F64" s="148" t="s">
+        <v>2488</v>
+      </c>
+      <c r="G64" s="148" t="s">
+        <v>146</v>
+      </c>
+      <c r="H64" s="149" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="65" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E65" s="148" t="s">
+        <v>2501</v>
+      </c>
+      <c r="F65" s="148" t="s">
+        <v>2488</v>
+      </c>
+      <c r="G65" s="148" t="s">
+        <v>149</v>
+      </c>
+      <c r="H65" s="149" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="66" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E66" s="148" t="s">
+        <v>2502</v>
+      </c>
+      <c r="F66" s="148" t="s">
         <v>2485</v>
       </c>
-      <c r="G12" s="149" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" s="150" t="s">
+      <c r="G66" s="148" t="s">
+        <v>132</v>
+      </c>
+      <c r="H66" s="149" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="67" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E67" s="148" t="s">
+        <v>2502</v>
+      </c>
+      <c r="F67" s="148" t="s">
+        <v>2485</v>
+      </c>
+      <c r="G67" s="148" t="s">
+        <v>129</v>
+      </c>
+      <c r="H67" s="149" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="68" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E68" s="148" t="s">
+        <v>2502</v>
+      </c>
+      <c r="F68" s="148" t="s">
+        <v>2486</v>
+      </c>
+      <c r="G68" s="148" t="s">
+        <v>117</v>
+      </c>
+      <c r="H68" s="149" t="s">
         <v>2513</v>
       </c>
     </row>
-    <row r="13" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E13" s="149" t="s">
-        <v>2484</v>
-      </c>
-      <c r="F13" s="149" t="s">
+    <row r="69" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E69" s="148" t="s">
+        <v>2502</v>
+      </c>
+      <c r="F69" s="148" t="s">
         <v>2486</v>
       </c>
-      <c r="G13" s="149" t="s">
-        <v>86</v>
-      </c>
-      <c r="H13" s="150" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="14" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E14" s="149" t="s">
-        <v>2487</v>
-      </c>
-      <c r="F14" s="149" t="s">
-        <v>2485</v>
-      </c>
-      <c r="G14" s="149" t="s">
-        <v>75</v>
-      </c>
-      <c r="H14" s="150" t="s">
-        <v>2515</v>
-      </c>
-    </row>
-    <row r="15" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E15" s="149" t="s">
-        <v>2487</v>
-      </c>
-      <c r="F15" s="149" t="s">
-        <v>2486</v>
-      </c>
-      <c r="G15" s="149" t="s">
-        <v>89</v>
-      </c>
-      <c r="H15" s="150" t="s">
-        <v>2516</v>
-      </c>
-    </row>
-    <row r="16" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E16" s="149" t="s">
-        <v>2487</v>
-      </c>
-      <c r="F16" s="149" t="s">
-        <v>2488</v>
-      </c>
-      <c r="G16" s="149" t="s">
-        <v>119</v>
-      </c>
-      <c r="H16" s="150" t="s">
+      <c r="G69" s="148" t="s">
+        <v>113</v>
+      </c>
+      <c r="H69" s="149" t="s">
         <v>2513</v>
       </c>
     </row>
-    <row r="17" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E17" s="149" t="s">
-        <v>2487</v>
-      </c>
-      <c r="F17" s="149" t="s">
-        <v>2489</v>
-      </c>
-      <c r="G17" s="149" t="s">
-        <v>101</v>
-      </c>
-      <c r="H17" s="150" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="18" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E18" s="149" t="s">
+    <row r="70" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E70" s="148" t="s">
+        <v>2502</v>
+      </c>
+      <c r="F70" s="148" t="s">
+        <v>2493</v>
+      </c>
+      <c r="G70" s="148" t="s">
+        <v>194</v>
+      </c>
+      <c r="H70" s="149" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="71" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E71" s="148" t="s">
+        <v>2502</v>
+      </c>
+      <c r="F71" s="148" t="s">
+        <v>2493</v>
+      </c>
+      <c r="G71" s="148" t="s">
+        <v>197</v>
+      </c>
+      <c r="H71" s="149" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="72" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E72" s="148" t="s">
+        <v>2503</v>
+      </c>
+      <c r="F72" s="148" t="s">
+        <v>2491</v>
+      </c>
+      <c r="G72" s="148" t="s">
+        <v>179</v>
+      </c>
+      <c r="H72" s="149" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="73" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E73" s="148" t="s">
+        <v>2503</v>
+      </c>
+      <c r="F73" s="148" t="s">
+        <v>2491</v>
+      </c>
+      <c r="G73" s="148" t="s">
+        <v>182</v>
+      </c>
+      <c r="H73" s="149" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="74" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E74" s="148" t="s">
+        <v>2503</v>
+      </c>
+      <c r="F74" s="148" t="s">
         <v>2490</v>
       </c>
-      <c r="F18" s="149" t="s">
-        <v>2488</v>
-      </c>
-      <c r="G18" s="149" t="s">
-        <v>122</v>
-      </c>
-      <c r="H18" s="150" t="s">
-        <v>2515</v>
-      </c>
-    </row>
-    <row r="19" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E19" s="149" t="s">
+      <c r="G74" s="148" t="s">
+        <v>165</v>
+      </c>
+      <c r="H74" s="149" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="75" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="E75" s="148" t="s">
+        <v>2503</v>
+      </c>
+      <c r="F75" s="148" t="s">
         <v>2490</v>
       </c>
-      <c r="F19" s="149" t="s">
-        <v>2489</v>
-      </c>
-      <c r="G19" s="149" t="s">
-        <v>105</v>
-      </c>
-      <c r="H19" s="150" t="s">
-        <v>2516</v>
-      </c>
-    </row>
-    <row r="20" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E20" s="149" t="s">
-        <v>2490</v>
-      </c>
-      <c r="F20" s="149" t="s">
-        <v>2491</v>
-      </c>
-      <c r="G20" s="149" t="s">
-        <v>134</v>
-      </c>
-      <c r="H20" s="150" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="21" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E21" s="149" t="s">
-        <v>2492</v>
-      </c>
-      <c r="F21" s="149" t="s">
-        <v>2491</v>
-      </c>
-      <c r="G21" s="149" t="s">
-        <v>138</v>
-      </c>
-      <c r="H21" s="150" t="s">
-        <v>2515</v>
-      </c>
-    </row>
-    <row r="22" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E22" s="149" t="s">
-        <v>2492</v>
-      </c>
-      <c r="F22" s="149" t="s">
-        <v>2493</v>
-      </c>
-      <c r="G22" s="149" t="s">
-        <v>151</v>
-      </c>
-      <c r="H22" s="150" t="s">
-        <v>2516</v>
-      </c>
-    </row>
-    <row r="23" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E23" s="149" t="s">
-        <v>2492</v>
-      </c>
-      <c r="F23" s="149" t="s">
-        <v>2493</v>
-      </c>
-      <c r="G23" s="149" t="s">
-        <v>154</v>
-      </c>
-      <c r="H23" s="150" t="s">
-        <v>2511</v>
-      </c>
-    </row>
-    <row r="24" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E24" s="149" t="s">
-        <v>2492</v>
-      </c>
-      <c r="F24" s="149" t="s">
-        <v>2494</v>
-      </c>
-      <c r="G24" s="149" t="s">
-        <v>167</v>
-      </c>
-      <c r="H24" s="150" t="s">
-        <v>2509</v>
-      </c>
-    </row>
-    <row r="25" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E25" s="149" t="s">
-        <v>2495</v>
-      </c>
-      <c r="F25" s="149" t="s">
-        <v>2496</v>
-      </c>
-      <c r="G25" s="149" t="s">
-        <v>184</v>
-      </c>
-      <c r="H25" s="150" t="s">
-        <v>2517</v>
-      </c>
-    </row>
-    <row r="26" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E26" s="149" t="s">
-        <v>2495</v>
-      </c>
-      <c r="F26" s="149" t="s">
-        <v>2496</v>
-      </c>
-      <c r="G26" s="149" t="s">
-        <v>187</v>
-      </c>
-      <c r="H26" s="150" t="s">
-        <v>2508</v>
-      </c>
-    </row>
-    <row r="27" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E27" s="149" t="s">
-        <v>2495</v>
-      </c>
-      <c r="F27" s="149" t="s">
-        <v>2494</v>
-      </c>
-      <c r="G27" s="149" t="s">
-        <v>171</v>
-      </c>
-      <c r="H27" s="150" t="s">
-        <v>2518</v>
-      </c>
-    </row>
-    <row r="28" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E28" s="149" t="s">
-        <v>2495</v>
-      </c>
-      <c r="F28" s="149" t="s">
-        <v>2478</v>
-      </c>
-      <c r="G28" s="149" t="s">
-        <v>11</v>
-      </c>
-      <c r="H28" s="150" t="s">
+      <c r="G75" s="148" t="s">
+        <v>161</v>
+      </c>
+      <c r="H75" s="149" t="s">
         <v>2513</v>
-      </c>
-    </row>
-    <row r="29" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E29" s="149" t="s">
-        <v>2495</v>
-      </c>
-      <c r="F29" s="149" t="s">
-        <v>2480</v>
-      </c>
-      <c r="G29" s="149" t="s">
-        <v>30</v>
-      </c>
-      <c r="H29" s="150" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="30" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E30" s="149" t="s">
-        <v>2497</v>
-      </c>
-      <c r="F30" s="149" t="s">
-        <v>2480</v>
-      </c>
-      <c r="G30" s="149" t="s">
-        <v>33</v>
-      </c>
-      <c r="H30" s="150" t="s">
-        <v>2515</v>
-      </c>
-    </row>
-    <row r="31" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E31" s="149" t="s">
-        <v>2497</v>
-      </c>
-      <c r="F31" s="149" t="s">
-        <v>2478</v>
-      </c>
-      <c r="G31" s="149" t="s">
-        <v>15</v>
-      </c>
-      <c r="H31" s="150" t="s">
-        <v>2516</v>
-      </c>
-    </row>
-    <row r="32" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E32" s="149" t="s">
-        <v>2497</v>
-      </c>
-      <c r="F32" s="149" t="s">
-        <v>2482</v>
-      </c>
-      <c r="G32" s="149" t="s">
-        <v>61</v>
-      </c>
-      <c r="H32" s="150" t="s">
-        <v>2511</v>
-      </c>
-    </row>
-    <row r="33" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E33" s="149" t="s">
-        <v>2497</v>
-      </c>
-      <c r="F33" s="149" t="s">
-        <v>2482</v>
-      </c>
-      <c r="G33" s="149" t="s">
-        <v>64</v>
-      </c>
-      <c r="H33" s="150" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="34" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E34" s="149" t="s">
-        <v>2498</v>
-      </c>
-      <c r="F34" s="149" t="s">
-        <v>2483</v>
-      </c>
-      <c r="G34" s="149" t="s">
-        <v>45</v>
-      </c>
-      <c r="H34" s="150" t="s">
-        <v>2515</v>
-      </c>
-    </row>
-    <row r="35" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E35" s="149" t="s">
-        <v>2498</v>
-      </c>
-      <c r="F35" s="149" t="s">
-        <v>2483</v>
-      </c>
-      <c r="G35" s="149" t="s">
-        <v>49</v>
-      </c>
-      <c r="H35" s="150" t="s">
-        <v>2516</v>
-      </c>
-    </row>
-    <row r="36" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E36" s="149" t="s">
-        <v>2498</v>
-      </c>
-      <c r="F36" s="149" t="s">
-        <v>2486</v>
-      </c>
-      <c r="G36" s="149" t="s">
-        <v>91</v>
-      </c>
-      <c r="H36" s="150" t="s">
-        <v>2509</v>
-      </c>
-    </row>
-    <row r="37" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E37" s="149" t="s">
-        <v>2499</v>
-      </c>
-      <c r="F37" s="149" t="s">
-        <v>2485</v>
-      </c>
-      <c r="G37" s="149" t="s">
-        <v>76</v>
-      </c>
-      <c r="H37" s="150" t="s">
-        <v>2517</v>
-      </c>
-    </row>
-    <row r="38" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E38" s="149" t="s">
-        <v>2499</v>
-      </c>
-      <c r="F38" s="149" t="s">
-        <v>2486</v>
-      </c>
-      <c r="G38" s="149" t="s">
-        <v>94</v>
-      </c>
-      <c r="H38" s="150" t="s">
-        <v>2508</v>
-      </c>
-    </row>
-    <row r="39" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E39" s="149" t="s">
-        <v>2499</v>
-      </c>
-      <c r="F39" s="149" t="s">
-        <v>2485</v>
-      </c>
-      <c r="G39" s="149" t="s">
-        <v>80</v>
-      </c>
-      <c r="H39" s="150" t="s">
-        <v>2510</v>
-      </c>
-    </row>
-    <row r="40" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E40" s="149" t="s">
-        <v>2499</v>
-      </c>
-      <c r="F40" s="149" t="s">
-        <v>2488</v>
-      </c>
-      <c r="G40" s="149" t="s">
-        <v>124</v>
-      </c>
-      <c r="H40" s="150" t="s">
-        <v>2513</v>
-      </c>
-    </row>
-    <row r="41" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E41" s="149" t="s">
-        <v>2499</v>
-      </c>
-      <c r="F41" s="149" t="s">
-        <v>2489</v>
-      </c>
-      <c r="G41" s="149" t="s">
-        <v>107</v>
-      </c>
-      <c r="H41" s="150" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="42" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E42" s="149" t="s">
-        <v>2500</v>
-      </c>
-      <c r="F42" s="149" t="s">
-        <v>2488</v>
-      </c>
-      <c r="G42" s="149" t="s">
-        <v>127</v>
-      </c>
-      <c r="H42" s="150" t="s">
-        <v>2515</v>
-      </c>
-    </row>
-    <row r="43" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E43" s="149" t="s">
-        <v>2500</v>
-      </c>
-      <c r="F43" s="149" t="s">
-        <v>2489</v>
-      </c>
-      <c r="G43" s="149" t="s">
-        <v>111</v>
-      </c>
-      <c r="H43" s="150" t="s">
-        <v>2516</v>
-      </c>
-    </row>
-    <row r="44" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E44" s="149" t="s">
-        <v>2500</v>
-      </c>
-      <c r="F44" s="149" t="s">
-        <v>2493</v>
-      </c>
-      <c r="G44" s="149" t="s">
-        <v>156</v>
-      </c>
-      <c r="H44" s="150" t="s">
-        <v>2509</v>
-      </c>
-    </row>
-    <row r="45" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E45" s="149" t="s">
-        <v>2501</v>
-      </c>
-      <c r="F45" s="149" t="s">
-        <v>2491</v>
-      </c>
-      <c r="G45" s="149" t="s">
-        <v>140</v>
-      </c>
-      <c r="H45" s="150" t="s">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="46" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E46" s="149" t="s">
-        <v>2501</v>
-      </c>
-      <c r="F46" s="149" t="s">
-        <v>2491</v>
-      </c>
-      <c r="G46" s="149" t="s">
-        <v>144</v>
-      </c>
-      <c r="H46" s="150" t="s">
-        <v>2510</v>
-      </c>
-    </row>
-    <row r="47" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E47" s="149" t="s">
-        <v>2501</v>
-      </c>
-      <c r="F47" s="149" t="s">
-        <v>2493</v>
-      </c>
-      <c r="G47" s="149" t="s">
-        <v>159</v>
-      </c>
-      <c r="H47" s="150" t="s">
-        <v>2519</v>
-      </c>
-    </row>
-    <row r="48" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E48" s="149" t="s">
-        <v>2501</v>
-      </c>
-      <c r="F48" s="149" t="s">
-        <v>2494</v>
-      </c>
-      <c r="G48" s="149" t="s">
-        <v>173</v>
-      </c>
-      <c r="H48" s="150" t="s">
-        <v>2509</v>
-      </c>
-    </row>
-    <row r="49" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E49" s="149" t="s">
-        <v>2502</v>
-      </c>
-      <c r="F49" s="149" t="s">
-        <v>2496</v>
-      </c>
-      <c r="G49" s="149" t="s">
-        <v>189</v>
-      </c>
-      <c r="H49" s="150" t="s">
-        <v>2517</v>
-      </c>
-    </row>
-    <row r="50" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E50" s="149" t="s">
-        <v>2502</v>
-      </c>
-      <c r="F50" s="149" t="s">
-        <v>2496</v>
-      </c>
-      <c r="G50" s="149" t="s">
-        <v>192</v>
-      </c>
-      <c r="H50" s="150" t="s">
-        <v>2508</v>
-      </c>
-    </row>
-    <row r="51" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E51" s="149" t="s">
-        <v>2502</v>
-      </c>
-      <c r="F51" s="149" t="s">
-        <v>2494</v>
-      </c>
-      <c r="G51" s="149" t="s">
-        <v>177</v>
-      </c>
-      <c r="H51" s="150" t="s">
-        <v>2518</v>
-      </c>
-    </row>
-    <row r="52" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E52" s="149" t="s">
-        <v>2502</v>
-      </c>
-      <c r="F52" s="149" t="s">
-        <v>2480</v>
-      </c>
-      <c r="G52" s="149" t="s">
-        <v>35</v>
-      </c>
-      <c r="H52" s="150" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="53" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E53" s="149" t="s">
-        <v>2502</v>
-      </c>
-      <c r="F53" s="149" t="s">
-        <v>2480</v>
-      </c>
-      <c r="G53" s="149" t="s">
-        <v>38</v>
-      </c>
-      <c r="H53" s="150" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="54" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E54" s="149" t="s">
-        <v>2503</v>
-      </c>
-      <c r="F54" s="149" t="s">
-        <v>2483</v>
-      </c>
-      <c r="G54" s="149" t="s">
-        <v>51</v>
-      </c>
-      <c r="H54" s="150" t="s">
-        <v>2515</v>
-      </c>
-    </row>
-    <row r="55" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E55" s="149" t="s">
-        <v>2503</v>
-      </c>
-      <c r="F55" s="149" t="s">
-        <v>2483</v>
-      </c>
-      <c r="G55" s="149" t="s">
-        <v>54</v>
-      </c>
-      <c r="H55" s="150" t="s">
-        <v>2515</v>
-      </c>
-    </row>
-    <row r="56" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E56" s="149" t="s">
-        <v>2503</v>
-      </c>
-      <c r="F56" s="149" t="s">
-        <v>2478</v>
-      </c>
-      <c r="G56" s="149" t="s">
-        <v>21</v>
-      </c>
-      <c r="H56" s="150" t="s">
-        <v>2516</v>
-      </c>
-    </row>
-    <row r="57" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E57" s="149" t="s">
-        <v>2503</v>
-      </c>
-      <c r="F57" s="149" t="s">
-        <v>2478</v>
-      </c>
-      <c r="G57" s="149" t="s">
-        <v>17</v>
-      </c>
-      <c r="H57" s="150" t="s">
-        <v>2516</v>
-      </c>
-    </row>
-    <row r="58" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E58" s="149" t="s">
-        <v>2503</v>
-      </c>
-      <c r="F58" s="149" t="s">
-        <v>2485</v>
-      </c>
-      <c r="G58" s="149" t="s">
-        <v>82</v>
-      </c>
-      <c r="H58" s="150" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="59" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E59" s="149" t="s">
-        <v>2503</v>
-      </c>
-      <c r="F59" s="149" t="s">
-        <v>2485</v>
-      </c>
-      <c r="G59" s="149" t="s">
-        <v>84</v>
-      </c>
-      <c r="H59" s="150" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="60" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E60" s="149" t="s">
-        <v>2504</v>
-      </c>
-      <c r="F60" s="149" t="s">
-        <v>2486</v>
-      </c>
-      <c r="G60" s="149" t="s">
-        <v>99</v>
-      </c>
-      <c r="H60" s="150" t="s">
-        <v>2515</v>
-      </c>
-    </row>
-    <row r="61" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E61" s="149" t="s">
-        <v>2504</v>
-      </c>
-      <c r="F61" s="149" t="s">
-        <v>2486</v>
-      </c>
-      <c r="G61" s="149" t="s">
-        <v>96</v>
-      </c>
-      <c r="H61" s="150" t="s">
-        <v>2515</v>
-      </c>
-    </row>
-    <row r="62" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E62" s="149" t="s">
-        <v>2504</v>
-      </c>
-      <c r="F62" s="149" t="s">
-        <v>2482</v>
-      </c>
-      <c r="G62" s="149" t="s">
-        <v>66</v>
-      </c>
-      <c r="H62" s="150" t="s">
-        <v>2516</v>
-      </c>
-    </row>
-    <row r="63" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E63" s="149" t="s">
-        <v>2504</v>
-      </c>
-      <c r="F63" s="149" t="s">
-        <v>2482</v>
-      </c>
-      <c r="G63" s="149" t="s">
-        <v>70</v>
-      </c>
-      <c r="H63" s="150" t="s">
-        <v>2516</v>
-      </c>
-    </row>
-    <row r="64" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E64" s="149" t="s">
-        <v>2504</v>
-      </c>
-      <c r="F64" s="149" t="s">
-        <v>2491</v>
-      </c>
-      <c r="G64" s="149" t="s">
-        <v>146</v>
-      </c>
-      <c r="H64" s="150" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="65" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E65" s="149" t="s">
-        <v>2504</v>
-      </c>
-      <c r="F65" s="149" t="s">
-        <v>2491</v>
-      </c>
-      <c r="G65" s="149" t="s">
-        <v>149</v>
-      </c>
-      <c r="H65" s="150" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="66" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E66" s="149" t="s">
-        <v>2505</v>
-      </c>
-      <c r="F66" s="149" t="s">
-        <v>2488</v>
-      </c>
-      <c r="G66" s="149" t="s">
-        <v>132</v>
-      </c>
-      <c r="H66" s="150" t="s">
-        <v>2515</v>
-      </c>
-    </row>
-    <row r="67" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E67" s="149" t="s">
-        <v>2505</v>
-      </c>
-      <c r="F67" s="149" t="s">
-        <v>2488</v>
-      </c>
-      <c r="G67" s="149" t="s">
-        <v>129</v>
-      </c>
-      <c r="H67" s="150" t="s">
-        <v>2515</v>
-      </c>
-    </row>
-    <row r="68" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E68" s="149" t="s">
-        <v>2505</v>
-      </c>
-      <c r="F68" s="149" t="s">
-        <v>2489</v>
-      </c>
-      <c r="G68" s="149" t="s">
-        <v>117</v>
-      </c>
-      <c r="H68" s="150" t="s">
-        <v>2516</v>
-      </c>
-    </row>
-    <row r="69" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E69" s="149" t="s">
-        <v>2505</v>
-      </c>
-      <c r="F69" s="149" t="s">
-        <v>2489</v>
-      </c>
-      <c r="G69" s="149" t="s">
-        <v>113</v>
-      </c>
-      <c r="H69" s="150" t="s">
-        <v>2516</v>
-      </c>
-    </row>
-    <row r="70" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E70" s="149" t="s">
-        <v>2505</v>
-      </c>
-      <c r="F70" s="149" t="s">
-        <v>2496</v>
-      </c>
-      <c r="G70" s="149" t="s">
-        <v>194</v>
-      </c>
-      <c r="H70" s="150" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="71" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E71" s="149" t="s">
-        <v>2505</v>
-      </c>
-      <c r="F71" s="149" t="s">
-        <v>2496</v>
-      </c>
-      <c r="G71" s="149" t="s">
-        <v>197</v>
-      </c>
-      <c r="H71" s="150" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="72" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E72" s="149" t="s">
-        <v>2506</v>
-      </c>
-      <c r="F72" s="149" t="s">
-        <v>2494</v>
-      </c>
-      <c r="G72" s="149" t="s">
-        <v>179</v>
-      </c>
-      <c r="H72" s="150" t="s">
-        <v>2515</v>
-      </c>
-    </row>
-    <row r="73" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E73" s="149" t="s">
-        <v>2506</v>
-      </c>
-      <c r="F73" s="149" t="s">
-        <v>2494</v>
-      </c>
-      <c r="G73" s="149" t="s">
-        <v>182</v>
-      </c>
-      <c r="H73" s="150" t="s">
-        <v>2515</v>
-      </c>
-    </row>
-    <row r="74" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E74" s="149" t="s">
-        <v>2506</v>
-      </c>
-      <c r="F74" s="149" t="s">
-        <v>2493</v>
-      </c>
-      <c r="G74" s="149" t="s">
-        <v>165</v>
-      </c>
-      <c r="H74" s="150" t="s">
-        <v>2516</v>
-      </c>
-    </row>
-    <row r="75" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E75" s="149" t="s">
-        <v>2506</v>
-      </c>
-      <c r="F75" s="149" t="s">
-        <v>2493</v>
-      </c>
-      <c r="G75" s="149" t="s">
-        <v>161</v>
-      </c>
-      <c r="H75" s="150" t="s">
-        <v>2516</v>
       </c>
     </row>
   </sheetData>

--- a/FIFAScheduleResults.xlsx
+++ b/FIFAScheduleResults.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World Cup Betting/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="171" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB30738B-8EA8-4390-BF48-70975A310CF3}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B2A727C-352D-4985-974A-5EB12AEC7A56}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA World Cup 2026" sheetId="1" r:id="rId1"/>
     <sheet name="Squad Lists" sheetId="2" r:id="rId2"/>
-    <sheet name="querylist" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FIFA World Cup 2026'!$A$1:$E$105</definedName>
@@ -61,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5897" uniqueCount="2525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5605" uniqueCount="2491">
   <si>
     <t>Match</t>
   </si>
@@ -7471,108 +7470,6 @@
   </si>
   <si>
     <t>game09</t>
-  </si>
-  <si>
-    <t>Date (2026)</t>
-  </si>
-  <si>
-    <t>Match (Group)</t>
-  </si>
-  <si>
-    <t>Teams (ISO 3)</t>
-  </si>
-  <si>
-    <t>Kickoff (Kyiv Time)</t>
-  </si>
-  <si>
-    <t>Thu, Jun 11</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Fri, Jun 12</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>Sat, Jun 13</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>Sun, Jun 14</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Mon, Jun 15</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>Tue, Jun 16</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>Wed, Jun 17</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>Thu, Jun 18</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>Fri, Jun 19</t>
-  </si>
-  <si>
-    <t>Sat, Jun 20</t>
-  </si>
-  <si>
-    <t>Sun, Jun 21</t>
-  </si>
-  <si>
-    <t>Mon, Jun 22</t>
-  </si>
-  <si>
-    <t>Tue, Jun 23</t>
-  </si>
-  <si>
-    <t>Wed, Jun 24</t>
-  </si>
-  <si>
-    <t>Thu, Jun 25</t>
-  </si>
-  <si>
-    <t>Fri, Jun 26</t>
-  </si>
-  <si>
-    <t>Sat, Jun 27</t>
-  </si>
-  <si>
-    <t>Sun, Jun 28</t>
   </si>
   <si>
     <t>22:00</t>
@@ -7642,7 +7539,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7668,20 +7565,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFF9FAFB"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFF9FAFB"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="54">
+  <fills count="53">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7943,12 +7828,6 @@
         <fgColor rgb="FFE0F0E8"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF151517"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -7997,7 +7876,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8431,24 +8310,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="53" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="53" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="53" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8776,7 +8640,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2517</v>
+        <v>2483</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -8785,16 +8649,16 @@
         <v>2361</v>
       </c>
       <c r="G1" s="144" t="s">
-        <v>2522</v>
+        <v>2488</v>
       </c>
       <c r="H1" s="144" t="s">
-        <v>2523</v>
+        <v>2489</v>
       </c>
       <c r="I1" s="144" t="s">
         <v>2457</v>
       </c>
       <c r="J1" s="144" t="s">
-        <v>2524</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -8808,7 +8672,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>2504</v>
+        <v>2470</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -8816,17 +8680,17 @@
       <c r="F2" s="127" t="s">
         <v>2461</v>
       </c>
-      <c r="G2" s="146" t="s">
-        <v>2518</v>
-      </c>
-      <c r="H2" s="150" t="s">
-        <v>2520</v>
+      <c r="G2" s="145" t="s">
+        <v>2484</v>
+      </c>
+      <c r="H2" s="146" t="s">
+        <v>2486</v>
       </c>
       <c r="I2" t="str" cm="1">
         <f t="array" ref="I2">_xlfn.IFS(LEFT(G2,1)-RIGHT(G2,1) &gt; 0, "W1",LEFT(G2,1)-RIGHT(G2,1) = 0, "D",LEFT(G2,1)-RIGHT(G2,1) &lt; 0, "W2", ISBLANK(G2), "")</f>
         <v>W1</v>
       </c>
-      <c r="J2" s="146">
+      <c r="J2" s="145">
         <f>LEFT(G2,1)-RIGHT(G2,1)</f>
         <v>2</v>
       </c>
@@ -8842,7 +8706,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2505</v>
+        <v>2471</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>7</v>
@@ -8850,17 +8714,17 @@
       <c r="F3" s="127" t="s">
         <v>2462</v>
       </c>
-      <c r="G3" s="146" t="s">
-        <v>2519</v>
-      </c>
-      <c r="H3" s="150" t="s">
-        <v>2521</v>
+      <c r="G3" s="145" t="s">
+        <v>2485</v>
+      </c>
+      <c r="H3" s="146" t="s">
+        <v>2487</v>
       </c>
       <c r="I3" t="str" cm="1">
         <f t="array" ref="I3">_xlfn.IFS(LEFT(G3,1)-RIGHT(G3,1) &gt; 0, "W1",LEFT(G3,1)-RIGHT(G3,1) = 0, "D",LEFT(G3,1)-RIGHT(G3,1) &lt; 0, "W2", ISBLANK(G3), "")</f>
         <v>W1</v>
       </c>
-      <c r="J3" s="146">
+      <c r="J3" s="145">
         <f>LEFT(G3,1)-RIGHT(G3,1)</f>
         <v>1</v>
       </c>
@@ -8876,7 +8740,7 @@
         <v>12</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2510</v>
+        <v>2476</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>13</v>
@@ -8888,7 +8752,7 @@
         <f t="array" ref="I4">_xlfn.IFS(LEFT(G4,1)-RIGHT(G4,1)&gt;0,"W1",LEFT(G4,1)-RIGHT(G4,1)=0,"D",LEFT(G4,1)-RIGHT(G4,1)&lt;0,"W2",ISBLANK(G4),"")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J4" s="146" t="e">
+      <c r="J4" s="145" t="e">
         <f t="shared" ref="J4:J67" si="0">LEFT(G4,1)-RIGHT(G4,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -8904,7 +8768,7 @@
         <v>12</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2513</v>
+        <v>2479</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>13</v>
@@ -8916,7 +8780,7 @@
         <f t="array" ref="I5">_xlfn.IFS(LEFT(G5,1)-RIGHT(G5,1) &gt; 0, "W1",LEFT(G5,1)-RIGHT(G5,1) = 0, "D",LEFT(G5,1)-RIGHT(G5,1) &lt; 0, "W2", ISBLANK(G5), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J5" s="146" t="e">
+      <c r="J5" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -8932,7 +8796,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2513</v>
+        <v>2479</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>19</v>
@@ -8944,7 +8808,7 @@
         <f t="array" ref="I6">_xlfn.IFS(LEFT(G6,1)-RIGHT(G6,1) &gt; 0, "W1",LEFT(G6,1)-RIGHT(G6,1) = 0, "D",LEFT(G6,1)-RIGHT(G6,1) &lt; 0, "W2", ISBLANK(G6), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J6" s="146" t="e">
+      <c r="J6" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -8960,7 +8824,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2513</v>
+        <v>2479</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>19</v>
@@ -8972,7 +8836,7 @@
         <f t="array" ref="I7">_xlfn.IFS(LEFT(G7,1)-RIGHT(G7,1) &gt; 0, "W1",LEFT(G7,1)-RIGHT(G7,1) = 0, "D",LEFT(G7,1)-RIGHT(G7,1) &lt; 0, "W2", ISBLANK(G7), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J7" s="146" t="e">
+      <c r="J7" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -8988,7 +8852,7 @@
         <v>24</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>2506</v>
+        <v>2472</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>25</v>
@@ -9000,7 +8864,7 @@
         <f t="array" ref="I8">_xlfn.IFS(LEFT(G8,1)-RIGHT(G8,1) &gt; 0, "W1",LEFT(G8,1)-RIGHT(G8,1) = 0, "D",LEFT(G8,1)-RIGHT(G8,1) &lt; 0, "W2", ISBLANK(G8), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J8" s="146" t="e">
+      <c r="J8" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9016,7 +8880,7 @@
         <v>28</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>2504</v>
+        <v>2470</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>25</v>
@@ -9028,7 +8892,7 @@
         <f t="array" ref="I9">_xlfn.IFS(LEFT(G9,1)-RIGHT(G9,1) &gt; 0, "W1",LEFT(G9,1)-RIGHT(G9,1) = 0, "D",LEFT(G9,1)-RIGHT(G9,1) &lt; 0, "W2", ISBLANK(G9), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J9" s="146" t="e">
+      <c r="J9" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9044,7 +8908,7 @@
         <v>12</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>2511</v>
+        <v>2477</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>31</v>
@@ -9056,7 +8920,7 @@
         <f t="array" ref="I10">_xlfn.IFS(LEFT(G10,1)-RIGHT(G10,1) &gt; 0, "W1",LEFT(G10,1)-RIGHT(G10,1) = 0, "D",LEFT(G10,1)-RIGHT(G10,1) &lt; 0, "W2", ISBLANK(G10), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J10" s="146" t="e">
+      <c r="J10" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9072,7 +8936,7 @@
         <v>12</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>2512</v>
+        <v>2478</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>31</v>
@@ -9084,7 +8948,7 @@
         <f t="array" ref="I11">_xlfn.IFS(LEFT(G11,1)-RIGHT(G11,1) &gt; 0, "W1",LEFT(G11,1)-RIGHT(G11,1) = 0, "D",LEFT(G11,1)-RIGHT(G11,1) &lt; 0, "W2", ISBLANK(G11), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J11" s="146" t="e">
+      <c r="J11" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9100,7 +8964,7 @@
         <v>18</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>2511</v>
+        <v>2477</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>36</v>
@@ -9112,7 +8976,7 @@
         <f t="array" ref="I12">_xlfn.IFS(LEFT(G12,1)-RIGHT(G12,1) &gt; 0, "W1",LEFT(G12,1)-RIGHT(G12,1) = 0, "D",LEFT(G12,1)-RIGHT(G12,1) &lt; 0, "W2", ISBLANK(G12), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J12" s="146" t="e">
+      <c r="J12" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9128,7 +8992,7 @@
         <v>18</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>2511</v>
+        <v>2477</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>36</v>
@@ -9140,7 +9004,7 @@
         <f t="array" ref="I13">_xlfn.IFS(LEFT(G13,1)-RIGHT(G13,1) &gt; 0, "W1",LEFT(G13,1)-RIGHT(G13,1) = 0, "D",LEFT(G13,1)-RIGHT(G13,1) &lt; 0, "W2", ISBLANK(G13), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J13" s="146" t="e">
+      <c r="J13" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9156,7 +9020,7 @@
         <v>28</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>2509</v>
+        <v>2475</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>41</v>
@@ -9168,7 +9032,7 @@
         <f t="array" ref="I14">_xlfn.IFS(LEFT(G14,1)-RIGHT(G14,1) &gt; 0, "W1",LEFT(G14,1)-RIGHT(G14,1) = 0, "D",LEFT(G14,1)-RIGHT(G14,1) &lt; 0, "W2", ISBLANK(G14), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J14" s="146" t="e">
+      <c r="J14" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9184,7 +9048,7 @@
         <v>28</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>2507</v>
+        <v>2473</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>41</v>
@@ -9196,7 +9060,7 @@
         <f t="array" ref="I15">_xlfn.IFS(LEFT(G15,1)-RIGHT(G15,1) &gt; 0, "W1",LEFT(G15,1)-RIGHT(G15,1) = 0, "D",LEFT(G15,1)-RIGHT(G15,1) &lt; 0, "W2", ISBLANK(G15), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J15" s="146" t="e">
+      <c r="J15" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9212,7 +9076,7 @@
         <v>46</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>2512</v>
+        <v>2478</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>47</v>
@@ -9224,7 +9088,7 @@
         <f t="array" ref="I16">_xlfn.IFS(LEFT(G16,1)-RIGHT(G16,1) &gt; 0, "W1",LEFT(G16,1)-RIGHT(G16,1) = 0, "D",LEFT(G16,1)-RIGHT(G16,1) &lt; 0, "W2", ISBLANK(G16), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J16" s="146" t="e">
+      <c r="J16" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9240,7 +9104,7 @@
         <v>46</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>2513</v>
+        <v>2479</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>47</v>
@@ -9252,7 +9116,7 @@
         <f t="array" ref="I17">_xlfn.IFS(LEFT(G17,1)-RIGHT(G17,1) &gt; 0, "W1",LEFT(G17,1)-RIGHT(G17,1) = 0, "D",LEFT(G17,1)-RIGHT(G17,1) &lt; 0, "W2", ISBLANK(G17), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J17" s="146" t="e">
+      <c r="J17" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9268,7 +9132,7 @@
         <v>18</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>2512</v>
+        <v>2478</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>52</v>
@@ -9280,7 +9144,7 @@
         <f t="array" ref="I18">_xlfn.IFS(LEFT(G18,1)-RIGHT(G18,1) &gt; 0, "W1",LEFT(G18,1)-RIGHT(G18,1) = 0, "D",LEFT(G18,1)-RIGHT(G18,1) &lt; 0, "W2", ISBLANK(G18), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J18" s="146" t="e">
+      <c r="J18" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9296,7 +9160,7 @@
         <v>18</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>2512</v>
+        <v>2478</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>52</v>
@@ -9308,7 +9172,7 @@
         <f t="array" ref="I19">_xlfn.IFS(LEFT(G19,1)-RIGHT(G19,1) &gt; 0, "W1",LEFT(G19,1)-RIGHT(G19,1) = 0, "D",LEFT(G19,1)-RIGHT(G19,1) &lt; 0, "W2", ISBLANK(G19), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J19" s="146" t="e">
+      <c r="J19" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9324,7 +9188,7 @@
         <v>24</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>2507</v>
+        <v>2473</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>57</v>
@@ -9336,7 +9200,7 @@
         <f t="array" ref="I20">_xlfn.IFS(LEFT(G20,1)-RIGHT(G20,1) &gt; 0, "W1",LEFT(G20,1)-RIGHT(G20,1) = 0, "D",LEFT(G20,1)-RIGHT(G20,1) &lt; 0, "W2", ISBLANK(G20), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J20" s="146" t="e">
+      <c r="J20" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9352,7 +9216,7 @@
         <v>28</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>2508</v>
+        <v>2474</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>57</v>
@@ -9364,7 +9228,7 @@
         <f t="array" ref="I21">_xlfn.IFS(LEFT(G21,1)-RIGHT(G21,1) &gt; 0, "W1",LEFT(G21,1)-RIGHT(G21,1) = 0, "D",LEFT(G21,1)-RIGHT(G21,1) &lt; 0, "W2", ISBLANK(G21), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J21" s="146" t="e">
+      <c r="J21" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9380,7 +9244,7 @@
         <v>46</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>2508</v>
+        <v>2474</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>62</v>
@@ -9392,7 +9256,7 @@
         <f t="array" ref="I22">_xlfn.IFS(LEFT(G22,1)-RIGHT(G22,1) &gt; 0, "W1",LEFT(G22,1)-RIGHT(G22,1) = 0, "D",LEFT(G22,1)-RIGHT(G22,1) &lt; 0, "W2", ISBLANK(G22), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J22" s="146" t="e">
+      <c r="J22" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9408,7 +9272,7 @@
         <v>46</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>2511</v>
+        <v>2477</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>62</v>
@@ -9420,7 +9284,7 @@
         <f t="array" ref="I23">_xlfn.IFS(LEFT(G23,1)-RIGHT(G23,1) &gt; 0, "W1",LEFT(G23,1)-RIGHT(G23,1) = 0, "D",LEFT(G23,1)-RIGHT(G23,1) &lt; 0, "W2", ISBLANK(G23), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J23" s="146" t="e">
+      <c r="J23" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9436,7 +9300,7 @@
         <v>67</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>2513</v>
+        <v>2479</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>68</v>
@@ -9448,7 +9312,7 @@
         <f t="array" ref="I24">_xlfn.IFS(LEFT(G24,1)-RIGHT(G24,1) &gt; 0, "W1",LEFT(G24,1)-RIGHT(G24,1) = 0, "D",LEFT(G24,1)-RIGHT(G24,1) &lt; 0, "W2", ISBLANK(G24), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J24" s="146" t="e">
+      <c r="J24" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9464,7 +9328,7 @@
         <v>67</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>2513</v>
+        <v>2479</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>68</v>
@@ -9476,7 +9340,7 @@
         <f t="array" ref="I25">_xlfn.IFS(LEFT(G25,1)-RIGHT(G25,1) &gt; 0, "W1",LEFT(G25,1)-RIGHT(G25,1) = 0, "D",LEFT(G25,1)-RIGHT(G25,1) &lt; 0, "W2", ISBLANK(G25), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J25" s="146" t="e">
+      <c r="J25" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9492,7 +9356,7 @@
         <v>73</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>2510</v>
+        <v>2476</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>74</v>
@@ -9504,7 +9368,7 @@
         <f t="array" ref="I26">_xlfn.IFS(LEFT(G26,1)-RIGHT(G26,1) &gt; 0, "W1",LEFT(G26,1)-RIGHT(G26,1) = 0, "D",LEFT(G26,1)-RIGHT(G26,1) &lt; 0, "W2", ISBLANK(G26), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J26" s="146" t="e">
+      <c r="J26" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9520,7 +9384,7 @@
         <v>73</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>2512</v>
+        <v>2478</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>74</v>
@@ -9532,7 +9396,7 @@
         <f t="array" ref="I27">_xlfn.IFS(LEFT(G27,1)-RIGHT(G27,1) &gt; 0, "W1",LEFT(G27,1)-RIGHT(G27,1) = 0, "D",LEFT(G27,1)-RIGHT(G27,1) &lt; 0, "W2", ISBLANK(G27), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J27" s="146" t="e">
+      <c r="J27" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9548,7 +9412,7 @@
         <v>77</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>2514</v>
+        <v>2480</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>78</v>
@@ -9560,7 +9424,7 @@
         <f t="array" ref="I28">_xlfn.IFS(LEFT(G28,1)-RIGHT(G28,1) &gt; 0, "W1",LEFT(G28,1)-RIGHT(G28,1) = 0, "D",LEFT(G28,1)-RIGHT(G28,1) &lt; 0, "W2", ISBLANK(G28), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J28" s="146" t="e">
+      <c r="J28" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9576,7 +9440,7 @@
         <v>77</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>2507</v>
+        <v>2473</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>78</v>
@@ -9588,7 +9452,7 @@
         <f t="array" ref="I29">_xlfn.IFS(LEFT(G29,1)-RIGHT(G29,1) &gt; 0, "W1",LEFT(G29,1)-RIGHT(G29,1) = 0, "D",LEFT(G29,1)-RIGHT(G29,1) &lt; 0, "W2", ISBLANK(G29), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J29" s="146" t="e">
+      <c r="J29" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9604,7 +9468,7 @@
         <v>67</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>2511</v>
+        <v>2477</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>83</v>
@@ -9616,7 +9480,7 @@
         <f t="array" ref="I30">_xlfn.IFS(LEFT(G30,1)-RIGHT(G30,1) &gt; 0, "W1",LEFT(G30,1)-RIGHT(G30,1) = 0, "D",LEFT(G30,1)-RIGHT(G30,1) &lt; 0, "W2", ISBLANK(G30), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J30" s="146" t="e">
+      <c r="J30" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9632,7 +9496,7 @@
         <v>67</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>2511</v>
+        <v>2477</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>83</v>
@@ -9644,7 +9508,7 @@
         <f t="array" ref="I31">_xlfn.IFS(LEFT(G31,1)-RIGHT(G31,1) &gt; 0, "W1",LEFT(G31,1)-RIGHT(G31,1) = 0, "D",LEFT(G31,1)-RIGHT(G31,1) &lt; 0, "W2", ISBLANK(G31), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J31" s="146" t="e">
+      <c r="J31" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9660,7 +9524,7 @@
         <v>73</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>2511</v>
+        <v>2477</v>
       </c>
       <c r="E32" s="13" t="s">
         <v>87</v>
@@ -9672,7 +9536,7 @@
         <f t="array" ref="I32">_xlfn.IFS(LEFT(G32,1)-RIGHT(G32,1) &gt; 0, "W1",LEFT(G32,1)-RIGHT(G32,1) = 0, "D",LEFT(G32,1)-RIGHT(G32,1) &lt; 0, "W2", ISBLANK(G32), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J32" s="146" t="e">
+      <c r="J32" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9688,7 +9552,7 @@
         <v>73</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>2513</v>
+        <v>2479</v>
       </c>
       <c r="E33" s="13" t="s">
         <v>87</v>
@@ -9700,7 +9564,7 @@
         <f t="array" ref="I33">_xlfn.IFS(LEFT(G33,1)-RIGHT(G33,1) &gt; 0, "W1",LEFT(G33,1)-RIGHT(G33,1) = 0, "D",LEFT(G33,1)-RIGHT(G33,1) &lt; 0, "W2", ISBLANK(G33), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J33" s="146" t="e">
+      <c r="J33" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9716,7 +9580,7 @@
         <v>77</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>2506</v>
+        <v>2472</v>
       </c>
       <c r="E34" s="13" t="s">
         <v>92</v>
@@ -9728,7 +9592,7 @@
         <f t="array" ref="I34">_xlfn.IFS(LEFT(G34,1)-RIGHT(G34,1) &gt; 0, "W1",LEFT(G34,1)-RIGHT(G34,1) = 0, "D",LEFT(G34,1)-RIGHT(G34,1) &lt; 0, "W2", ISBLANK(G34), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J34" s="146" t="e">
+      <c r="J34" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9744,7 +9608,7 @@
         <v>77</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>2505</v>
+        <v>2471</v>
       </c>
       <c r="E35" s="13" t="s">
         <v>92</v>
@@ -9756,7 +9620,7 @@
         <f t="array" ref="I35">_xlfn.IFS(LEFT(G35,1)-RIGHT(G35,1) &gt; 0, "W1",LEFT(G35,1)-RIGHT(G35,1) = 0, "D",LEFT(G35,1)-RIGHT(G35,1) &lt; 0, "W2", ISBLANK(G35), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J35" s="146" t="e">
+      <c r="J35" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9772,7 +9636,7 @@
         <v>67</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>2512</v>
+        <v>2478</v>
       </c>
       <c r="E36" s="13" t="s">
         <v>97</v>
@@ -9784,7 +9648,7 @@
         <f t="array" ref="I36">_xlfn.IFS(LEFT(G36,1)-RIGHT(G36,1) &gt; 0, "W1",LEFT(G36,1)-RIGHT(G36,1) = 0, "D",LEFT(G36,1)-RIGHT(G36,1) &lt; 0, "W2", ISBLANK(G36), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J36" s="146" t="e">
+      <c r="J36" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9800,7 +9664,7 @@
         <v>67</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>2512</v>
+        <v>2478</v>
       </c>
       <c r="E37" s="13" t="s">
         <v>97</v>
@@ -9812,7 +9676,7 @@
         <f t="array" ref="I37">_xlfn.IFS(LEFT(G37,1)-RIGHT(G37,1) &gt; 0, "W1",LEFT(G37,1)-RIGHT(G37,1) = 0, "D",LEFT(G37,1)-RIGHT(G37,1) &lt; 0, "W2", ISBLANK(G37), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J37" s="146" t="e">
+      <c r="J37" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9828,7 +9692,7 @@
         <v>102</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>2511</v>
+        <v>2477</v>
       </c>
       <c r="E38" s="15" t="s">
         <v>103</v>
@@ -9840,7 +9704,7 @@
         <f t="array" ref="I38">_xlfn.IFS(LEFT(G38,1)-RIGHT(G38,1) &gt; 0, "W1",LEFT(G38,1)-RIGHT(G38,1) = 0, "D",LEFT(G38,1)-RIGHT(G38,1) &lt; 0, "W2", ISBLANK(G38), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J38" s="146" t="e">
+      <c r="J38" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9856,7 +9720,7 @@
         <v>102</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>2513</v>
+        <v>2479</v>
       </c>
       <c r="E39" s="15" t="s">
         <v>103</v>
@@ -9868,7 +9732,7 @@
         <f t="array" ref="I39">_xlfn.IFS(LEFT(G39,1)-RIGHT(G39,1) &gt; 0, "W1",LEFT(G39,1)-RIGHT(G39,1) = 0, "D",LEFT(G39,1)-RIGHT(G39,1) &lt; 0, "W2", ISBLANK(G39), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J39" s="146" t="e">
+      <c r="J39" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9884,7 +9748,7 @@
         <v>108</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>2511</v>
+        <v>2477</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>109</v>
@@ -9896,7 +9760,7 @@
         <f t="array" ref="I40">_xlfn.IFS(LEFT(G40,1)-RIGHT(G40,1) &gt; 0, "W1",LEFT(G40,1)-RIGHT(G40,1) = 0, "D",LEFT(G40,1)-RIGHT(G40,1) &lt; 0, "W2", ISBLANK(G40), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J40" s="146" t="e">
+      <c r="J40" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9912,7 +9776,7 @@
         <v>108</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>2513</v>
+        <v>2479</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>109</v>
@@ -9924,7 +9788,7 @@
         <f t="array" ref="I41">_xlfn.IFS(LEFT(G41,1)-RIGHT(G41,1) &gt; 0, "W1",LEFT(G41,1)-RIGHT(G41,1) = 0, "D",LEFT(G41,1)-RIGHT(G41,1) &lt; 0, "W2", ISBLANK(G41), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J41" s="146" t="e">
+      <c r="J41" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9940,7 +9804,7 @@
         <v>114</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>2513</v>
+        <v>2479</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>115</v>
@@ -9952,7 +9816,7 @@
         <f t="array" ref="I42">_xlfn.IFS(LEFT(G42,1)-RIGHT(G42,1) &gt; 0, "W1",LEFT(G42,1)-RIGHT(G42,1) = 0, "D",LEFT(G42,1)-RIGHT(G42,1) &lt; 0, "W2", ISBLANK(G42), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J42" s="146" t="e">
+      <c r="J42" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9968,7 +9832,7 @@
         <v>114</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>2513</v>
+        <v>2479</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>115</v>
@@ -9980,7 +9844,7 @@
         <f t="array" ref="I43">_xlfn.IFS(LEFT(G43,1)-RIGHT(G43,1) &gt; 0, "W1",LEFT(G43,1)-RIGHT(G43,1) = 0, "D",LEFT(G43,1)-RIGHT(G43,1) &lt; 0, "W2", ISBLANK(G43), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J43" s="146" t="e">
+      <c r="J43" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -9996,7 +9860,7 @@
         <v>102</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>2510</v>
+        <v>2476</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>120</v>
@@ -10008,7 +9872,7 @@
         <f t="array" ref="I44">_xlfn.IFS(LEFT(G44,1)-RIGHT(G44,1) &gt; 0, "W1",LEFT(G44,1)-RIGHT(G44,1) = 0, "D",LEFT(G44,1)-RIGHT(G44,1) &lt; 0, "W2", ISBLANK(G44), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J44" s="146" t="e">
+      <c r="J44" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10024,7 +9888,7 @@
         <v>102</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>2512</v>
+        <v>2478</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>120</v>
@@ -10036,7 +9900,7 @@
         <f t="array" ref="I45">_xlfn.IFS(LEFT(G45,1)-RIGHT(G45,1) &gt; 0, "W1",LEFT(G45,1)-RIGHT(G45,1) = 0, "D",LEFT(G45,1)-RIGHT(G45,1) &lt; 0, "W2", ISBLANK(G45), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J45" s="146" t="e">
+      <c r="J45" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10052,7 +9916,7 @@
         <v>108</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>2510</v>
+        <v>2476</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>125</v>
@@ -10064,7 +9928,7 @@
         <f t="array" ref="I46">_xlfn.IFS(LEFT(G46,1)-RIGHT(G46,1) &gt; 0, "W1",LEFT(G46,1)-RIGHT(G46,1) = 0, "D",LEFT(G46,1)-RIGHT(G46,1) &lt; 0, "W2", ISBLANK(G46), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J46" s="146" t="e">
+      <c r="J46" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10080,7 +9944,7 @@
         <v>108</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>2512</v>
+        <v>2478</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>125</v>
@@ -10092,7 +9956,7 @@
         <f t="array" ref="I47">_xlfn.IFS(LEFT(G47,1)-RIGHT(G47,1) &gt; 0, "W1",LEFT(G47,1)-RIGHT(G47,1) = 0, "D",LEFT(G47,1)-RIGHT(G47,1) &lt; 0, "W2", ISBLANK(G47), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J47" s="146" t="e">
+      <c r="J47" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10108,7 +9972,7 @@
         <v>114</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>2512</v>
+        <v>2478</v>
       </c>
       <c r="E48" s="17" t="s">
         <v>130</v>
@@ -10120,7 +9984,7 @@
         <f t="array" ref="I48">_xlfn.IFS(LEFT(G48,1)-RIGHT(G48,1) &gt; 0, "W1",LEFT(G48,1)-RIGHT(G48,1) = 0, "D",LEFT(G48,1)-RIGHT(G48,1) &lt; 0, "W2", ISBLANK(G48), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J48" s="146" t="e">
+      <c r="J48" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10136,7 +10000,7 @@
         <v>114</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>2512</v>
+        <v>2478</v>
       </c>
       <c r="E49" s="17" t="s">
         <v>130</v>
@@ -10148,7 +10012,7 @@
         <f t="array" ref="I49">_xlfn.IFS(LEFT(G49,1)-RIGHT(G49,1) &gt; 0, "W1",LEFT(G49,1)-RIGHT(G49,1) = 0, "D",LEFT(G49,1)-RIGHT(G49,1) &lt; 0, "W2", ISBLANK(G49), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J49" s="146" t="e">
+      <c r="J49" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10164,7 +10028,7 @@
         <v>135</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>2511</v>
+        <v>2477</v>
       </c>
       <c r="E50" s="19" t="s">
         <v>136</v>
@@ -10176,7 +10040,7 @@
         <f t="array" ref="I50">_xlfn.IFS(LEFT(G50,1)-RIGHT(G50,1) &gt; 0, "W1",LEFT(G50,1)-RIGHT(G50,1) = 0, "D",LEFT(G50,1)-RIGHT(G50,1) &lt; 0, "W2", ISBLANK(G50), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J50" s="146" t="e">
+      <c r="J50" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10192,7 +10056,7 @@
         <v>135</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>2512</v>
+        <v>2478</v>
       </c>
       <c r="E51" s="19" t="s">
         <v>136</v>
@@ -10204,7 +10068,7 @@
         <f t="array" ref="I51">_xlfn.IFS(LEFT(G51,1)-RIGHT(G51,1) &gt; 0, "W1",LEFT(G51,1)-RIGHT(G51,1) = 0, "D",LEFT(G51,1)-RIGHT(G51,1) &lt; 0, "W2", ISBLANK(G51), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J51" s="146" t="e">
+      <c r="J51" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10220,7 +10084,7 @@
         <v>141</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>2509</v>
+        <v>2475</v>
       </c>
       <c r="E52" s="19" t="s">
         <v>142</v>
@@ -10232,7 +10096,7 @@
         <f t="array" ref="I52">_xlfn.IFS(LEFT(G52,1)-RIGHT(G52,1) &gt; 0, "W1",LEFT(G52,1)-RIGHT(G52,1) = 0, "D",LEFT(G52,1)-RIGHT(G52,1) &lt; 0, "W2", ISBLANK(G52), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J52" s="146" t="e">
+      <c r="J52" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10248,7 +10112,7 @@
         <v>141</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>2507</v>
+        <v>2473</v>
       </c>
       <c r="E53" s="19" t="s">
         <v>142</v>
@@ -10260,7 +10124,7 @@
         <f t="array" ref="I53">_xlfn.IFS(LEFT(G53,1)-RIGHT(G53,1) &gt; 0, "W1",LEFT(G53,1)-RIGHT(G53,1) = 0, "D",LEFT(G53,1)-RIGHT(G53,1) &lt; 0, "W2", ISBLANK(G53), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J53" s="146" t="e">
+      <c r="J53" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10276,7 +10140,7 @@
         <v>114</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>2511</v>
+        <v>2477</v>
       </c>
       <c r="E54" s="19" t="s">
         <v>147</v>
@@ -10288,7 +10152,7 @@
         <f t="array" ref="I54">_xlfn.IFS(LEFT(G54,1)-RIGHT(G54,1) &gt; 0, "W1",LEFT(G54,1)-RIGHT(G54,1) = 0, "D",LEFT(G54,1)-RIGHT(G54,1) &lt; 0, "W2", ISBLANK(G54), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J54" s="146" t="e">
+      <c r="J54" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10304,7 +10168,7 @@
         <v>114</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>2511</v>
+        <v>2477</v>
       </c>
       <c r="E55" s="19" t="s">
         <v>147</v>
@@ -10316,7 +10180,7 @@
         <f t="array" ref="I55">_xlfn.IFS(LEFT(G55,1)-RIGHT(G55,1) &gt; 0, "W1",LEFT(G55,1)-RIGHT(G55,1) = 0, "D",LEFT(G55,1)-RIGHT(G55,1) &lt; 0, "W2", ISBLANK(G55), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J55" s="146" t="e">
+      <c r="J55" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10332,7 +10196,7 @@
         <v>135</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>2513</v>
+        <v>2479</v>
       </c>
       <c r="E56" s="21" t="s">
         <v>152</v>
@@ -10344,7 +10208,7 @@
         <f t="array" ref="I56">_xlfn.IFS(LEFT(G56,1)-RIGHT(G56,1) &gt; 0, "W1",LEFT(G56,1)-RIGHT(G56,1) = 0, "D",LEFT(G56,1)-RIGHT(G56,1) &lt; 0, "W2", ISBLANK(G56), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J56" s="146" t="e">
+      <c r="J56" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10360,7 +10224,7 @@
         <v>135</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>2508</v>
+        <v>2474</v>
       </c>
       <c r="E57" s="21" t="s">
         <v>152</v>
@@ -10372,7 +10236,7 @@
         <f t="array" ref="I57">_xlfn.IFS(LEFT(G57,1)-RIGHT(G57,1) &gt; 0, "W1",LEFT(G57,1)-RIGHT(G57,1) = 0, "D",LEFT(G57,1)-RIGHT(G57,1) &lt; 0, "W2", ISBLANK(G57), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J57" s="146" t="e">
+      <c r="J57" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10388,7 +10252,7 @@
         <v>141</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>2506</v>
+        <v>2472</v>
       </c>
       <c r="E58" s="21" t="s">
         <v>157</v>
@@ -10400,7 +10264,7 @@
         <f t="array" ref="I58">_xlfn.IFS(LEFT(G58,1)-RIGHT(G58,1) &gt; 0, "W1",LEFT(G58,1)-RIGHT(G58,1) = 0, "D",LEFT(G58,1)-RIGHT(G58,1) &lt; 0, "W2", ISBLANK(G58), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J58" s="146" t="e">
+      <c r="J58" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10416,7 +10280,7 @@
         <v>141</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>2516</v>
+        <v>2482</v>
       </c>
       <c r="E59" s="21" t="s">
         <v>157</v>
@@ -10428,7 +10292,7 @@
         <f t="array" ref="I59">_xlfn.IFS(LEFT(G59,1)-RIGHT(G59,1) &gt; 0, "W1",LEFT(G59,1)-RIGHT(G59,1) = 0, "D",LEFT(G59,1)-RIGHT(G59,1) &lt; 0, "W2", ISBLANK(G59), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J59" s="146" t="e">
+      <c r="J59" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10444,7 +10308,7 @@
         <v>162</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>2513</v>
+        <v>2479</v>
       </c>
       <c r="E60" s="21" t="s">
         <v>163</v>
@@ -10456,7 +10320,7 @@
         <f t="array" ref="I60">_xlfn.IFS(LEFT(G60,1)-RIGHT(G60,1) &gt; 0, "W1",LEFT(G60,1)-RIGHT(G60,1) = 0, "D",LEFT(G60,1)-RIGHT(G60,1) &lt; 0, "W2", ISBLANK(G60), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J60" s="146" t="e">
+      <c r="J60" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10472,7 +10336,7 @@
         <v>162</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>2513</v>
+        <v>2479</v>
       </c>
       <c r="E61" s="21" t="s">
         <v>163</v>
@@ -10484,7 +10348,7 @@
         <f t="array" ref="I61">_xlfn.IFS(LEFT(G61,1)-RIGHT(G61,1) &gt; 0, "W1",LEFT(G61,1)-RIGHT(G61,1) = 0, "D",LEFT(G61,1)-RIGHT(G61,1) &lt; 0, "W2", ISBLANK(G61), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J61" s="146" t="e">
+      <c r="J61" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10500,7 +10364,7 @@
         <v>168</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>2506</v>
+        <v>2472</v>
       </c>
       <c r="E62" s="23" t="s">
         <v>169</v>
@@ -10512,7 +10376,7 @@
         <f t="array" ref="I62">_xlfn.IFS(LEFT(G62,1)-RIGHT(G62,1) &gt; 0, "W1",LEFT(G62,1)-RIGHT(G62,1) = 0, "D",LEFT(G62,1)-RIGHT(G62,1) &lt; 0, "W2", ISBLANK(G62), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J62" s="146" t="e">
+      <c r="J62" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10528,7 +10392,7 @@
         <v>168</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>2515</v>
+        <v>2481</v>
       </c>
       <c r="E63" s="23" t="s">
         <v>169</v>
@@ -10540,7 +10404,7 @@
         <f t="array" ref="I63">_xlfn.IFS(LEFT(G63,1)-RIGHT(G63,1) &gt; 0, "W1",LEFT(G63,1)-RIGHT(G63,1) = 0, "D",LEFT(G63,1)-RIGHT(G63,1) &lt; 0, "W2", ISBLANK(G63), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J63" s="146" t="e">
+      <c r="J63" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10556,7 +10420,7 @@
         <v>174</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>2506</v>
+        <v>2472</v>
       </c>
       <c r="E64" s="23" t="s">
         <v>175</v>
@@ -10568,7 +10432,7 @@
         <f t="array" ref="I64">_xlfn.IFS(LEFT(G64,1)-RIGHT(G64,1) &gt; 0, "W1",LEFT(G64,1)-RIGHT(G64,1) = 0, "D",LEFT(G64,1)-RIGHT(G64,1) &lt; 0, "W2", ISBLANK(G64), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J64" s="146" t="e">
+      <c r="J64" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10584,7 +10448,7 @@
         <v>174</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>2515</v>
+        <v>2481</v>
       </c>
       <c r="E65" s="23" t="s">
         <v>175</v>
@@ -10596,7 +10460,7 @@
         <f t="array" ref="I65">_xlfn.IFS(LEFT(G65,1)-RIGHT(G65,1) &gt; 0, "W1",LEFT(G65,1)-RIGHT(G65,1) = 0, "D",LEFT(G65,1)-RIGHT(G65,1) &lt; 0, "W2", ISBLANK(G65), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J65" s="146" t="e">
+      <c r="J65" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10612,7 +10476,7 @@
         <v>162</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>2512</v>
+        <v>2478</v>
       </c>
       <c r="E66" s="23" t="s">
         <v>180</v>
@@ -10624,7 +10488,7 @@
         <f t="array" ref="I66">_xlfn.IFS(LEFT(G66,1)-RIGHT(G66,1) &gt; 0, "W1",LEFT(G66,1)-RIGHT(G66,1) = 0, "D",LEFT(G66,1)-RIGHT(G66,1) &lt; 0, "W2", ISBLANK(G66), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J66" s="146" t="e">
+      <c r="J66" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10640,7 +10504,7 @@
         <v>162</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>2512</v>
+        <v>2478</v>
       </c>
       <c r="E67" s="23" t="s">
         <v>180</v>
@@ -10652,7 +10516,7 @@
         <f t="array" ref="I67">_xlfn.IFS(LEFT(G67,1)-RIGHT(G67,1) &gt; 0, "W1",LEFT(G67,1)-RIGHT(G67,1) = 0, "D",LEFT(G67,1)-RIGHT(G67,1) &lt; 0, "W2", ISBLANK(G67), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J67" s="146" t="e">
+      <c r="J67" s="145" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -10668,7 +10532,7 @@
         <v>168</v>
       </c>
       <c r="D68" s="25" t="s">
-        <v>2514</v>
+        <v>2480</v>
       </c>
       <c r="E68" s="25" t="s">
         <v>185</v>
@@ -10680,7 +10544,7 @@
         <f t="array" ref="I68">_xlfn.IFS(LEFT(G68,1)-RIGHT(G68,1) &gt; 0, "W1",LEFT(G68,1)-RIGHT(G68,1) = 0, "D",LEFT(G68,1)-RIGHT(G68,1) &lt; 0, "W2", ISBLANK(G68), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J68" s="146" t="e">
+      <c r="J68" s="145" t="e">
         <f t="shared" ref="J68:J105" si="1">LEFT(G68,1)-RIGHT(G68,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -10696,7 +10560,7 @@
         <v>168</v>
       </c>
       <c r="D69" s="25" t="s">
-        <v>2505</v>
+        <v>2471</v>
       </c>
       <c r="E69" s="25" t="s">
         <v>185</v>
@@ -10708,7 +10572,7 @@
         <f t="array" ref="I69">_xlfn.IFS(LEFT(G69,1)-RIGHT(G69,1) &gt; 0, "W1",LEFT(G69,1)-RIGHT(G69,1) = 0, "D",LEFT(G69,1)-RIGHT(G69,1) &lt; 0, "W2", ISBLANK(G69), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J69" s="146" t="e">
+      <c r="J69" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -10724,7 +10588,7 @@
         <v>174</v>
       </c>
       <c r="D70" s="25" t="s">
-        <v>2514</v>
+        <v>2480</v>
       </c>
       <c r="E70" s="25" t="s">
         <v>190</v>
@@ -10736,7 +10600,7 @@
         <f t="array" ref="I70">_xlfn.IFS(LEFT(G70,1)-RIGHT(G70,1) &gt; 0, "W1",LEFT(G70,1)-RIGHT(G70,1) = 0, "D",LEFT(G70,1)-RIGHT(G70,1) &lt; 0, "W2", ISBLANK(G70), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J70" s="146" t="e">
+      <c r="J70" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -10752,7 +10616,7 @@
         <v>174</v>
       </c>
       <c r="D71" s="25" t="s">
-        <v>2505</v>
+        <v>2471</v>
       </c>
       <c r="E71" s="25" t="s">
         <v>190</v>
@@ -10764,7 +10628,7 @@
         <f t="array" ref="I71">_xlfn.IFS(LEFT(G71,1)-RIGHT(G71,1) &gt; 0, "W1",LEFT(G71,1)-RIGHT(G71,1) = 0, "D",LEFT(G71,1)-RIGHT(G71,1) &lt; 0, "W2", ISBLANK(G71), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J71" s="146" t="e">
+      <c r="J71" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -10780,7 +10644,7 @@
         <v>162</v>
       </c>
       <c r="D72" s="25" t="s">
-        <v>2511</v>
+        <v>2477</v>
       </c>
       <c r="E72" s="25" t="s">
         <v>195</v>
@@ -10792,7 +10656,7 @@
         <f t="array" ref="I72">_xlfn.IFS(LEFT(G72,1)-RIGHT(G72,1) &gt; 0, "W1",LEFT(G72,1)-RIGHT(G72,1) = 0, "D",LEFT(G72,1)-RIGHT(G72,1) &lt; 0, "W2", ISBLANK(G72), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J72" s="146" t="e">
+      <c r="J72" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -10808,7 +10672,7 @@
         <v>162</v>
       </c>
       <c r="D73" s="25" t="s">
-        <v>2511</v>
+        <v>2477</v>
       </c>
       <c r="E73" s="25" t="s">
         <v>195</v>
@@ -10820,7 +10684,7 @@
         <f t="array" ref="I73">_xlfn.IFS(LEFT(G73,1)-RIGHT(G73,1) &gt; 0, "W1",LEFT(G73,1)-RIGHT(G73,1) = 0, "D",LEFT(G73,1)-RIGHT(G73,1) &lt; 0, "W2", ISBLANK(G73), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J73" s="146" t="e">
+      <c r="J73" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -10846,7 +10710,7 @@
         <f t="array" ref="I74">_xlfn.IFS(LEFT(G74,1)-RIGHT(G74,1) &gt; 0, "W1",LEFT(G74,1)-RIGHT(G74,1) = 0, "D",LEFT(G74,1)-RIGHT(G74,1) &lt; 0, "W2", ISBLANK(G74), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J74" s="146" t="e">
+      <c r="J74" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -10872,7 +10736,7 @@
         <f t="array" ref="I75">_xlfn.IFS(LEFT(G75,1)-RIGHT(G75,1) &gt; 0, "W1",LEFT(G75,1)-RIGHT(G75,1) = 0, "D",LEFT(G75,1)-RIGHT(G75,1) &lt; 0, "W2", ISBLANK(G75), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J75" s="146" t="e">
+      <c r="J75" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -10898,7 +10762,7 @@
         <f t="array" ref="I76">_xlfn.IFS(LEFT(G76,1)-RIGHT(G76,1) &gt; 0, "W1",LEFT(G76,1)-RIGHT(G76,1) = 0, "D",LEFT(G76,1)-RIGHT(G76,1) &lt; 0, "W2", ISBLANK(G76), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J76" s="146" t="e">
+      <c r="J76" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -10924,7 +10788,7 @@
         <f t="array" ref="I77">_xlfn.IFS(LEFT(G77,1)-RIGHT(G77,1) &gt; 0, "W1",LEFT(G77,1)-RIGHT(G77,1) = 0, "D",LEFT(G77,1)-RIGHT(G77,1) &lt; 0, "W2", ISBLANK(G77), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J77" s="146" t="e">
+      <c r="J77" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -10950,7 +10814,7 @@
         <f t="array" ref="I78">_xlfn.IFS(LEFT(G78,1)-RIGHT(G78,1) &gt; 0, "W1",LEFT(G78,1)-RIGHT(G78,1) = 0, "D",LEFT(G78,1)-RIGHT(G78,1) &lt; 0, "W2", ISBLANK(G78), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J78" s="146" t="e">
+      <c r="J78" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -10976,7 +10840,7 @@
         <f t="array" ref="I79">_xlfn.IFS(LEFT(G79,1)-RIGHT(G79,1) &gt; 0, "W1",LEFT(G79,1)-RIGHT(G79,1) = 0, "D",LEFT(G79,1)-RIGHT(G79,1) &lt; 0, "W2", ISBLANK(G79), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J79" s="146" t="e">
+      <c r="J79" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11002,7 +10866,7 @@
         <f t="array" ref="I80">_xlfn.IFS(LEFT(G80,1)-RIGHT(G80,1) &gt; 0, "W1",LEFT(G80,1)-RIGHT(G80,1) = 0, "D",LEFT(G80,1)-RIGHT(G80,1) &lt; 0, "W2", ISBLANK(G80), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J80" s="146" t="e">
+      <c r="J80" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11028,7 +10892,7 @@
         <f t="array" ref="I81">_xlfn.IFS(LEFT(G81,1)-RIGHT(G81,1) &gt; 0, "W1",LEFT(G81,1)-RIGHT(G81,1) = 0, "D",LEFT(G81,1)-RIGHT(G81,1) &lt; 0, "W2", ISBLANK(G81), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J81" s="146" t="e">
+      <c r="J81" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11054,7 +10918,7 @@
         <f t="array" ref="I82">_xlfn.IFS(LEFT(G82,1)-RIGHT(G82,1) &gt; 0, "W1",LEFT(G82,1)-RIGHT(G82,1) = 0, "D",LEFT(G82,1)-RIGHT(G82,1) &lt; 0, "W2", ISBLANK(G82), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J82" s="146" t="e">
+      <c r="J82" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11080,7 +10944,7 @@
         <f t="array" ref="I83">_xlfn.IFS(LEFT(G83,1)-RIGHT(G83,1) &gt; 0, "W1",LEFT(G83,1)-RIGHT(G83,1) = 0, "D",LEFT(G83,1)-RIGHT(G83,1) &lt; 0, "W2", ISBLANK(G83), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J83" s="146" t="e">
+      <c r="J83" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11106,7 +10970,7 @@
         <f t="array" ref="I84">_xlfn.IFS(LEFT(G84,1)-RIGHT(G84,1) &gt; 0, "W1",LEFT(G84,1)-RIGHT(G84,1) = 0, "D",LEFT(G84,1)-RIGHT(G84,1) &lt; 0, "W2", ISBLANK(G84), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J84" s="146" t="e">
+      <c r="J84" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11132,7 +10996,7 @@
         <f t="array" ref="I85">_xlfn.IFS(LEFT(G85,1)-RIGHT(G85,1) &gt; 0, "W1",LEFT(G85,1)-RIGHT(G85,1) = 0, "D",LEFT(G85,1)-RIGHT(G85,1) &lt; 0, "W2", ISBLANK(G85), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J85" s="146" t="e">
+      <c r="J85" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11158,7 +11022,7 @@
         <f t="array" ref="I86">_xlfn.IFS(LEFT(G86,1)-RIGHT(G86,1) &gt; 0, "W1",LEFT(G86,1)-RIGHT(G86,1) = 0, "D",LEFT(G86,1)-RIGHT(G86,1) &lt; 0, "W2", ISBLANK(G86), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J86" s="146" t="e">
+      <c r="J86" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11184,7 +11048,7 @@
         <f t="array" ref="I87">_xlfn.IFS(LEFT(G87,1)-RIGHT(G87,1) &gt; 0, "W1",LEFT(G87,1)-RIGHT(G87,1) = 0, "D",LEFT(G87,1)-RIGHT(G87,1) &lt; 0, "W2", ISBLANK(G87), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J87" s="146" t="e">
+      <c r="J87" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11210,7 +11074,7 @@
         <f t="array" ref="I88">_xlfn.IFS(LEFT(G88,1)-RIGHT(G88,1) &gt; 0, "W1",LEFT(G88,1)-RIGHT(G88,1) = 0, "D",LEFT(G88,1)-RIGHT(G88,1) &lt; 0, "W2", ISBLANK(G88), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J88" s="146" t="e">
+      <c r="J88" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11236,7 +11100,7 @@
         <f t="array" ref="I89">_xlfn.IFS(LEFT(G89,1)-RIGHT(G89,1) &gt; 0, "W1",LEFT(G89,1)-RIGHT(G89,1) = 0, "D",LEFT(G89,1)-RIGHT(G89,1) &lt; 0, "W2", ISBLANK(G89), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J89" s="146" t="e">
+      <c r="J89" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11262,7 +11126,7 @@
         <f t="array" ref="I90">_xlfn.IFS(LEFT(G90,1)-RIGHT(G90,1) &gt; 0, "W1",LEFT(G90,1)-RIGHT(G90,1) = 0, "D",LEFT(G90,1)-RIGHT(G90,1) &lt; 0, "W2", ISBLANK(G90), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J90" s="146" t="e">
+      <c r="J90" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11288,7 +11152,7 @@
         <f t="array" ref="I91">_xlfn.IFS(LEFT(G91,1)-RIGHT(G91,1) &gt; 0, "W1",LEFT(G91,1)-RIGHT(G91,1) = 0, "D",LEFT(G91,1)-RIGHT(G91,1) &lt; 0, "W2", ISBLANK(G91), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J91" s="146" t="e">
+      <c r="J91" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11314,7 +11178,7 @@
         <f t="array" ref="I92">_xlfn.IFS(LEFT(G92,1)-RIGHT(G92,1) &gt; 0, "W1",LEFT(G92,1)-RIGHT(G92,1) = 0, "D",LEFT(G92,1)-RIGHT(G92,1) &lt; 0, "W2", ISBLANK(G92), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J92" s="146" t="e">
+      <c r="J92" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11340,7 +11204,7 @@
         <f t="array" ref="I93">_xlfn.IFS(LEFT(G93,1)-RIGHT(G93,1) &gt; 0, "W1",LEFT(G93,1)-RIGHT(G93,1) = 0, "D",LEFT(G93,1)-RIGHT(G93,1) &lt; 0, "W2", ISBLANK(G93), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J93" s="146" t="e">
+      <c r="J93" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11366,7 +11230,7 @@
         <f t="array" ref="I94">_xlfn.IFS(LEFT(G94,1)-RIGHT(G94,1) &gt; 0, "W1",LEFT(G94,1)-RIGHT(G94,1) = 0, "D",LEFT(G94,1)-RIGHT(G94,1) &lt; 0, "W2", ISBLANK(G94), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J94" s="146" t="e">
+      <c r="J94" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11392,7 +11256,7 @@
         <f t="array" ref="I95">_xlfn.IFS(LEFT(G95,1)-RIGHT(G95,1) &gt; 0, "W1",LEFT(G95,1)-RIGHT(G95,1) = 0, "D",LEFT(G95,1)-RIGHT(G95,1) &lt; 0, "W2", ISBLANK(G95), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J95" s="146" t="e">
+      <c r="J95" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11418,7 +11282,7 @@
         <f t="array" ref="I96">_xlfn.IFS(LEFT(G96,1)-RIGHT(G96,1) &gt; 0, "W1",LEFT(G96,1)-RIGHT(G96,1) = 0, "D",LEFT(G96,1)-RIGHT(G96,1) &lt; 0, "W2", ISBLANK(G96), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J96" s="146" t="e">
+      <c r="J96" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11444,7 +11308,7 @@
         <f t="array" ref="I97">_xlfn.IFS(LEFT(G97,1)-RIGHT(G97,1) &gt; 0, "W1",LEFT(G97,1)-RIGHT(G97,1) = 0, "D",LEFT(G97,1)-RIGHT(G97,1) &lt; 0, "W2", ISBLANK(G97), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J97" s="146" t="e">
+      <c r="J97" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11470,7 +11334,7 @@
         <f t="array" ref="I98">_xlfn.IFS(LEFT(G98,1)-RIGHT(G98,1) &gt; 0, "W1",LEFT(G98,1)-RIGHT(G98,1) = 0, "D",LEFT(G98,1)-RIGHT(G98,1) &lt; 0, "W2", ISBLANK(G98), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J98" s="146" t="e">
+      <c r="J98" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11496,7 +11360,7 @@
         <f t="array" ref="I99">_xlfn.IFS(LEFT(G99,1)-RIGHT(G99,1) &gt; 0, "W1",LEFT(G99,1)-RIGHT(G99,1) = 0, "D",LEFT(G99,1)-RIGHT(G99,1) &lt; 0, "W2", ISBLANK(G99), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J99" s="146" t="e">
+      <c r="J99" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11522,7 +11386,7 @@
         <f t="array" ref="I100">_xlfn.IFS(LEFT(G100,1)-RIGHT(G100,1) &gt; 0, "W1",LEFT(G100,1)-RIGHT(G100,1) = 0, "D",LEFT(G100,1)-RIGHT(G100,1) &lt; 0, "W2", ISBLANK(G100), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J100" s="146" t="e">
+      <c r="J100" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11548,7 +11412,7 @@
         <f t="array" ref="I101">_xlfn.IFS(LEFT(G101,1)-RIGHT(G101,1) &gt; 0, "W1",LEFT(G101,1)-RIGHT(G101,1) = 0, "D",LEFT(G101,1)-RIGHT(G101,1) &lt; 0, "W2", ISBLANK(G101), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J101" s="146" t="e">
+      <c r="J101" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11574,7 +11438,7 @@
         <f t="array" ref="I102">_xlfn.IFS(LEFT(G102,1)-RIGHT(G102,1) &gt; 0, "W1",LEFT(G102,1)-RIGHT(G102,1) = 0, "D",LEFT(G102,1)-RIGHT(G102,1) &lt; 0, "W2", ISBLANK(G102), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J102" s="146" t="e">
+      <c r="J102" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11600,7 +11464,7 @@
         <f t="array" ref="I103">_xlfn.IFS(LEFT(G103,1)-RIGHT(G103,1) &gt; 0, "W1",LEFT(G103,1)-RIGHT(G103,1) = 0, "D",LEFT(G103,1)-RIGHT(G103,1) &lt; 0, "W2", ISBLANK(G103), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J103" s="146" t="e">
+      <c r="J103" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11626,7 +11490,7 @@
         <f t="array" ref="I104">_xlfn.IFS(LEFT(G104,1)-RIGHT(G104,1) &gt; 0, "W1",LEFT(G104,1)-RIGHT(G104,1) = 0, "D",LEFT(G104,1)-RIGHT(G104,1) &lt; 0, "W2", ISBLANK(G104), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J104" s="146" t="e">
+      <c r="J104" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -11652,7 +11516,7 @@
         <f t="array" ref="I105">_xlfn.IFS(LEFT(G105,1)-RIGHT(G105,1) &gt; 0, "W1",LEFT(G105,1)-RIGHT(G105,1) = 0, "D",LEFT(G105,1)-RIGHT(G105,1) &lt; 0, "W2", ISBLANK(G105), "")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J105" s="146" t="e">
+      <c r="J105" s="145" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -42905,1058 +42769,4 @@
   <autoFilter ref="A1:E1249" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7913A399-FAEC-4960-8405-4D9FDC7023F8}">
-  <dimension ref="E1:N75"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="11.26953125" customWidth="1"/>
-    <col min="2" max="2" width="18.90625" customWidth="1"/>
-    <col min="5" max="6" width="14" customWidth="1"/>
-    <col min="11" max="11" width="14.6328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="F1" s="145"/>
-      <c r="G1" s="151"/>
-      <c r="H1" s="151"/>
-      <c r="I1" s="151"/>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-    </row>
-    <row r="3" spans="5:14" ht="34.5" x14ac:dyDescent="0.35">
-      <c r="E3" s="147" t="s">
-        <v>2470</v>
-      </c>
-      <c r="F3" s="147" t="s">
-        <v>2471</v>
-      </c>
-      <c r="G3" s="147" t="s">
-        <v>2472</v>
-      </c>
-      <c r="H3" s="147" t="s">
-        <v>2473</v>
-      </c>
-    </row>
-    <row r="4" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E4" s="148" t="s">
-        <v>2474</v>
-      </c>
-      <c r="F4" s="148" t="s">
-        <v>2475</v>
-      </c>
-      <c r="G4" s="148" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="149" t="s">
-        <v>2504</v>
-      </c>
-    </row>
-    <row r="5" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E5" s="148" t="s">
-        <v>2476</v>
-      </c>
-      <c r="F5" s="148" t="s">
-        <v>2475</v>
-      </c>
-      <c r="G5" s="148" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="149" t="s">
-        <v>2505</v>
-      </c>
-    </row>
-    <row r="6" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E6" s="148" t="s">
-        <v>2476</v>
-      </c>
-      <c r="F6" s="148" t="s">
-        <v>2477</v>
-      </c>
-      <c r="G6" s="148" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="149" t="s">
-        <v>2506</v>
-      </c>
-    </row>
-    <row r="7" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E7" s="148" t="s">
-        <v>2478</v>
-      </c>
-      <c r="F7" s="148" t="s">
-        <v>2479</v>
-      </c>
-      <c r="G7" s="148" t="s">
-        <v>56</v>
-      </c>
-      <c r="H7" s="149" t="s">
-        <v>2507</v>
-      </c>
-    </row>
-    <row r="8" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E8" s="148" t="s">
-        <v>2478</v>
-      </c>
-      <c r="F8" s="148" t="s">
-        <v>2479</v>
-      </c>
-      <c r="G8" s="148" t="s">
-        <v>59</v>
-      </c>
-      <c r="H8" s="149" t="s">
-        <v>2508</v>
-      </c>
-    </row>
-    <row r="9" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E9" s="148" t="s">
-        <v>2478</v>
-      </c>
-      <c r="F9" s="148" t="s">
-        <v>2477</v>
-      </c>
-      <c r="G9" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="149" t="s">
-        <v>2504</v>
-      </c>
-    </row>
-    <row r="10" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E10" s="148" t="s">
-        <v>2478</v>
-      </c>
-      <c r="F10" s="148" t="s">
-        <v>2480</v>
-      </c>
-      <c r="G10" s="148" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="149" t="s">
-        <v>2509</v>
-      </c>
-    </row>
-    <row r="11" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E11" s="148" t="s">
-        <v>2481</v>
-      </c>
-      <c r="F11" s="148" t="s">
-        <v>2480</v>
-      </c>
-      <c r="G11" s="148" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="149" t="s">
-        <v>2507</v>
-      </c>
-    </row>
-    <row r="12" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E12" s="148" t="s">
-        <v>2481</v>
-      </c>
-      <c r="F12" s="148" t="s">
-        <v>2482</v>
-      </c>
-      <c r="G12" s="148" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" s="149" t="s">
-        <v>2510</v>
-      </c>
-    </row>
-    <row r="13" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E13" s="148" t="s">
-        <v>2481</v>
-      </c>
-      <c r="F13" s="148" t="s">
-        <v>2483</v>
-      </c>
-      <c r="G13" s="148" t="s">
-        <v>86</v>
-      </c>
-      <c r="H13" s="149" t="s">
-        <v>2511</v>
-      </c>
-    </row>
-    <row r="14" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E14" s="148" t="s">
-        <v>2484</v>
-      </c>
-      <c r="F14" s="148" t="s">
-        <v>2482</v>
-      </c>
-      <c r="G14" s="148" t="s">
-        <v>75</v>
-      </c>
-      <c r="H14" s="149" t="s">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="15" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E15" s="148" t="s">
-        <v>2484</v>
-      </c>
-      <c r="F15" s="148" t="s">
-        <v>2483</v>
-      </c>
-      <c r="G15" s="148" t="s">
-        <v>89</v>
-      </c>
-      <c r="H15" s="149" t="s">
-        <v>2513</v>
-      </c>
-    </row>
-    <row r="16" spans="5:14" x14ac:dyDescent="0.35">
-      <c r="E16" s="148" t="s">
-        <v>2484</v>
-      </c>
-      <c r="F16" s="148" t="s">
-        <v>2485</v>
-      </c>
-      <c r="G16" s="148" t="s">
-        <v>119</v>
-      </c>
-      <c r="H16" s="149" t="s">
-        <v>2510</v>
-      </c>
-    </row>
-    <row r="17" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E17" s="148" t="s">
-        <v>2484</v>
-      </c>
-      <c r="F17" s="148" t="s">
-        <v>2486</v>
-      </c>
-      <c r="G17" s="148" t="s">
-        <v>101</v>
-      </c>
-      <c r="H17" s="149" t="s">
-        <v>2511</v>
-      </c>
-    </row>
-    <row r="18" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E18" s="148" t="s">
-        <v>2487</v>
-      </c>
-      <c r="F18" s="148" t="s">
-        <v>2485</v>
-      </c>
-      <c r="G18" s="148" t="s">
-        <v>122</v>
-      </c>
-      <c r="H18" s="149" t="s">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="19" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E19" s="148" t="s">
-        <v>2487</v>
-      </c>
-      <c r="F19" s="148" t="s">
-        <v>2486</v>
-      </c>
-      <c r="G19" s="148" t="s">
-        <v>105</v>
-      </c>
-      <c r="H19" s="149" t="s">
-        <v>2513</v>
-      </c>
-    </row>
-    <row r="20" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E20" s="148" t="s">
-        <v>2487</v>
-      </c>
-      <c r="F20" s="148" t="s">
-        <v>2488</v>
-      </c>
-      <c r="G20" s="148" t="s">
-        <v>134</v>
-      </c>
-      <c r="H20" s="149" t="s">
-        <v>2511</v>
-      </c>
-    </row>
-    <row r="21" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E21" s="148" t="s">
-        <v>2489</v>
-      </c>
-      <c r="F21" s="148" t="s">
-        <v>2488</v>
-      </c>
-      <c r="G21" s="148" t="s">
-        <v>138</v>
-      </c>
-      <c r="H21" s="149" t="s">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="22" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E22" s="148" t="s">
-        <v>2489</v>
-      </c>
-      <c r="F22" s="148" t="s">
-        <v>2490</v>
-      </c>
-      <c r="G22" s="148" t="s">
-        <v>151</v>
-      </c>
-      <c r="H22" s="149" t="s">
-        <v>2513</v>
-      </c>
-    </row>
-    <row r="23" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E23" s="148" t="s">
-        <v>2489</v>
-      </c>
-      <c r="F23" s="148" t="s">
-        <v>2490</v>
-      </c>
-      <c r="G23" s="148" t="s">
-        <v>154</v>
-      </c>
-      <c r="H23" s="149" t="s">
-        <v>2508</v>
-      </c>
-    </row>
-    <row r="24" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E24" s="148" t="s">
-        <v>2489</v>
-      </c>
-      <c r="F24" s="148" t="s">
-        <v>2491</v>
-      </c>
-      <c r="G24" s="148" t="s">
-        <v>167</v>
-      </c>
-      <c r="H24" s="149" t="s">
-        <v>2506</v>
-      </c>
-    </row>
-    <row r="25" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E25" s="148" t="s">
-        <v>2492</v>
-      </c>
-      <c r="F25" s="148" t="s">
-        <v>2493</v>
-      </c>
-      <c r="G25" s="148" t="s">
-        <v>184</v>
-      </c>
-      <c r="H25" s="149" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="26" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E26" s="148" t="s">
-        <v>2492</v>
-      </c>
-      <c r="F26" s="148" t="s">
-        <v>2493</v>
-      </c>
-      <c r="G26" s="148" t="s">
-        <v>187</v>
-      </c>
-      <c r="H26" s="149" t="s">
-        <v>2505</v>
-      </c>
-    </row>
-    <row r="27" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E27" s="148" t="s">
-        <v>2492</v>
-      </c>
-      <c r="F27" s="148" t="s">
-        <v>2491</v>
-      </c>
-      <c r="G27" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="H27" s="149" t="s">
-        <v>2515</v>
-      </c>
-    </row>
-    <row r="28" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E28" s="148" t="s">
-        <v>2492</v>
-      </c>
-      <c r="F28" s="148" t="s">
-        <v>2475</v>
-      </c>
-      <c r="G28" s="148" t="s">
-        <v>11</v>
-      </c>
-      <c r="H28" s="149" t="s">
-        <v>2510</v>
-      </c>
-    </row>
-    <row r="29" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E29" s="148" t="s">
-        <v>2492</v>
-      </c>
-      <c r="F29" s="148" t="s">
-        <v>2477</v>
-      </c>
-      <c r="G29" s="148" t="s">
-        <v>30</v>
-      </c>
-      <c r="H29" s="149" t="s">
-        <v>2511</v>
-      </c>
-    </row>
-    <row r="30" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E30" s="148" t="s">
-        <v>2494</v>
-      </c>
-      <c r="F30" s="148" t="s">
-        <v>2477</v>
-      </c>
-      <c r="G30" s="148" t="s">
-        <v>33</v>
-      </c>
-      <c r="H30" s="149" t="s">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="31" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E31" s="148" t="s">
-        <v>2494</v>
-      </c>
-      <c r="F31" s="148" t="s">
-        <v>2475</v>
-      </c>
-      <c r="G31" s="148" t="s">
-        <v>15</v>
-      </c>
-      <c r="H31" s="149" t="s">
-        <v>2513</v>
-      </c>
-    </row>
-    <row r="32" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E32" s="148" t="s">
-        <v>2494</v>
-      </c>
-      <c r="F32" s="148" t="s">
-        <v>2479</v>
-      </c>
-      <c r="G32" s="148" t="s">
-        <v>61</v>
-      </c>
-      <c r="H32" s="149" t="s">
-        <v>2508</v>
-      </c>
-    </row>
-    <row r="33" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E33" s="148" t="s">
-        <v>2494</v>
-      </c>
-      <c r="F33" s="148" t="s">
-        <v>2479</v>
-      </c>
-      <c r="G33" s="148" t="s">
-        <v>64</v>
-      </c>
-      <c r="H33" s="149" t="s">
-        <v>2511</v>
-      </c>
-    </row>
-    <row r="34" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E34" s="148" t="s">
-        <v>2495</v>
-      </c>
-      <c r="F34" s="148" t="s">
-        <v>2480</v>
-      </c>
-      <c r="G34" s="148" t="s">
-        <v>45</v>
-      </c>
-      <c r="H34" s="149" t="s">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="35" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E35" s="148" t="s">
-        <v>2495</v>
-      </c>
-      <c r="F35" s="148" t="s">
-        <v>2480</v>
-      </c>
-      <c r="G35" s="148" t="s">
-        <v>49</v>
-      </c>
-      <c r="H35" s="149" t="s">
-        <v>2513</v>
-      </c>
-    </row>
-    <row r="36" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E36" s="148" t="s">
-        <v>2495</v>
-      </c>
-      <c r="F36" s="148" t="s">
-        <v>2483</v>
-      </c>
-      <c r="G36" s="148" t="s">
-        <v>91</v>
-      </c>
-      <c r="H36" s="149" t="s">
-        <v>2506</v>
-      </c>
-    </row>
-    <row r="37" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E37" s="148" t="s">
-        <v>2496</v>
-      </c>
-      <c r="F37" s="148" t="s">
-        <v>2482</v>
-      </c>
-      <c r="G37" s="148" t="s">
-        <v>76</v>
-      </c>
-      <c r="H37" s="149" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="38" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E38" s="148" t="s">
-        <v>2496</v>
-      </c>
-      <c r="F38" s="148" t="s">
-        <v>2483</v>
-      </c>
-      <c r="G38" s="148" t="s">
-        <v>94</v>
-      </c>
-      <c r="H38" s="149" t="s">
-        <v>2505</v>
-      </c>
-    </row>
-    <row r="39" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E39" s="148" t="s">
-        <v>2496</v>
-      </c>
-      <c r="F39" s="148" t="s">
-        <v>2482</v>
-      </c>
-      <c r="G39" s="148" t="s">
-        <v>80</v>
-      </c>
-      <c r="H39" s="149" t="s">
-        <v>2507</v>
-      </c>
-    </row>
-    <row r="40" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E40" s="148" t="s">
-        <v>2496</v>
-      </c>
-      <c r="F40" s="148" t="s">
-        <v>2485</v>
-      </c>
-      <c r="G40" s="148" t="s">
-        <v>124</v>
-      </c>
-      <c r="H40" s="149" t="s">
-        <v>2510</v>
-      </c>
-    </row>
-    <row r="41" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E41" s="148" t="s">
-        <v>2496</v>
-      </c>
-      <c r="F41" s="148" t="s">
-        <v>2486</v>
-      </c>
-      <c r="G41" s="148" t="s">
-        <v>107</v>
-      </c>
-      <c r="H41" s="149" t="s">
-        <v>2511</v>
-      </c>
-    </row>
-    <row r="42" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E42" s="148" t="s">
-        <v>2497</v>
-      </c>
-      <c r="F42" s="148" t="s">
-        <v>2485</v>
-      </c>
-      <c r="G42" s="148" t="s">
-        <v>127</v>
-      </c>
-      <c r="H42" s="149" t="s">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="43" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E43" s="148" t="s">
-        <v>2497</v>
-      </c>
-      <c r="F43" s="148" t="s">
-        <v>2486</v>
-      </c>
-      <c r="G43" s="148" t="s">
-        <v>111</v>
-      </c>
-      <c r="H43" s="149" t="s">
-        <v>2513</v>
-      </c>
-    </row>
-    <row r="44" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E44" s="148" t="s">
-        <v>2497</v>
-      </c>
-      <c r="F44" s="148" t="s">
-        <v>2490</v>
-      </c>
-      <c r="G44" s="148" t="s">
-        <v>156</v>
-      </c>
-      <c r="H44" s="149" t="s">
-        <v>2506</v>
-      </c>
-    </row>
-    <row r="45" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E45" s="148" t="s">
-        <v>2498</v>
-      </c>
-      <c r="F45" s="148" t="s">
-        <v>2488</v>
-      </c>
-      <c r="G45" s="148" t="s">
-        <v>140</v>
-      </c>
-      <c r="H45" s="149" t="s">
-        <v>2509</v>
-      </c>
-    </row>
-    <row r="46" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E46" s="148" t="s">
-        <v>2498</v>
-      </c>
-      <c r="F46" s="148" t="s">
-        <v>2488</v>
-      </c>
-      <c r="G46" s="148" t="s">
-        <v>144</v>
-      </c>
-      <c r="H46" s="149" t="s">
-        <v>2507</v>
-      </c>
-    </row>
-    <row r="47" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E47" s="148" t="s">
-        <v>2498</v>
-      </c>
-      <c r="F47" s="148" t="s">
-        <v>2490</v>
-      </c>
-      <c r="G47" s="148" t="s">
-        <v>159</v>
-      </c>
-      <c r="H47" s="149" t="s">
-        <v>2516</v>
-      </c>
-    </row>
-    <row r="48" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E48" s="148" t="s">
-        <v>2498</v>
-      </c>
-      <c r="F48" s="148" t="s">
-        <v>2491</v>
-      </c>
-      <c r="G48" s="148" t="s">
-        <v>173</v>
-      </c>
-      <c r="H48" s="149" t="s">
-        <v>2506</v>
-      </c>
-    </row>
-    <row r="49" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E49" s="148" t="s">
-        <v>2499</v>
-      </c>
-      <c r="F49" s="148" t="s">
-        <v>2493</v>
-      </c>
-      <c r="G49" s="148" t="s">
-        <v>189</v>
-      </c>
-      <c r="H49" s="149" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="50" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E50" s="148" t="s">
-        <v>2499</v>
-      </c>
-      <c r="F50" s="148" t="s">
-        <v>2493</v>
-      </c>
-      <c r="G50" s="148" t="s">
-        <v>192</v>
-      </c>
-      <c r="H50" s="149" t="s">
-        <v>2505</v>
-      </c>
-    </row>
-    <row r="51" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E51" s="148" t="s">
-        <v>2499</v>
-      </c>
-      <c r="F51" s="148" t="s">
-        <v>2491</v>
-      </c>
-      <c r="G51" s="148" t="s">
-        <v>177</v>
-      </c>
-      <c r="H51" s="149" t="s">
-        <v>2515</v>
-      </c>
-    </row>
-    <row r="52" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E52" s="148" t="s">
-        <v>2499</v>
-      </c>
-      <c r="F52" s="148" t="s">
-        <v>2477</v>
-      </c>
-      <c r="G52" s="148" t="s">
-        <v>35</v>
-      </c>
-      <c r="H52" s="149" t="s">
-        <v>2511</v>
-      </c>
-    </row>
-    <row r="53" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E53" s="148" t="s">
-        <v>2499</v>
-      </c>
-      <c r="F53" s="148" t="s">
-        <v>2477</v>
-      </c>
-      <c r="G53" s="148" t="s">
-        <v>38</v>
-      </c>
-      <c r="H53" s="149" t="s">
-        <v>2511</v>
-      </c>
-    </row>
-    <row r="54" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E54" s="148" t="s">
-        <v>2500</v>
-      </c>
-      <c r="F54" s="148" t="s">
-        <v>2480</v>
-      </c>
-      <c r="G54" s="148" t="s">
-        <v>51</v>
-      </c>
-      <c r="H54" s="149" t="s">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="55" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E55" s="148" t="s">
-        <v>2500</v>
-      </c>
-      <c r="F55" s="148" t="s">
-        <v>2480</v>
-      </c>
-      <c r="G55" s="148" t="s">
-        <v>54</v>
-      </c>
-      <c r="H55" s="149" t="s">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="56" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E56" s="148" t="s">
-        <v>2500</v>
-      </c>
-      <c r="F56" s="148" t="s">
-        <v>2475</v>
-      </c>
-      <c r="G56" s="148" t="s">
-        <v>21</v>
-      </c>
-      <c r="H56" s="149" t="s">
-        <v>2513</v>
-      </c>
-    </row>
-    <row r="57" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E57" s="148" t="s">
-        <v>2500</v>
-      </c>
-      <c r="F57" s="148" t="s">
-        <v>2475</v>
-      </c>
-      <c r="G57" s="148" t="s">
-        <v>17</v>
-      </c>
-      <c r="H57" s="149" t="s">
-        <v>2513</v>
-      </c>
-    </row>
-    <row r="58" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E58" s="148" t="s">
-        <v>2500</v>
-      </c>
-      <c r="F58" s="148" t="s">
-        <v>2482</v>
-      </c>
-      <c r="G58" s="148" t="s">
-        <v>82</v>
-      </c>
-      <c r="H58" s="149" t="s">
-        <v>2511</v>
-      </c>
-    </row>
-    <row r="59" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E59" s="148" t="s">
-        <v>2500</v>
-      </c>
-      <c r="F59" s="148" t="s">
-        <v>2482</v>
-      </c>
-      <c r="G59" s="148" t="s">
-        <v>84</v>
-      </c>
-      <c r="H59" s="149" t="s">
-        <v>2511</v>
-      </c>
-    </row>
-    <row r="60" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E60" s="148" t="s">
-        <v>2501</v>
-      </c>
-      <c r="F60" s="148" t="s">
-        <v>2483</v>
-      </c>
-      <c r="G60" s="148" t="s">
-        <v>99</v>
-      </c>
-      <c r="H60" s="149" t="s">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="61" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E61" s="148" t="s">
-        <v>2501</v>
-      </c>
-      <c r="F61" s="148" t="s">
-        <v>2483</v>
-      </c>
-      <c r="G61" s="148" t="s">
-        <v>96</v>
-      </c>
-      <c r="H61" s="149" t="s">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="62" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E62" s="148" t="s">
-        <v>2501</v>
-      </c>
-      <c r="F62" s="148" t="s">
-        <v>2479</v>
-      </c>
-      <c r="G62" s="148" t="s">
-        <v>66</v>
-      </c>
-      <c r="H62" s="149" t="s">
-        <v>2513</v>
-      </c>
-    </row>
-    <row r="63" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E63" s="148" t="s">
-        <v>2501</v>
-      </c>
-      <c r="F63" s="148" t="s">
-        <v>2479</v>
-      </c>
-      <c r="G63" s="148" t="s">
-        <v>70</v>
-      </c>
-      <c r="H63" s="149" t="s">
-        <v>2513</v>
-      </c>
-    </row>
-    <row r="64" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E64" s="148" t="s">
-        <v>2501</v>
-      </c>
-      <c r="F64" s="148" t="s">
-        <v>2488</v>
-      </c>
-      <c r="G64" s="148" t="s">
-        <v>146</v>
-      </c>
-      <c r="H64" s="149" t="s">
-        <v>2511</v>
-      </c>
-    </row>
-    <row r="65" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E65" s="148" t="s">
-        <v>2501</v>
-      </c>
-      <c r="F65" s="148" t="s">
-        <v>2488</v>
-      </c>
-      <c r="G65" s="148" t="s">
-        <v>149</v>
-      </c>
-      <c r="H65" s="149" t="s">
-        <v>2511</v>
-      </c>
-    </row>
-    <row r="66" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E66" s="148" t="s">
-        <v>2502</v>
-      </c>
-      <c r="F66" s="148" t="s">
-        <v>2485</v>
-      </c>
-      <c r="G66" s="148" t="s">
-        <v>132</v>
-      </c>
-      <c r="H66" s="149" t="s">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="67" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E67" s="148" t="s">
-        <v>2502</v>
-      </c>
-      <c r="F67" s="148" t="s">
-        <v>2485</v>
-      </c>
-      <c r="G67" s="148" t="s">
-        <v>129</v>
-      </c>
-      <c r="H67" s="149" t="s">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="68" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E68" s="148" t="s">
-        <v>2502</v>
-      </c>
-      <c r="F68" s="148" t="s">
-        <v>2486</v>
-      </c>
-      <c r="G68" s="148" t="s">
-        <v>117</v>
-      </c>
-      <c r="H68" s="149" t="s">
-        <v>2513</v>
-      </c>
-    </row>
-    <row r="69" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E69" s="148" t="s">
-        <v>2502</v>
-      </c>
-      <c r="F69" s="148" t="s">
-        <v>2486</v>
-      </c>
-      <c r="G69" s="148" t="s">
-        <v>113</v>
-      </c>
-      <c r="H69" s="149" t="s">
-        <v>2513</v>
-      </c>
-    </row>
-    <row r="70" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E70" s="148" t="s">
-        <v>2502</v>
-      </c>
-      <c r="F70" s="148" t="s">
-        <v>2493</v>
-      </c>
-      <c r="G70" s="148" t="s">
-        <v>194</v>
-      </c>
-      <c r="H70" s="149" t="s">
-        <v>2511</v>
-      </c>
-    </row>
-    <row r="71" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E71" s="148" t="s">
-        <v>2502</v>
-      </c>
-      <c r="F71" s="148" t="s">
-        <v>2493</v>
-      </c>
-      <c r="G71" s="148" t="s">
-        <v>197</v>
-      </c>
-      <c r="H71" s="149" t="s">
-        <v>2511</v>
-      </c>
-    </row>
-    <row r="72" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E72" s="148" t="s">
-        <v>2503</v>
-      </c>
-      <c r="F72" s="148" t="s">
-        <v>2491</v>
-      </c>
-      <c r="G72" s="148" t="s">
-        <v>179</v>
-      </c>
-      <c r="H72" s="149" t="s">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="73" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E73" s="148" t="s">
-        <v>2503</v>
-      </c>
-      <c r="F73" s="148" t="s">
-        <v>2491</v>
-      </c>
-      <c r="G73" s="148" t="s">
-        <v>182</v>
-      </c>
-      <c r="H73" s="149" t="s">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="74" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E74" s="148" t="s">
-        <v>2503</v>
-      </c>
-      <c r="F74" s="148" t="s">
-        <v>2490</v>
-      </c>
-      <c r="G74" s="148" t="s">
-        <v>165</v>
-      </c>
-      <c r="H74" s="149" t="s">
-        <v>2513</v>
-      </c>
-    </row>
-    <row r="75" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E75" s="148" t="s">
-        <v>2503</v>
-      </c>
-      <c r="F75" s="148" t="s">
-        <v>2490</v>
-      </c>
-      <c r="G75" s="148" t="s">
-        <v>161</v>
-      </c>
-      <c r="H75" s="149" t="s">
-        <v>2513</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/FIFAScheduleResults.xlsx
+++ b/FIFAScheduleResults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World Cup Betting/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="352" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C913E90B-F68C-4667-A308-0B93A3E91F24}"/>
+  <xr:revisionPtr revIDLastSave="358" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA4E0B95-30AC-46B0-A81D-2FE0CA6D3B35}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA World Cup 2026" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8168" uniqueCount="3813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8170" uniqueCount="3814">
   <si>
     <t>Match</t>
   </si>
@@ -11565,6 +11565,9 @@
   </si>
   <si>
     <t>FRA10, FRA12, SEN20, FRA10</t>
+  </si>
+  <si>
+    <t>AUT18, JOR9, OG, AUT7</t>
   </si>
 </sst>
 </file>
@@ -14644,15 +14647,19 @@
       <c r="F57" s="135" t="s">
         <v>2379</v>
       </c>
-      <c r="G57" s="204"/>
-      <c r="H57" s="21"/>
-      <c r="I57" t="e" cm="1">
+      <c r="G57" s="204" t="s">
+        <v>3809</v>
+      </c>
+      <c r="H57" s="21" t="s">
+        <v>3813</v>
+      </c>
+      <c r="I57" t="str" cm="1">
         <f t="array" ref="I57">_xlfn.IFS(LEFT(G57,1)-RIGHT(G57,1) &gt; 0, "W1",LEFT(G57,1)-RIGHT(G57,1) = 0, "D",LEFT(G57,1)-RIGHT(G57,1) &lt; 0, "W2", ISBLANK(G57), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J57" s="144" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J57" s="144">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">

--- a/FIFAScheduleResults.xlsx
+++ b/FIFAScheduleResults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World Cup Betting/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="370" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{821E26A0-61F5-4460-99BC-A9ACB36DF1AD}"/>
+  <xr:revisionPtr revIDLastSave="388" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85ACAC5D-7F57-4CA4-834F-E2518EEEFC10}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA World Cup 2026" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8170" uniqueCount="3814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8178" uniqueCount="3820">
   <si>
     <t>Match</t>
   </si>
@@ -11568,6 +11568,24 @@
   </si>
   <si>
     <t>AUT18, JOR9, OG, AUT7</t>
+  </si>
+  <si>
+    <t>PRT15, COD20</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>GHA3</t>
+  </si>
+  <si>
+    <t>ENG9, HRV16, ENG9, HRV26, ENG10, ENG11</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>COL2, UZB22, COL7, COL21</t>
   </si>
 </sst>
 </file>
@@ -14630,15 +14648,19 @@
       <c r="F62" s="136" t="s">
         <v>2384</v>
       </c>
-      <c r="G62" s="156"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="23" t="e" cm="1">
+      <c r="G62" s="156" t="s">
+        <v>2461</v>
+      </c>
+      <c r="H62" s="22" t="s">
+        <v>3814</v>
+      </c>
+      <c r="I62" s="23" t="str" cm="1">
         <f t="array" ref="I62">_xlfn.IFS(LEFT(G62,1)-RIGHT(G62,1) &gt; 0, "W1",LEFT(G62,1)-RIGHT(G62,1) = 0, "D",LEFT(G62,1)-RIGHT(G62,1) &lt; 0, "W2", ISBLANK(G62), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J62" s="23" t="e">
+        <v>D</v>
+      </c>
+      <c r="J62" s="23">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -14660,15 +14682,19 @@
       <c r="F63" s="136" t="s">
         <v>2385</v>
       </c>
-      <c r="G63" s="156"/>
-      <c r="H63" s="22"/>
-      <c r="I63" s="23" t="e" cm="1">
+      <c r="G63" s="156" t="s">
+        <v>3818</v>
+      </c>
+      <c r="H63" s="22" t="s">
+        <v>3819</v>
+      </c>
+      <c r="I63" s="23" t="str" cm="1">
         <f t="array" ref="I63">_xlfn.IFS(LEFT(G63,1)-RIGHT(G63,1) &gt; 0, "W1",LEFT(G63,1)-RIGHT(G63,1) = 0, "D",LEFT(G63,1)-RIGHT(G63,1) &lt; 0, "W2", ISBLANK(G63), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J63" s="23" t="e">
+        <v>W2</v>
+      </c>
+      <c r="J63" s="23">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -14791,7 +14817,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="24" t="s">
         <v>183</v>
       </c>
@@ -14810,15 +14836,19 @@
       <c r="F68" s="137" t="s">
         <v>2390</v>
       </c>
-      <c r="G68" s="157"/>
-      <c r="H68" s="24"/>
-      <c r="I68" s="25" t="e" cm="1">
+      <c r="G68" s="157" t="s">
+        <v>3815</v>
+      </c>
+      <c r="H68" s="24" t="s">
+        <v>3817</v>
+      </c>
+      <c r="I68" s="25" t="str" cm="1">
         <f t="array" ref="I68">_xlfn.IFS(LEFT(G68,1)-RIGHT(G68,1) &gt; 0, "W1",LEFT(G68,1)-RIGHT(G68,1) = 0, "D",LEFT(G68,1)-RIGHT(G68,1) &lt; 0, "W2", ISBLANK(G68), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J68" s="25" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J68" s="25">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -14840,15 +14870,19 @@
       <c r="F69" s="137" t="s">
         <v>2391</v>
       </c>
-      <c r="G69" s="157"/>
-      <c r="H69" s="24"/>
-      <c r="I69" s="25" t="e" cm="1">
+      <c r="G69" s="157" t="s">
+        <v>2478</v>
+      </c>
+      <c r="H69" s="24" t="s">
+        <v>3816</v>
+      </c>
+      <c r="I69" s="25" t="str" cm="1">
         <f t="array" ref="I69">_xlfn.IFS(LEFT(G69,1)-RIGHT(G69,1) &gt; 0, "W1",LEFT(G69,1)-RIGHT(G69,1) = 0, "D",LEFT(G69,1)-RIGHT(G69,1) &lt; 0, "W2", ISBLANK(G69), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J69" s="25" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J69" s="25">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">

--- a/FIFAScheduleResults.xlsx
+++ b/FIFAScheduleResults.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World Cup Betting/World-Cup-betting/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="388" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85ACAC5D-7F57-4CA4-834F-E2518EEEFC10}"/>
+  <xr:revisionPtr revIDLastSave="389" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D4D8271-5994-481D-8266-3890DD250E76}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA World Cup 2026" sheetId="1" r:id="rId1"/>
@@ -12714,7 +12714,7 @@
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="15.81640625" customWidth="1"/>
     <col min="7" max="7" width="30" style="143" customWidth="1"/>
-    <col min="8" max="8" width="30" style="163" customWidth="1"/>
+    <col min="8" max="8" width="38.08984375" style="163" customWidth="1"/>
     <col min="9" max="9" width="20.7265625" customWidth="1"/>
     <col min="10" max="10" width="19.7265625" customWidth="1"/>
   </cols>

--- a/FIFAScheduleResults.xlsx
+++ b/FIFAScheduleResults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="389" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D4D8271-5994-481D-8266-3890DD250E76}"/>
+  <xr:revisionPtr revIDLastSave="392" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2879D2FD-66D0-4F39-A16D-0F5ED820AE41}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA World Cup 2026" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8178" uniqueCount="3820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8180" uniqueCount="3821">
   <si>
     <t>Match</t>
   </si>
@@ -11586,6 +11586,9 @@
   </si>
   <si>
     <t>COL2, UZB22, COL7, COL21</t>
+  </si>
+  <si>
+    <t>CZE18, ZAF4</t>
   </si>
 </sst>
 </file>
@@ -12838,15 +12841,19 @@
       <c r="F4" s="126" t="s">
         <v>2333</v>
       </c>
-      <c r="G4" s="146"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="3" t="e" cm="1">
+      <c r="G4" s="146" t="s">
+        <v>2461</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>3820</v>
+      </c>
+      <c r="I4" s="3" t="str" cm="1">
         <f t="array" ref="I4">_xlfn.IFS(LEFT(G4,1)-RIGHT(G4,1)&gt;0,"W1",LEFT(G4,1)-RIGHT(G4,1)=0,"D",LEFT(G4,1)-RIGHT(G4,1)&lt;0,"W2",ISBLANK(G4),"")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J4" s="3" t="e">
+        <v>D</v>
+      </c>
+      <c r="J4" s="3">
         <f t="shared" ref="J4:J24" si="0">LEFT(G4,1)-RIGHT(G4,1)</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">

--- a/FIFAScheduleResults.xlsx
+++ b/FIFAScheduleResults.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="392" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2879D2FD-66D0-4F39-A16D-0F5ED820AE41}"/>
+  <xr:revisionPtr revIDLastSave="407" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D70964F-0FCF-43E3-8960-589EE7ED5F0C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8180" uniqueCount="3821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8186" uniqueCount="3825">
   <si>
     <t>Match</t>
   </si>
@@ -11589,6 +11589,18 @@
   </si>
   <si>
     <t>CZE18, ZAF4</t>
+  </si>
+  <si>
+    <t>CAN9, CAN10, CAN10, CAN25, OG, CAN10</t>
+  </si>
+  <si>
+    <t>6-0</t>
+  </si>
+  <si>
+    <t>CHE9, CHE17, CHE9, BIH26, CHE10</t>
+  </si>
+  <si>
+    <t>MEX7</t>
   </si>
 </sst>
 </file>
@@ -12718,8 +12730,8 @@
     <col min="6" max="6" width="15.81640625" customWidth="1"/>
     <col min="7" max="7" width="30" style="143" customWidth="1"/>
     <col min="8" max="8" width="38.08984375" style="163" customWidth="1"/>
-    <col min="9" max="9" width="20.7265625" customWidth="1"/>
-    <col min="10" max="10" width="19.7265625" customWidth="1"/>
+    <col min="9" max="9" width="12.26953125" style="163" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.35">
@@ -12779,7 +12791,7 @@
       <c r="H2" s="2" t="s">
         <v>2456</v>
       </c>
-      <c r="I2" s="3" t="str" cm="1">
+      <c r="I2" s="2" t="str" cm="1">
         <f t="array" ref="I2">_xlfn.IFS(LEFT(G2,1)-RIGHT(G2,1) &gt; 0, "W1",LEFT(G2,1)-RIGHT(G2,1) = 0, "D",LEFT(G2,1)-RIGHT(G2,1) &lt; 0, "W2", ISBLANK(G2), "")</f>
         <v>W1</v>
       </c>
@@ -12813,7 +12825,7 @@
       <c r="H3" s="2" t="s">
         <v>2457</v>
       </c>
-      <c r="I3" s="3" t="str" cm="1">
+      <c r="I3" s="2" t="str" cm="1">
         <f t="array" ref="I3">_xlfn.IFS(LEFT(G3,1)-RIGHT(G3,1) &gt; 0, "W1",LEFT(G3,1)-RIGHT(G3,1) = 0, "D",LEFT(G3,1)-RIGHT(G3,1) &lt; 0, "W2", ISBLANK(G3), "")</f>
         <v>W1</v>
       </c>
@@ -12847,8 +12859,8 @@
       <c r="H4" s="2" t="s">
         <v>3820</v>
       </c>
-      <c r="I4" s="3" t="str" cm="1">
-        <f t="array" ref="I4">_xlfn.IFS(LEFT(G4,1)-RIGHT(G4,1)&gt;0,"W1",LEFT(G4,1)-RIGHT(G4,1)=0,"D",LEFT(G4,1)-RIGHT(G4,1)&lt;0,"W2",ISBLANK(G4),"")</f>
+      <c r="I4" s="2" t="str" cm="1">
+        <f t="array" ref="I4">_xlfn.IFS(LEFT(G4,1)-RIGHT(G4,1) &gt; 0, "W1",LEFT(G4,1)-RIGHT(G4,1) = 0, "D",LEFT(G4,1)-RIGHT(G4,1) &lt; 0, "W2", ISBLANK(G4), "")</f>
         <v>D</v>
       </c>
       <c r="J4" s="3">
@@ -12875,15 +12887,19 @@
       <c r="F5" s="126" t="s">
         <v>2334</v>
       </c>
-      <c r="G5" s="146"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="3" t="e" cm="1">
+      <c r="G5" s="146" t="s">
+        <v>2478</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>3824</v>
+      </c>
+      <c r="I5" s="2" t="str" cm="1">
         <f t="array" ref="I5">_xlfn.IFS(LEFT(G5,1)-RIGHT(G5,1) &gt; 0, "W1",LEFT(G5,1)-RIGHT(G5,1) = 0, "D",LEFT(G5,1)-RIGHT(G5,1) &lt; 0, "W2", ISBLANK(G5), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J5" s="3" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J5" s="3">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -12907,7 +12923,7 @@
       </c>
       <c r="G6" s="146"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="3" t="e" cm="1">
+      <c r="I6" s="2" t="e" cm="1">
         <f t="array" ref="I6">_xlfn.IFS(LEFT(G6,1)-RIGHT(G6,1) &gt; 0, "W1",LEFT(G6,1)-RIGHT(G6,1) = 0, "D",LEFT(G6,1)-RIGHT(G6,1) &lt; 0, "W2", ISBLANK(G6), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -12937,7 +12953,7 @@
       </c>
       <c r="G7" s="146"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="3" t="e" cm="1">
+      <c r="I7" s="2" t="e" cm="1">
         <f t="array" ref="I7">_xlfn.IFS(LEFT(G7,1)-RIGHT(G7,1) &gt; 0, "W1",LEFT(G7,1)-RIGHT(G7,1) = 0, "D",LEFT(G7,1)-RIGHT(G7,1) &lt; 0, "W2", ISBLANK(G7), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -12971,7 +12987,7 @@
       <c r="H8" s="4" t="s">
         <v>2463</v>
       </c>
-      <c r="I8" s="5" t="str" cm="1">
+      <c r="I8" s="4" t="str" cm="1">
         <f t="array" ref="I8">_xlfn.IFS(LEFT(G8,1)-RIGHT(G8,1) &gt; 0, "W1",LEFT(G8,1)-RIGHT(G8,1) = 0, "D",LEFT(G8,1)-RIGHT(G8,1) &lt; 0, "W2", ISBLANK(G8), "")</f>
         <v>D</v>
       </c>
@@ -13005,7 +13021,7 @@
       <c r="H9" s="4" t="s">
         <v>2473</v>
       </c>
-      <c r="I9" s="5" t="str" cm="1">
+      <c r="I9" s="4" t="str" cm="1">
         <f t="array" ref="I9">_xlfn.IFS(LEFT(G9,1)-RIGHT(G9,1) &gt; 0, "W1",LEFT(G9,1)-RIGHT(G9,1) = 0, "D",LEFT(G9,1)-RIGHT(G9,1) &lt; 0, "W2", ISBLANK(G9), "")</f>
         <v>D</v>
       </c>
@@ -13033,15 +13049,19 @@
       <c r="F10" s="127" t="s">
         <v>2337</v>
       </c>
-      <c r="G10" s="147"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="5" t="e" cm="1">
+      <c r="G10" s="147" t="s">
+        <v>2462</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>3823</v>
+      </c>
+      <c r="I10" s="4" t="str" cm="1">
         <f t="array" ref="I10">_xlfn.IFS(LEFT(G10,1)-RIGHT(G10,1) &gt; 0, "W1",LEFT(G10,1)-RIGHT(G10,1) = 0, "D",LEFT(G10,1)-RIGHT(G10,1) &lt; 0, "W2", ISBLANK(G10), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J10" s="5" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J10" s="5">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -13063,15 +13083,19 @@
       <c r="F11" s="127" t="s">
         <v>2338</v>
       </c>
-      <c r="G11" s="147"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="5" t="e" cm="1">
+      <c r="G11" s="147" t="s">
+        <v>3822</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>3821</v>
+      </c>
+      <c r="I11" s="4" t="str" cm="1">
         <f t="array" ref="I11">_xlfn.IFS(LEFT(G11,1)-RIGHT(G11,1) &gt; 0, "W1",LEFT(G11,1)-RIGHT(G11,1) = 0, "D",LEFT(G11,1)-RIGHT(G11,1) &lt; 0, "W2", ISBLANK(G11), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J11" s="5" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J11" s="5">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -13095,7 +13119,7 @@
       </c>
       <c r="G12" s="147"/>
       <c r="H12" s="4"/>
-      <c r="I12" s="5" t="e" cm="1">
+      <c r="I12" s="4" t="e" cm="1">
         <f t="array" ref="I12">_xlfn.IFS(LEFT(G12,1)-RIGHT(G12,1) &gt; 0, "W1",LEFT(G12,1)-RIGHT(G12,1) = 0, "D",LEFT(G12,1)-RIGHT(G12,1) &lt; 0, "W2", ISBLANK(G12), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -13125,7 +13149,7 @@
       </c>
       <c r="G13" s="147"/>
       <c r="H13" s="4"/>
-      <c r="I13" s="5" t="e" cm="1">
+      <c r="I13" s="4" t="e" cm="1">
         <f t="array" ref="I13">_xlfn.IFS(LEFT(G13,1)-RIGHT(G13,1) &gt; 0, "W1",LEFT(G13,1)-RIGHT(G13,1) = 0, "D",LEFT(G13,1)-RIGHT(G13,1) &lt; 0, "W2", ISBLANK(G13), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -13159,7 +13183,7 @@
       <c r="H14" s="6" t="s">
         <v>2474</v>
       </c>
-      <c r="I14" s="7" t="str" cm="1">
+      <c r="I14" s="6" t="str" cm="1">
         <f t="array" ref="I14">_xlfn.IFS(LEFT(G14,1)-RIGHT(G14,1) &gt; 0, "W1",LEFT(G14,1)-RIGHT(G14,1) = 0, "D",LEFT(G14,1)-RIGHT(G14,1) &lt; 0, "W2", ISBLANK(G14), "")</f>
         <v>D</v>
       </c>
@@ -13193,7 +13217,7 @@
       <c r="H15" s="6" t="s">
         <v>2472</v>
       </c>
-      <c r="I15" s="7" t="str" cm="1">
+      <c r="I15" s="6" t="str" cm="1">
         <f t="array" ref="I15">_xlfn.IFS(LEFT(G15,1)-RIGHT(G15,1) &gt; 0, "W1",LEFT(G15,1)-RIGHT(G15,1) = 0, "D",LEFT(G15,1)-RIGHT(G15,1) &lt; 0, "W2", ISBLANK(G15), "")</f>
         <v>W2</v>
       </c>
@@ -13223,7 +13247,7 @@
       </c>
       <c r="G16" s="148"/>
       <c r="H16" s="6"/>
-      <c r="I16" s="7" t="e" cm="1">
+      <c r="I16" s="6" t="e" cm="1">
         <f t="array" ref="I16">_xlfn.IFS(LEFT(G16,1)-RIGHT(G16,1) &gt; 0, "W1",LEFT(G16,1)-RIGHT(G16,1) = 0, "D",LEFT(G16,1)-RIGHT(G16,1) &lt; 0, "W2", ISBLANK(G16), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -13253,7 +13277,7 @@
       </c>
       <c r="G17" s="148"/>
       <c r="H17" s="6"/>
-      <c r="I17" s="7" t="e" cm="1">
+      <c r="I17" s="6" t="e" cm="1">
         <f t="array" ref="I17">_xlfn.IFS(LEFT(G17,1)-RIGHT(G17,1) &gt; 0, "W1",LEFT(G17,1)-RIGHT(G17,1) = 0, "D",LEFT(G17,1)-RIGHT(G17,1) &lt; 0, "W2", ISBLANK(G17), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -13283,7 +13307,7 @@
       </c>
       <c r="G18" s="148"/>
       <c r="H18" s="6"/>
-      <c r="I18" s="7" t="e" cm="1">
+      <c r="I18" s="6" t="e" cm="1">
         <f t="array" ref="I18">_xlfn.IFS(LEFT(G18,1)-RIGHT(G18,1) &gt; 0, "W1",LEFT(G18,1)-RIGHT(G18,1) = 0, "D",LEFT(G18,1)-RIGHT(G18,1) &lt; 0, "W2", ISBLANK(G18), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -13313,7 +13337,7 @@
       </c>
       <c r="G19" s="148"/>
       <c r="H19" s="6"/>
-      <c r="I19" s="7" t="e" cm="1">
+      <c r="I19" s="6" t="e" cm="1">
         <f t="array" ref="I19">_xlfn.IFS(LEFT(G19,1)-RIGHT(G19,1) &gt; 0, "W1",LEFT(G19,1)-RIGHT(G19,1) = 0, "D",LEFT(G19,1)-RIGHT(G19,1) &lt; 0, "W2", ISBLANK(G19), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -13322,7 +13346,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="25" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>55</v>
       </c>
@@ -13347,7 +13371,7 @@
       <c r="H20" s="8" t="s">
         <v>2464</v>
       </c>
-      <c r="I20" s="9" t="str" cm="1">
+      <c r="I20" s="8" t="str" cm="1">
         <f t="array" ref="I20">_xlfn.IFS(LEFT(G20,1)-RIGHT(G20,1) &gt; 0, "W1",LEFT(G20,1)-RIGHT(G20,1) = 0, "D",LEFT(G20,1)-RIGHT(G20,1) &lt; 0, "W2", ISBLANK(G20), "")</f>
         <v>W1</v>
       </c>
@@ -13381,7 +13405,7 @@
       <c r="H21" s="8" t="s">
         <v>2475</v>
       </c>
-      <c r="I21" s="9" t="str" cm="1">
+      <c r="I21" s="8" t="str" cm="1">
         <f t="array" ref="I21">_xlfn.IFS(LEFT(G21,1)-RIGHT(G21,1) &gt; 0, "W1",LEFT(G21,1)-RIGHT(G21,1) = 0, "D",LEFT(G21,1)-RIGHT(G21,1) &lt; 0, "W2", ISBLANK(G21), "")</f>
         <v>W1</v>
       </c>
@@ -13411,7 +13435,7 @@
       </c>
       <c r="G22" s="149"/>
       <c r="H22" s="8"/>
-      <c r="I22" s="9" t="e" cm="1">
+      <c r="I22" s="8" t="e" cm="1">
         <f t="array" ref="I22">_xlfn.IFS(LEFT(G22,1)-RIGHT(G22,1) &gt; 0, "W1",LEFT(G22,1)-RIGHT(G22,1) = 0, "D",LEFT(G22,1)-RIGHT(G22,1) &lt; 0, "W2", ISBLANK(G22), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -13441,7 +13465,7 @@
       </c>
       <c r="G23" s="149"/>
       <c r="H23" s="8"/>
-      <c r="I23" s="9" t="e" cm="1">
+      <c r="I23" s="8" t="e" cm="1">
         <f t="array" ref="I23">_xlfn.IFS(LEFT(G23,1)-RIGHT(G23,1) &gt; 0, "W1",LEFT(G23,1)-RIGHT(G23,1) = 0, "D",LEFT(G23,1)-RIGHT(G23,1) &lt; 0, "W2", ISBLANK(G23), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -13471,7 +13495,7 @@
       </c>
       <c r="G24" s="149"/>
       <c r="H24" s="8"/>
-      <c r="I24" s="9" t="e" cm="1">
+      <c r="I24" s="8" t="e" cm="1">
         <f t="array" ref="I24">_xlfn.IFS(LEFT(G24,1)-RIGHT(G24,1) &gt; 0, "W1",LEFT(G24,1)-RIGHT(G24,1) = 0, "D",LEFT(G24,1)-RIGHT(G24,1) &lt; 0, "W2", ISBLANK(G24), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -13501,7 +13525,7 @@
       </c>
       <c r="G25" s="149"/>
       <c r="H25" s="8"/>
-      <c r="I25" s="9" t="e" cm="1">
+      <c r="I25" s="8" t="e" cm="1">
         <f t="array" ref="I25">_xlfn.IFS(LEFT(G25,1)-RIGHT(G25,1) &gt; 0, "W1",LEFT(G25,1)-RIGHT(G25,1) = 0, "D",LEFT(G25,1)-RIGHT(G25,1) &lt; 0, "W2", ISBLANK(G25), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -13535,7 +13559,7 @@
       <c r="H26" s="10" t="s">
         <v>2476</v>
       </c>
-      <c r="I26" s="11" t="str" cm="1">
+      <c r="I26" s="10" t="str" cm="1">
         <f t="array" ref="I26">_xlfn.IFS(LEFT(G26,1)-RIGHT(G26,1) &gt; 0, "W1",LEFT(G26,1)-RIGHT(G26,1) = 0, "D",LEFT(G26,1)-RIGHT(G26,1) &lt; 0, "W2", ISBLANK(G26), "")</f>
         <v>W1</v>
       </c>
@@ -13569,7 +13593,7 @@
       <c r="H27" s="10" t="s">
         <v>2479</v>
       </c>
-      <c r="I27" s="11" t="str" cm="1">
+      <c r="I27" s="10" t="str" cm="1">
         <f t="array" ref="I27">_xlfn.IFS(LEFT(G27,1)-RIGHT(G27,1) &gt; 0, "W1",LEFT(G27,1)-RIGHT(G27,1) = 0, "D",LEFT(G27,1)-RIGHT(G27,1) &lt; 0, "W2", ISBLANK(G27), "")</f>
         <v>W1</v>
       </c>
@@ -13599,7 +13623,7 @@
       </c>
       <c r="G28" s="150"/>
       <c r="H28" s="10"/>
-      <c r="I28" s="11" t="e" cm="1">
+      <c r="I28" s="10" t="e" cm="1">
         <f t="array" ref="I28">_xlfn.IFS(LEFT(G28,1)-RIGHT(G28,1) &gt; 0, "W1",LEFT(G28,1)-RIGHT(G28,1) = 0, "D",LEFT(G28,1)-RIGHT(G28,1) &lt; 0, "W2", ISBLANK(G28), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -13629,7 +13653,7 @@
       </c>
       <c r="G29" s="150"/>
       <c r="H29" s="10"/>
-      <c r="I29" s="11" t="e" cm="1">
+      <c r="I29" s="10" t="e" cm="1">
         <f t="array" ref="I29">_xlfn.IFS(LEFT(G29,1)-RIGHT(G29,1) &gt; 0, "W1",LEFT(G29,1)-RIGHT(G29,1) = 0, "D",LEFT(G29,1)-RIGHT(G29,1) &lt; 0, "W2", ISBLANK(G29), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -13659,7 +13683,7 @@
       </c>
       <c r="G30" s="150"/>
       <c r="H30" s="10"/>
-      <c r="I30" s="11" t="e" cm="1">
+      <c r="I30" s="10" t="e" cm="1">
         <f t="array" ref="I30">_xlfn.IFS(LEFT(G30,1)-RIGHT(G30,1) &gt; 0, "W1",LEFT(G30,1)-RIGHT(G30,1) = 0, "D",LEFT(G30,1)-RIGHT(G30,1) &lt; 0, "W2", ISBLANK(G30), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -13689,7 +13713,7 @@
       </c>
       <c r="G31" s="150"/>
       <c r="H31" s="10"/>
-      <c r="I31" s="11" t="e" cm="1">
+      <c r="I31" s="10" t="e" cm="1">
         <f t="array" ref="I31">_xlfn.IFS(LEFT(G31,1)-RIGHT(G31,1) &gt; 0, "W1",LEFT(G31,1)-RIGHT(G31,1) = 0, "D",LEFT(G31,1)-RIGHT(G31,1) &lt; 0, "W2", ISBLANK(G31), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -13723,7 +13747,7 @@
       <c r="H32" s="12" t="s">
         <v>2483</v>
       </c>
-      <c r="I32" s="13" t="str" cm="1">
+      <c r="I32" s="12" t="str" cm="1">
         <f t="array" ref="I32">_xlfn.IFS(LEFT(G32,1)-RIGHT(G32,1) &gt; 0, "W1",LEFT(G32,1)-RIGHT(G32,1) = 0, "D",LEFT(G32,1)-RIGHT(G32,1) &lt; 0, "W2", ISBLANK(G32), "")</f>
         <v>D</v>
       </c>
@@ -13757,7 +13781,7 @@
       <c r="H33" s="12" t="s">
         <v>2481</v>
       </c>
-      <c r="I33" s="13" t="str" cm="1">
+      <c r="I33" s="12" t="str" cm="1">
         <f t="array" ref="I33">_xlfn.IFS(LEFT(G33,1)-RIGHT(G33,1) &gt; 0, "W1",LEFT(G33,1)-RIGHT(G33,1) = 0, "D",LEFT(G33,1)-RIGHT(G33,1) &lt; 0, "W2", ISBLANK(G33), "")</f>
         <v>W1</v>
       </c>
@@ -13787,7 +13811,7 @@
       </c>
       <c r="G34" s="151"/>
       <c r="H34" s="12"/>
-      <c r="I34" s="13" t="e" cm="1">
+      <c r="I34" s="12" t="e" cm="1">
         <f t="array" ref="I34">_xlfn.IFS(LEFT(G34,1)-RIGHT(G34,1) &gt; 0, "W1",LEFT(G34,1)-RIGHT(G34,1) = 0, "D",LEFT(G34,1)-RIGHT(G34,1) &lt; 0, "W2", ISBLANK(G34), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -13817,7 +13841,7 @@
       </c>
       <c r="G35" s="151"/>
       <c r="H35" s="12"/>
-      <c r="I35" s="13" t="e" cm="1">
+      <c r="I35" s="12" t="e" cm="1">
         <f t="array" ref="I35">_xlfn.IFS(LEFT(G35,1)-RIGHT(G35,1) &gt; 0, "W1",LEFT(G35,1)-RIGHT(G35,1) = 0, "D",LEFT(G35,1)-RIGHT(G35,1) &lt; 0, "W2", ISBLANK(G35), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -13847,7 +13871,7 @@
       </c>
       <c r="G36" s="151"/>
       <c r="H36" s="12"/>
-      <c r="I36" s="13" t="e" cm="1">
+      <c r="I36" s="12" t="e" cm="1">
         <f t="array" ref="I36">_xlfn.IFS(LEFT(G36,1)-RIGHT(G36,1) &gt; 0, "W1",LEFT(G36,1)-RIGHT(G36,1) = 0, "D",LEFT(G36,1)-RIGHT(G36,1) &lt; 0, "W2", ISBLANK(G36), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -13877,7 +13901,7 @@
       </c>
       <c r="G37" s="151"/>
       <c r="H37" s="12"/>
-      <c r="I37" s="13" t="e" cm="1">
+      <c r="I37" s="12" t="e" cm="1">
         <f t="array" ref="I37">_xlfn.IFS(LEFT(G37,1)-RIGHT(G37,1) &gt; 0, "W1",LEFT(G37,1)-RIGHT(G37,1) = 0, "D",LEFT(G37,1)-RIGHT(G37,1) &lt; 0, "W2", ISBLANK(G37), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -13911,7 +13935,7 @@
       <c r="H38" s="14" t="s">
         <v>2486</v>
       </c>
-      <c r="I38" s="15" t="str" cm="1">
+      <c r="I38" s="14" t="str" cm="1">
         <f t="array" ref="I38">_xlfn.IFS(LEFT(G38,1)-RIGHT(G38,1) &gt; 0, "W1",LEFT(G38,1)-RIGHT(G38,1) = 0, "D",LEFT(G38,1)-RIGHT(G38,1) &lt; 0, "W2", ISBLANK(G38), "")</f>
         <v>D</v>
       </c>
@@ -13945,7 +13969,7 @@
       <c r="H39" s="14" t="s">
         <v>2487</v>
       </c>
-      <c r="I39" s="15" t="str" cm="1">
+      <c r="I39" s="14" t="str" cm="1">
         <f t="array" ref="I39">_xlfn.IFS(LEFT(G39,1)-RIGHT(G39,1) &gt; 0, "W1",LEFT(G39,1)-RIGHT(G39,1) = 0, "D",LEFT(G39,1)-RIGHT(G39,1) &lt; 0, "W2", ISBLANK(G39), "")</f>
         <v>D</v>
       </c>
@@ -13975,7 +13999,7 @@
       </c>
       <c r="G40" s="152"/>
       <c r="H40" s="14"/>
-      <c r="I40" s="15" t="e" cm="1">
+      <c r="I40" s="14" t="e" cm="1">
         <f t="array" ref="I40">_xlfn.IFS(LEFT(G40,1)-RIGHT(G40,1) &gt; 0, "W1",LEFT(G40,1)-RIGHT(G40,1) = 0, "D",LEFT(G40,1)-RIGHT(G40,1) &lt; 0, "W2", ISBLANK(G40), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14005,7 +14029,7 @@
       </c>
       <c r="G41" s="152"/>
       <c r="H41" s="14"/>
-      <c r="I41" s="15" t="e" cm="1">
+      <c r="I41" s="14" t="e" cm="1">
         <f t="array" ref="I41">_xlfn.IFS(LEFT(G41,1)-RIGHT(G41,1) &gt; 0, "W1",LEFT(G41,1)-RIGHT(G41,1) = 0, "D",LEFT(G41,1)-RIGHT(G41,1) &lt; 0, "W2", ISBLANK(G41), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14035,7 +14059,7 @@
       </c>
       <c r="G42" s="152"/>
       <c r="H42" s="14"/>
-      <c r="I42" s="15" t="e" cm="1">
+      <c r="I42" s="14" t="e" cm="1">
         <f t="array" ref="I42">_xlfn.IFS(LEFT(G42,1)-RIGHT(G42,1) &gt; 0, "W1",LEFT(G42,1)-RIGHT(G42,1) = 0, "D",LEFT(G42,1)-RIGHT(G42,1) &lt; 0, "W2", ISBLANK(G42), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14065,7 +14089,7 @@
       </c>
       <c r="G43" s="152"/>
       <c r="H43" s="14"/>
-      <c r="I43" s="15" t="e" cm="1">
+      <c r="I43" s="14" t="e" cm="1">
         <f t="array" ref="I43">_xlfn.IFS(LEFT(G43,1)-RIGHT(G43,1) &gt; 0, "W1",LEFT(G43,1)-RIGHT(G43,1) = 0, "D",LEFT(G43,1)-RIGHT(G43,1) &lt; 0, "W2", ISBLANK(G43), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14097,7 +14121,7 @@
         <v>2484</v>
       </c>
       <c r="H44" s="16"/>
-      <c r="I44" s="17" t="str" cm="1">
+      <c r="I44" s="16" t="str" cm="1">
         <f t="array" ref="I44">_xlfn.IFS(LEFT(G44,1)-RIGHT(G44,1) &gt; 0, "W1",LEFT(G44,1)-RIGHT(G44,1) = 0, "D",LEFT(G44,1)-RIGHT(G44,1) &lt; 0, "W2", ISBLANK(G44), "")</f>
         <v>D</v>
       </c>
@@ -14131,7 +14155,7 @@
       <c r="H45" s="16" t="s">
         <v>2485</v>
       </c>
-      <c r="I45" s="17" t="str" cm="1">
+      <c r="I45" s="16" t="str" cm="1">
         <f t="array" ref="I45">_xlfn.IFS(LEFT(G45,1)-RIGHT(G45,1) &gt; 0, "W1",LEFT(G45,1)-RIGHT(G45,1) = 0, "D",LEFT(G45,1)-RIGHT(G45,1) &lt; 0, "W2", ISBLANK(G45), "")</f>
         <v>D</v>
       </c>
@@ -14161,7 +14185,7 @@
       </c>
       <c r="G46" s="153"/>
       <c r="H46" s="16"/>
-      <c r="I46" s="17" t="e" cm="1">
+      <c r="I46" s="16" t="e" cm="1">
         <f t="array" ref="I46">_xlfn.IFS(LEFT(G46,1)-RIGHT(G46,1) &gt; 0, "W1",LEFT(G46,1)-RIGHT(G46,1) = 0, "D",LEFT(G46,1)-RIGHT(G46,1) &lt; 0, "W2", ISBLANK(G46), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14191,7 +14215,7 @@
       </c>
       <c r="G47" s="153"/>
       <c r="H47" s="16"/>
-      <c r="I47" s="17" t="e" cm="1">
+      <c r="I47" s="16" t="e" cm="1">
         <f t="array" ref="I47">_xlfn.IFS(LEFT(G47,1)-RIGHT(G47,1) &gt; 0, "W1",LEFT(G47,1)-RIGHT(G47,1) = 0, "D",LEFT(G47,1)-RIGHT(G47,1) &lt; 0, "W2", ISBLANK(G47), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14221,7 +14245,7 @@
       </c>
       <c r="G48" s="153"/>
       <c r="H48" s="16"/>
-      <c r="I48" s="17" t="e" cm="1">
+      <c r="I48" s="16" t="e" cm="1">
         <f t="array" ref="I48">_xlfn.IFS(LEFT(G48,1)-RIGHT(G48,1) &gt; 0, "W1",LEFT(G48,1)-RIGHT(G48,1) = 0, "D",LEFT(G48,1)-RIGHT(G48,1) &lt; 0, "W2", ISBLANK(G48), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14251,7 +14275,7 @@
       </c>
       <c r="G49" s="153"/>
       <c r="H49" s="16"/>
-      <c r="I49" s="17" t="e" cm="1">
+      <c r="I49" s="16" t="e" cm="1">
         <f t="array" ref="I49">_xlfn.IFS(LEFT(G49,1)-RIGHT(G49,1) &gt; 0, "W1",LEFT(G49,1)-RIGHT(G49,1) = 0, "D",LEFT(G49,1)-RIGHT(G49,1) &lt; 0, "W2", ISBLANK(G49), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14285,7 +14309,7 @@
       <c r="H50" s="18" t="s">
         <v>3812</v>
       </c>
-      <c r="I50" s="19" t="str" cm="1">
+      <c r="I50" s="18" t="str" cm="1">
         <f t="array" ref="I50">_xlfn.IFS(LEFT(G50,1)-RIGHT(G50,1) &gt; 0, "W1",LEFT(G50,1)-RIGHT(G50,1) = 0, "D",LEFT(G50,1)-RIGHT(G50,1) &lt; 0, "W2", ISBLANK(G50), "")</f>
         <v>W1</v>
       </c>
@@ -14319,7 +14343,7 @@
       <c r="H51" s="18" t="s">
         <v>3811</v>
       </c>
-      <c r="I51" s="19" t="str" cm="1">
+      <c r="I51" s="18" t="str" cm="1">
         <f t="array" ref="I51">_xlfn.IFS(LEFT(G51,1)-RIGHT(G51,1) &gt; 0, "W1",LEFT(G51,1)-RIGHT(G51,1) = 0, "D",LEFT(G51,1)-RIGHT(G51,1) &lt; 0, "W2", ISBLANK(G51), "")</f>
         <v>W2</v>
       </c>
@@ -14349,7 +14373,7 @@
       </c>
       <c r="G52" s="154"/>
       <c r="H52" s="18"/>
-      <c r="I52" s="19" t="e" cm="1">
+      <c r="I52" s="18" t="e" cm="1">
         <f t="array" ref="I52">_xlfn.IFS(LEFT(G52,1)-RIGHT(G52,1) &gt; 0, "W1",LEFT(G52,1)-RIGHT(G52,1) = 0, "D",LEFT(G52,1)-RIGHT(G52,1) &lt; 0, "W2", ISBLANK(G52), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14379,7 +14403,7 @@
       </c>
       <c r="G53" s="154"/>
       <c r="H53" s="18"/>
-      <c r="I53" s="19" t="e" cm="1">
+      <c r="I53" s="18" t="e" cm="1">
         <f t="array" ref="I53">_xlfn.IFS(LEFT(G53,1)-RIGHT(G53,1) &gt; 0, "W1",LEFT(G53,1)-RIGHT(G53,1) = 0, "D",LEFT(G53,1)-RIGHT(G53,1) &lt; 0, "W2", ISBLANK(G53), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14409,7 +14433,7 @@
       </c>
       <c r="G54" s="154"/>
       <c r="H54" s="18"/>
-      <c r="I54" s="19" t="e" cm="1">
+      <c r="I54" s="18" t="e" cm="1">
         <f t="array" ref="I54">_xlfn.IFS(LEFT(G54,1)-RIGHT(G54,1) &gt; 0, "W1",LEFT(G54,1)-RIGHT(G54,1) = 0, "D",LEFT(G54,1)-RIGHT(G54,1) &lt; 0, "W2", ISBLANK(G54), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14439,7 +14463,7 @@
       </c>
       <c r="G55" s="154"/>
       <c r="H55" s="18"/>
-      <c r="I55" s="19" t="e" cm="1">
+      <c r="I55" s="18" t="e" cm="1">
         <f t="array" ref="I55">_xlfn.IFS(LEFT(G55,1)-RIGHT(G55,1) &gt; 0, "W1",LEFT(G55,1)-RIGHT(G55,1) = 0, "D",LEFT(G55,1)-RIGHT(G55,1) &lt; 0, "W2", ISBLANK(G55), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14473,7 +14497,7 @@
       <c r="H56" s="20" t="s">
         <v>3808</v>
       </c>
-      <c r="I56" s="21" t="str" cm="1">
+      <c r="I56" s="20" t="str" cm="1">
         <f t="array" ref="I56">_xlfn.IFS(LEFT(G56,1)-RIGHT(G56,1) &gt; 0, "W1",LEFT(G56,1)-RIGHT(G56,1) = 0, "D",LEFT(G56,1)-RIGHT(G56,1) &lt; 0, "W2", ISBLANK(G56), "")</f>
         <v>W1</v>
       </c>
@@ -14507,7 +14531,7 @@
       <c r="H57" s="20" t="s">
         <v>3813</v>
       </c>
-      <c r="I57" s="21" t="str" cm="1">
+      <c r="I57" s="20" t="str" cm="1">
         <f t="array" ref="I57">_xlfn.IFS(LEFT(G57,1)-RIGHT(G57,1) &gt; 0, "W1",LEFT(G57,1)-RIGHT(G57,1) = 0, "D",LEFT(G57,1)-RIGHT(G57,1) &lt; 0, "W2", ISBLANK(G57), "")</f>
         <v>W1</v>
       </c>
@@ -14537,7 +14561,7 @@
       </c>
       <c r="G58" s="155"/>
       <c r="H58" s="20"/>
-      <c r="I58" s="21" t="e" cm="1">
+      <c r="I58" s="20" t="e" cm="1">
         <f t="array" ref="I58">_xlfn.IFS(LEFT(G58,1)-RIGHT(G58,1) &gt; 0, "W1",LEFT(G58,1)-RIGHT(G58,1) = 0, "D",LEFT(G58,1)-RIGHT(G58,1) &lt; 0, "W2", ISBLANK(G58), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14567,7 +14591,7 @@
       </c>
       <c r="G59" s="155"/>
       <c r="H59" s="20"/>
-      <c r="I59" s="21" t="e" cm="1">
+      <c r="I59" s="20" t="e" cm="1">
         <f t="array" ref="I59">_xlfn.IFS(LEFT(G59,1)-RIGHT(G59,1) &gt; 0, "W1",LEFT(G59,1)-RIGHT(G59,1) = 0, "D",LEFT(G59,1)-RIGHT(G59,1) &lt; 0, "W2", ISBLANK(G59), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14597,7 +14621,7 @@
       </c>
       <c r="G60" s="155"/>
       <c r="H60" s="20"/>
-      <c r="I60" s="21" t="e" cm="1">
+      <c r="I60" s="20" t="e" cm="1">
         <f t="array" ref="I60">_xlfn.IFS(LEFT(G60,1)-RIGHT(G60,1) &gt; 0, "W1",LEFT(G60,1)-RIGHT(G60,1) = 0, "D",LEFT(G60,1)-RIGHT(G60,1) &lt; 0, "W2", ISBLANK(G60), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14627,7 +14651,7 @@
       </c>
       <c r="G61" s="155"/>
       <c r="H61" s="20"/>
-      <c r="I61" s="21" t="e" cm="1">
+      <c r="I61" s="20" t="e" cm="1">
         <f t="array" ref="I61">_xlfn.IFS(LEFT(G61,1)-RIGHT(G61,1) &gt; 0, "W1",LEFT(G61,1)-RIGHT(G61,1) = 0, "D",LEFT(G61,1)-RIGHT(G61,1) &lt; 0, "W2", ISBLANK(G61), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14661,7 +14685,7 @@
       <c r="H62" s="22" t="s">
         <v>3814</v>
       </c>
-      <c r="I62" s="23" t="str" cm="1">
+      <c r="I62" s="22" t="str" cm="1">
         <f t="array" ref="I62">_xlfn.IFS(LEFT(G62,1)-RIGHT(G62,1) &gt; 0, "W1",LEFT(G62,1)-RIGHT(G62,1) = 0, "D",LEFT(G62,1)-RIGHT(G62,1) &lt; 0, "W2", ISBLANK(G62), "")</f>
         <v>D</v>
       </c>
@@ -14695,7 +14719,7 @@
       <c r="H63" s="22" t="s">
         <v>3819</v>
       </c>
-      <c r="I63" s="23" t="str" cm="1">
+      <c r="I63" s="22" t="str" cm="1">
         <f t="array" ref="I63">_xlfn.IFS(LEFT(G63,1)-RIGHT(G63,1) &gt; 0, "W1",LEFT(G63,1)-RIGHT(G63,1) = 0, "D",LEFT(G63,1)-RIGHT(G63,1) &lt; 0, "W2", ISBLANK(G63), "")</f>
         <v>W2</v>
       </c>
@@ -14725,7 +14749,7 @@
       </c>
       <c r="G64" s="156"/>
       <c r="H64" s="22"/>
-      <c r="I64" s="23" t="e" cm="1">
+      <c r="I64" s="22" t="e" cm="1">
         <f t="array" ref="I64">_xlfn.IFS(LEFT(G64,1)-RIGHT(G64,1) &gt; 0, "W1",LEFT(G64,1)-RIGHT(G64,1) = 0, "D",LEFT(G64,1)-RIGHT(G64,1) &lt; 0, "W2", ISBLANK(G64), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14755,7 +14779,7 @@
       </c>
       <c r="G65" s="156"/>
       <c r="H65" s="22"/>
-      <c r="I65" s="23" t="e" cm="1">
+      <c r="I65" s="22" t="e" cm="1">
         <f t="array" ref="I65">_xlfn.IFS(LEFT(G65,1)-RIGHT(G65,1) &gt; 0, "W1",LEFT(G65,1)-RIGHT(G65,1) = 0, "D",LEFT(G65,1)-RIGHT(G65,1) &lt; 0, "W2", ISBLANK(G65), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14785,7 +14809,7 @@
       </c>
       <c r="G66" s="156"/>
       <c r="H66" s="22"/>
-      <c r="I66" s="23" t="e" cm="1">
+      <c r="I66" s="22" t="e" cm="1">
         <f t="array" ref="I66">_xlfn.IFS(LEFT(G66,1)-RIGHT(G66,1) &gt; 0, "W1",LEFT(G66,1)-RIGHT(G66,1) = 0, "D",LEFT(G66,1)-RIGHT(G66,1) &lt; 0, "W2", ISBLANK(G66), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14815,7 +14839,7 @@
       </c>
       <c r="G67" s="156"/>
       <c r="H67" s="22"/>
-      <c r="I67" s="23" t="e" cm="1">
+      <c r="I67" s="22" t="e" cm="1">
         <f t="array" ref="I67">_xlfn.IFS(LEFT(G67,1)-RIGHT(G67,1) &gt; 0, "W1",LEFT(G67,1)-RIGHT(G67,1) = 0, "D",LEFT(G67,1)-RIGHT(G67,1) &lt; 0, "W2", ISBLANK(G67), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14849,7 +14873,7 @@
       <c r="H68" s="24" t="s">
         <v>3817</v>
       </c>
-      <c r="I68" s="25" t="str" cm="1">
+      <c r="I68" s="24" t="str" cm="1">
         <f t="array" ref="I68">_xlfn.IFS(LEFT(G68,1)-RIGHT(G68,1) &gt; 0, "W1",LEFT(G68,1)-RIGHT(G68,1) = 0, "D",LEFT(G68,1)-RIGHT(G68,1) &lt; 0, "W2", ISBLANK(G68), "")</f>
         <v>W1</v>
       </c>
@@ -14883,7 +14907,7 @@
       <c r="H69" s="24" t="s">
         <v>3816</v>
       </c>
-      <c r="I69" s="25" t="str" cm="1">
+      <c r="I69" s="24" t="str" cm="1">
         <f t="array" ref="I69">_xlfn.IFS(LEFT(G69,1)-RIGHT(G69,1) &gt; 0, "W1",LEFT(G69,1)-RIGHT(G69,1) = 0, "D",LEFT(G69,1)-RIGHT(G69,1) &lt; 0, "W2", ISBLANK(G69), "")</f>
         <v>W1</v>
       </c>
@@ -14913,7 +14937,7 @@
       </c>
       <c r="G70" s="157"/>
       <c r="H70" s="24"/>
-      <c r="I70" s="25" t="e" cm="1">
+      <c r="I70" s="24" t="e" cm="1">
         <f t="array" ref="I70">_xlfn.IFS(LEFT(G70,1)-RIGHT(G70,1) &gt; 0, "W1",LEFT(G70,1)-RIGHT(G70,1) = 0, "D",LEFT(G70,1)-RIGHT(G70,1) &lt; 0, "W2", ISBLANK(G70), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14943,7 +14967,7 @@
       </c>
       <c r="G71" s="157"/>
       <c r="H71" s="24"/>
-      <c r="I71" s="25" t="e" cm="1">
+      <c r="I71" s="24" t="e" cm="1">
         <f t="array" ref="I71">_xlfn.IFS(LEFT(G71,1)-RIGHT(G71,1) &gt; 0, "W1",LEFT(G71,1)-RIGHT(G71,1) = 0, "D",LEFT(G71,1)-RIGHT(G71,1) &lt; 0, "W2", ISBLANK(G71), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -14973,7 +14997,7 @@
       </c>
       <c r="G72" s="157"/>
       <c r="H72" s="24"/>
-      <c r="I72" s="25" t="e" cm="1">
+      <c r="I72" s="24" t="e" cm="1">
         <f t="array" ref="I72">_xlfn.IFS(LEFT(G72,1)-RIGHT(G72,1) &gt; 0, "W1",LEFT(G72,1)-RIGHT(G72,1) = 0, "D",LEFT(G72,1)-RIGHT(G72,1) &lt; 0, "W2", ISBLANK(G72), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15003,7 +15027,7 @@
       </c>
       <c r="G73" s="157"/>
       <c r="H73" s="24"/>
-      <c r="I73" s="25" t="e" cm="1">
+      <c r="I73" s="24" t="e" cm="1">
         <f t="array" ref="I73">_xlfn.IFS(LEFT(G73,1)-RIGHT(G73,1) &gt; 0, "W1",LEFT(G73,1)-RIGHT(G73,1) = 0, "D",LEFT(G73,1)-RIGHT(G73,1) &lt; 0, "W2", ISBLANK(G73), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15033,7 +15057,7 @@
       </c>
       <c r="G74" s="158"/>
       <c r="H74" s="26"/>
-      <c r="I74" s="27" t="e" cm="1">
+      <c r="I74" s="26" t="e" cm="1">
         <f t="array" ref="I74">_xlfn.IFS(LEFT(G74,1)-RIGHT(G74,1) &gt; 0, "W1",LEFT(G74,1)-RIGHT(G74,1) = 0, "D",LEFT(G74,1)-RIGHT(G74,1) &lt; 0, "W2", ISBLANK(G74), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15063,7 +15087,7 @@
       </c>
       <c r="G75" s="158"/>
       <c r="H75" s="26"/>
-      <c r="I75" s="27" t="e" cm="1">
+      <c r="I75" s="26" t="e" cm="1">
         <f t="array" ref="I75">_xlfn.IFS(LEFT(G75,1)-RIGHT(G75,1) &gt; 0, "W1",LEFT(G75,1)-RIGHT(G75,1) = 0, "D",LEFT(G75,1)-RIGHT(G75,1) &lt; 0, "W2", ISBLANK(G75), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15093,7 +15117,7 @@
       </c>
       <c r="G76" s="158"/>
       <c r="H76" s="26"/>
-      <c r="I76" s="27" t="e" cm="1">
+      <c r="I76" s="26" t="e" cm="1">
         <f t="array" ref="I76">_xlfn.IFS(LEFT(G76,1)-RIGHT(G76,1) &gt; 0, "W1",LEFT(G76,1)-RIGHT(G76,1) = 0, "D",LEFT(G76,1)-RIGHT(G76,1) &lt; 0, "W2", ISBLANK(G76), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15123,7 +15147,7 @@
       </c>
       <c r="G77" s="158"/>
       <c r="H77" s="26"/>
-      <c r="I77" s="27" t="e" cm="1">
+      <c r="I77" s="26" t="e" cm="1">
         <f t="array" ref="I77">_xlfn.IFS(LEFT(G77,1)-RIGHT(G77,1) &gt; 0, "W1",LEFT(G77,1)-RIGHT(G77,1) = 0, "D",LEFT(G77,1)-RIGHT(G77,1) &lt; 0, "W2", ISBLANK(G77), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15153,7 +15177,7 @@
       </c>
       <c r="G78" s="158"/>
       <c r="H78" s="26"/>
-      <c r="I78" s="27" t="e" cm="1">
+      <c r="I78" s="26" t="e" cm="1">
         <f t="array" ref="I78">_xlfn.IFS(LEFT(G78,1)-RIGHT(G78,1) &gt; 0, "W1",LEFT(G78,1)-RIGHT(G78,1) = 0, "D",LEFT(G78,1)-RIGHT(G78,1) &lt; 0, "W2", ISBLANK(G78), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15183,7 +15207,7 @@
       </c>
       <c r="G79" s="158"/>
       <c r="H79" s="26"/>
-      <c r="I79" s="27" t="e" cm="1">
+      <c r="I79" s="26" t="e" cm="1">
         <f t="array" ref="I79">_xlfn.IFS(LEFT(G79,1)-RIGHT(G79,1) &gt; 0, "W1",LEFT(G79,1)-RIGHT(G79,1) = 0, "D",LEFT(G79,1)-RIGHT(G79,1) &lt; 0, "W2", ISBLANK(G79), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15213,7 +15237,7 @@
       </c>
       <c r="G80" s="158"/>
       <c r="H80" s="26"/>
-      <c r="I80" s="27" t="e" cm="1">
+      <c r="I80" s="26" t="e" cm="1">
         <f t="array" ref="I80">_xlfn.IFS(LEFT(G80,1)-RIGHT(G80,1) &gt; 0, "W1",LEFT(G80,1)-RIGHT(G80,1) = 0, "D",LEFT(G80,1)-RIGHT(G80,1) &lt; 0, "W2", ISBLANK(G80), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15243,7 +15267,7 @@
       </c>
       <c r="G81" s="158"/>
       <c r="H81" s="26"/>
-      <c r="I81" s="27" t="e" cm="1">
+      <c r="I81" s="26" t="e" cm="1">
         <f t="array" ref="I81">_xlfn.IFS(LEFT(G81,1)-RIGHT(G81,1) &gt; 0, "W1",LEFT(G81,1)-RIGHT(G81,1) = 0, "D",LEFT(G81,1)-RIGHT(G81,1) &lt; 0, "W2", ISBLANK(G81), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15273,7 +15297,7 @@
       </c>
       <c r="G82" s="158"/>
       <c r="H82" s="26"/>
-      <c r="I82" s="27" t="e" cm="1">
+      <c r="I82" s="26" t="e" cm="1">
         <f t="array" ref="I82">_xlfn.IFS(LEFT(G82,1)-RIGHT(G82,1) &gt; 0, "W1",LEFT(G82,1)-RIGHT(G82,1) = 0, "D",LEFT(G82,1)-RIGHT(G82,1) &lt; 0, "W2", ISBLANK(G82), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15303,7 +15327,7 @@
       </c>
       <c r="G83" s="158"/>
       <c r="H83" s="26"/>
-      <c r="I83" s="27" t="e" cm="1">
+      <c r="I83" s="26" t="e" cm="1">
         <f t="array" ref="I83">_xlfn.IFS(LEFT(G83,1)-RIGHT(G83,1) &gt; 0, "W1",LEFT(G83,1)-RIGHT(G83,1) = 0, "D",LEFT(G83,1)-RIGHT(G83,1) &lt; 0, "W2", ISBLANK(G83), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15333,7 +15357,7 @@
       </c>
       <c r="G84" s="158"/>
       <c r="H84" s="26"/>
-      <c r="I84" s="27" t="e" cm="1">
+      <c r="I84" s="26" t="e" cm="1">
         <f t="array" ref="I84">_xlfn.IFS(LEFT(G84,1)-RIGHT(G84,1) &gt; 0, "W1",LEFT(G84,1)-RIGHT(G84,1) = 0, "D",LEFT(G84,1)-RIGHT(G84,1) &lt; 0, "W2", ISBLANK(G84), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15363,7 +15387,7 @@
       </c>
       <c r="G85" s="158"/>
       <c r="H85" s="26"/>
-      <c r="I85" s="27" t="e" cm="1">
+      <c r="I85" s="26" t="e" cm="1">
         <f t="array" ref="I85">_xlfn.IFS(LEFT(G85,1)-RIGHT(G85,1) &gt; 0, "W1",LEFT(G85,1)-RIGHT(G85,1) = 0, "D",LEFT(G85,1)-RIGHT(G85,1) &lt; 0, "W2", ISBLANK(G85), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15393,7 +15417,7 @@
       </c>
       <c r="G86" s="158"/>
       <c r="H86" s="26"/>
-      <c r="I86" s="27" t="e" cm="1">
+      <c r="I86" s="26" t="e" cm="1">
         <f t="array" ref="I86">_xlfn.IFS(LEFT(G86,1)-RIGHT(G86,1) &gt; 0, "W1",LEFT(G86,1)-RIGHT(G86,1) = 0, "D",LEFT(G86,1)-RIGHT(G86,1) &lt; 0, "W2", ISBLANK(G86), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15423,7 +15447,7 @@
       </c>
       <c r="G87" s="158"/>
       <c r="H87" s="26"/>
-      <c r="I87" s="27" t="e" cm="1">
+      <c r="I87" s="26" t="e" cm="1">
         <f t="array" ref="I87">_xlfn.IFS(LEFT(G87,1)-RIGHT(G87,1) &gt; 0, "W1",LEFT(G87,1)-RIGHT(G87,1) = 0, "D",LEFT(G87,1)-RIGHT(G87,1) &lt; 0, "W2", ISBLANK(G87), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15453,7 +15477,7 @@
       </c>
       <c r="G88" s="158"/>
       <c r="H88" s="26"/>
-      <c r="I88" s="27" t="e" cm="1">
+      <c r="I88" s="26" t="e" cm="1">
         <f t="array" ref="I88">_xlfn.IFS(LEFT(G88,1)-RIGHT(G88,1) &gt; 0, "W1",LEFT(G88,1)-RIGHT(G88,1) = 0, "D",LEFT(G88,1)-RIGHT(G88,1) &lt; 0, "W2", ISBLANK(G88), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15483,7 +15507,7 @@
       </c>
       <c r="G89" s="158"/>
       <c r="H89" s="26"/>
-      <c r="I89" s="27" t="e" cm="1">
+      <c r="I89" s="26" t="e" cm="1">
         <f t="array" ref="I89">_xlfn.IFS(LEFT(G89,1)-RIGHT(G89,1) &gt; 0, "W1",LEFT(G89,1)-RIGHT(G89,1) = 0, "D",LEFT(G89,1)-RIGHT(G89,1) &lt; 0, "W2", ISBLANK(G89), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15513,7 +15537,7 @@
       </c>
       <c r="G90" s="159"/>
       <c r="H90" s="28"/>
-      <c r="I90" s="29" t="e" cm="1">
+      <c r="I90" s="28" t="e" cm="1">
         <f t="array" ref="I90">_xlfn.IFS(LEFT(G90,1)-RIGHT(G90,1) &gt; 0, "W1",LEFT(G90,1)-RIGHT(G90,1) = 0, "D",LEFT(G90,1)-RIGHT(G90,1) &lt; 0, "W2", ISBLANK(G90), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15543,7 +15567,7 @@
       </c>
       <c r="G91" s="159"/>
       <c r="H91" s="28"/>
-      <c r="I91" s="29" t="e" cm="1">
+      <c r="I91" s="28" t="e" cm="1">
         <f t="array" ref="I91">_xlfn.IFS(LEFT(G91,1)-RIGHT(G91,1) &gt; 0, "W1",LEFT(G91,1)-RIGHT(G91,1) = 0, "D",LEFT(G91,1)-RIGHT(G91,1) &lt; 0, "W2", ISBLANK(G91), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15573,7 +15597,7 @@
       </c>
       <c r="G92" s="159"/>
       <c r="H92" s="28"/>
-      <c r="I92" s="29" t="e" cm="1">
+      <c r="I92" s="28" t="e" cm="1">
         <f t="array" ref="I92">_xlfn.IFS(LEFT(G92,1)-RIGHT(G92,1) &gt; 0, "W1",LEFT(G92,1)-RIGHT(G92,1) = 0, "D",LEFT(G92,1)-RIGHT(G92,1) &lt; 0, "W2", ISBLANK(G92), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15603,7 +15627,7 @@
       </c>
       <c r="G93" s="159"/>
       <c r="H93" s="28"/>
-      <c r="I93" s="29" t="e" cm="1">
+      <c r="I93" s="28" t="e" cm="1">
         <f t="array" ref="I93">_xlfn.IFS(LEFT(G93,1)-RIGHT(G93,1) &gt; 0, "W1",LEFT(G93,1)-RIGHT(G93,1) = 0, "D",LEFT(G93,1)-RIGHT(G93,1) &lt; 0, "W2", ISBLANK(G93), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15633,7 +15657,7 @@
       </c>
       <c r="G94" s="159"/>
       <c r="H94" s="28"/>
-      <c r="I94" s="29" t="e" cm="1">
+      <c r="I94" s="28" t="e" cm="1">
         <f t="array" ref="I94">_xlfn.IFS(LEFT(G94,1)-RIGHT(G94,1) &gt; 0, "W1",LEFT(G94,1)-RIGHT(G94,1) = 0, "D",LEFT(G94,1)-RIGHT(G94,1) &lt; 0, "W2", ISBLANK(G94), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15663,7 +15687,7 @@
       </c>
       <c r="G95" s="159"/>
       <c r="H95" s="28"/>
-      <c r="I95" s="29" t="e" cm="1">
+      <c r="I95" s="28" t="e" cm="1">
         <f t="array" ref="I95">_xlfn.IFS(LEFT(G95,1)-RIGHT(G95,1) &gt; 0, "W1",LEFT(G95,1)-RIGHT(G95,1) = 0, "D",LEFT(G95,1)-RIGHT(G95,1) &lt; 0, "W2", ISBLANK(G95), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15693,7 +15717,7 @@
       </c>
       <c r="G96" s="159"/>
       <c r="H96" s="28"/>
-      <c r="I96" s="29" t="e" cm="1">
+      <c r="I96" s="28" t="e" cm="1">
         <f t="array" ref="I96">_xlfn.IFS(LEFT(G96,1)-RIGHT(G96,1) &gt; 0, "W1",LEFT(G96,1)-RIGHT(G96,1) = 0, "D",LEFT(G96,1)-RIGHT(G96,1) &lt; 0, "W2", ISBLANK(G96), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15723,7 +15747,7 @@
       </c>
       <c r="G97" s="159"/>
       <c r="H97" s="28"/>
-      <c r="I97" s="29" t="e" cm="1">
+      <c r="I97" s="28" t="e" cm="1">
         <f t="array" ref="I97">_xlfn.IFS(LEFT(G97,1)-RIGHT(G97,1) &gt; 0, "W1",LEFT(G97,1)-RIGHT(G97,1) = 0, "D",LEFT(G97,1)-RIGHT(G97,1) &lt; 0, "W2", ISBLANK(G97), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15753,7 +15777,7 @@
       </c>
       <c r="G98" s="160"/>
       <c r="H98" s="30"/>
-      <c r="I98" s="31" t="e" cm="1">
+      <c r="I98" s="30" t="e" cm="1">
         <f t="array" ref="I98">_xlfn.IFS(LEFT(G98,1)-RIGHT(G98,1) &gt; 0, "W1",LEFT(G98,1)-RIGHT(G98,1) = 0, "D",LEFT(G98,1)-RIGHT(G98,1) &lt; 0, "W2", ISBLANK(G98), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15783,7 +15807,7 @@
       </c>
       <c r="G99" s="160"/>
       <c r="H99" s="30"/>
-      <c r="I99" s="31" t="e" cm="1">
+      <c r="I99" s="30" t="e" cm="1">
         <f t="array" ref="I99">_xlfn.IFS(LEFT(G99,1)-RIGHT(G99,1) &gt; 0, "W1",LEFT(G99,1)-RIGHT(G99,1) = 0, "D",LEFT(G99,1)-RIGHT(G99,1) &lt; 0, "W2", ISBLANK(G99), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15813,7 +15837,7 @@
       </c>
       <c r="G100" s="160"/>
       <c r="H100" s="30"/>
-      <c r="I100" s="31" t="e" cm="1">
+      <c r="I100" s="30" t="e" cm="1">
         <f t="array" ref="I100">_xlfn.IFS(LEFT(G100,1)-RIGHT(G100,1) &gt; 0, "W1",LEFT(G100,1)-RIGHT(G100,1) = 0, "D",LEFT(G100,1)-RIGHT(G100,1) &lt; 0, "W2", ISBLANK(G100), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15843,7 +15867,7 @@
       </c>
       <c r="G101" s="160"/>
       <c r="H101" s="30"/>
-      <c r="I101" s="31" t="e" cm="1">
+      <c r="I101" s="30" t="e" cm="1">
         <f t="array" ref="I101">_xlfn.IFS(LEFT(G101,1)-RIGHT(G101,1) &gt; 0, "W1",LEFT(G101,1)-RIGHT(G101,1) = 0, "D",LEFT(G101,1)-RIGHT(G101,1) &lt; 0, "W2", ISBLANK(G101), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15873,7 +15897,7 @@
       </c>
       <c r="G102" s="161"/>
       <c r="H102" s="32"/>
-      <c r="I102" s="33" t="e" cm="1">
+      <c r="I102" s="32" t="e" cm="1">
         <f t="array" ref="I102">_xlfn.IFS(LEFT(G102,1)-RIGHT(G102,1) &gt; 0, "W1",LEFT(G102,1)-RIGHT(G102,1) = 0, "D",LEFT(G102,1)-RIGHT(G102,1) &lt; 0, "W2", ISBLANK(G102), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15903,7 +15927,7 @@
       </c>
       <c r="G103" s="161"/>
       <c r="H103" s="32"/>
-      <c r="I103" s="33" t="e" cm="1">
+      <c r="I103" s="32" t="e" cm="1">
         <f t="array" ref="I103">_xlfn.IFS(LEFT(G103,1)-RIGHT(G103,1) &gt; 0, "W1",LEFT(G103,1)-RIGHT(G103,1) = 0, "D",LEFT(G103,1)-RIGHT(G103,1) &lt; 0, "W2", ISBLANK(G103), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15933,7 +15957,7 @@
       </c>
       <c r="G104" s="162"/>
       <c r="H104" s="34"/>
-      <c r="I104" s="35" t="e" cm="1">
+      <c r="I104" s="34" t="e" cm="1">
         <f t="array" ref="I104">_xlfn.IFS(LEFT(G104,1)-RIGHT(G104,1) &gt; 0, "W1",LEFT(G104,1)-RIGHT(G104,1) = 0, "D",LEFT(G104,1)-RIGHT(G104,1) &lt; 0, "W2", ISBLANK(G104), "")</f>
         <v>#VALUE!</v>
       </c>
@@ -15963,7 +15987,7 @@
       </c>
       <c r="G105" s="158"/>
       <c r="H105" s="26"/>
-      <c r="I105" s="27" t="e" cm="1">
+      <c r="I105" s="26" t="e" cm="1">
         <f t="array" ref="I105">_xlfn.IFS(LEFT(G105,1)-RIGHT(G105,1) &gt; 0, "W1",LEFT(G105,1)-RIGHT(G105,1) = 0, "D",LEFT(G105,1)-RIGHT(G105,1) &lt; 0, "W2", ISBLANK(G105), "")</f>
         <v>#VALUE!</v>
       </c>

--- a/FIFAScheduleResults.xlsx
+++ b/FIFAScheduleResults.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="407" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D70964F-0FCF-43E3-8960-589EE7ED5F0C}"/>
+  <xr:revisionPtr revIDLastSave="419" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09286228-89B3-4C7E-88B2-679AF56B6540}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8186" uniqueCount="3825">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8194" uniqueCount="3829">
   <si>
     <t>Match</t>
   </si>
@@ -11601,6 +11601,18 @@
   </si>
   <si>
     <t>MEX7</t>
+  </si>
+  <si>
+    <t>MAR11</t>
+  </si>
+  <si>
+    <t>BRA9, BRA9, BRA7</t>
+  </si>
+  <si>
+    <t>OG, USA16</t>
+  </si>
+  <si>
+    <t>PRY21</t>
   </si>
 </sst>
 </file>
@@ -11930,7 +11942,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -12419,6 +12431,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13245,15 +13260,19 @@
       <c r="F16" s="128" t="s">
         <v>2341</v>
       </c>
-      <c r="G16" s="148"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6" t="e" cm="1">
+      <c r="G16" s="148" t="s">
+        <v>2471</v>
+      </c>
+      <c r="H16" s="164" t="s">
+        <v>3825</v>
+      </c>
+      <c r="I16" s="6" t="str" cm="1">
         <f t="array" ref="I16">_xlfn.IFS(LEFT(G16,1)-RIGHT(G16,1) &gt; 0, "W1",LEFT(G16,1)-RIGHT(G16,1) = 0, "D",LEFT(G16,1)-RIGHT(G16,1) &lt; 0, "W2", ISBLANK(G16), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J16" s="7" t="e">
+        <v>W2</v>
+      </c>
+      <c r="J16" s="7">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -13275,15 +13294,19 @@
       <c r="F17" s="128" t="s">
         <v>2342</v>
       </c>
-      <c r="G17" s="148"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6" t="e" cm="1">
+      <c r="G17" s="148" t="s">
+        <v>3807</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>3826</v>
+      </c>
+      <c r="I17" s="6" t="str" cm="1">
         <f t="array" ref="I17">_xlfn.IFS(LEFT(G17,1)-RIGHT(G17,1) &gt; 0, "W1",LEFT(G17,1)-RIGHT(G17,1) = 0, "D",LEFT(G17,1)-RIGHT(G17,1) &lt; 0, "W2", ISBLANK(G17), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J17" s="7" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J17" s="7">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -13433,15 +13456,19 @@
       <c r="F22" s="129" t="s">
         <v>2345</v>
       </c>
-      <c r="G22" s="149"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8" t="e" cm="1">
+      <c r="G22" s="149" t="s">
+        <v>2471</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>3828</v>
+      </c>
+      <c r="I22" s="8" t="str" cm="1">
         <f t="array" ref="I22">_xlfn.IFS(LEFT(G22,1)-RIGHT(G22,1) &gt; 0, "W1",LEFT(G22,1)-RIGHT(G22,1) = 0, "D",LEFT(G22,1)-RIGHT(G22,1) &lt; 0, "W2", ISBLANK(G22), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J22" s="9" t="e">
+        <v>W2</v>
+      </c>
+      <c r="J22" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -13463,15 +13490,19 @@
       <c r="F23" s="129" t="s">
         <v>2346</v>
       </c>
-      <c r="G23" s="149"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8" t="e" cm="1">
+      <c r="G23" s="149" t="s">
+        <v>2454</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>3827</v>
+      </c>
+      <c r="I23" s="8" t="str" cm="1">
         <f t="array" ref="I23">_xlfn.IFS(LEFT(G23,1)-RIGHT(G23,1) &gt; 0, "W1",LEFT(G23,1)-RIGHT(G23,1) = 0, "D",LEFT(G23,1)-RIGHT(G23,1) &lt; 0, "W2", ISBLANK(G23), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J23" s="9" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J23" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">

--- a/FIFAScheduleResults.xlsx
+++ b/FIFAScheduleResults.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="419" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09286228-89B3-4C7E-88B2-679AF56B6540}"/>
+  <xr:revisionPtr revIDLastSave="428" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{914DF451-E662-43F0-BBC4-F95EEF690379}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8194" uniqueCount="3829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8201" uniqueCount="3833">
   <si>
     <t>Match</t>
   </si>
@@ -11613,6 +11613,18 @@
   </si>
   <si>
     <t>PRY21</t>
+  </si>
+  <si>
+    <t>CIV8, DEU26, DEU26</t>
+  </si>
+  <si>
+    <t>NLD19, NLD19, NLD11, NLD11, SWE11, NLD24</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>JPN15, JPN18, JPN14, JPN18</t>
   </si>
 </sst>
 </file>
@@ -13652,15 +13664,19 @@
       <c r="F28" s="130" t="s">
         <v>2350</v>
       </c>
-      <c r="G28" s="150"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10" t="e" cm="1">
+      <c r="G28" s="150" t="s">
+        <v>2455</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>3829</v>
+      </c>
+      <c r="I28" s="10" t="str" cm="1">
         <f t="array" ref="I28">_xlfn.IFS(LEFT(G28,1)-RIGHT(G28,1) &gt; 0, "W1",LEFT(G28,1)-RIGHT(G28,1) = 0, "D",LEFT(G28,1)-RIGHT(G28,1) &lt; 0, "W2", ISBLANK(G28), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J28" s="11" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J28" s="11">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -13682,15 +13698,17 @@
       <c r="F29" s="130" t="s">
         <v>2351</v>
       </c>
-      <c r="G29" s="150"/>
+      <c r="G29" s="150" t="s">
+        <v>2484</v>
+      </c>
       <c r="H29" s="10"/>
-      <c r="I29" s="10" t="e" cm="1">
+      <c r="I29" s="10" t="str" cm="1">
         <f t="array" ref="I29">_xlfn.IFS(LEFT(G29,1)-RIGHT(G29,1) &gt; 0, "W1",LEFT(G29,1)-RIGHT(G29,1) = 0, "D",LEFT(G29,1)-RIGHT(G29,1) &lt; 0, "W2", ISBLANK(G29), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J29" s="11" t="e">
+        <v>D</v>
+      </c>
+      <c r="J29" s="11">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -13821,7 +13839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" ht="41" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
         <v>90</v>
       </c>
@@ -13840,15 +13858,19 @@
       <c r="F34" s="131" t="s">
         <v>2356</v>
       </c>
-      <c r="G34" s="151"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12" t="e" cm="1">
+      <c r="G34" s="151" t="s">
+        <v>2482</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>3830</v>
+      </c>
+      <c r="I34" s="12" t="str" cm="1">
         <f t="array" ref="I34">_xlfn.IFS(LEFT(G34,1)-RIGHT(G34,1) &gt; 0, "W1",LEFT(G34,1)-RIGHT(G34,1) = 0, "D",LEFT(G34,1)-RIGHT(G34,1) &lt; 0, "W2", ISBLANK(G34), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J34" s="13" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J34" s="13">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -13870,15 +13892,19 @@
       <c r="F35" s="131" t="s">
         <v>2357</v>
       </c>
-      <c r="G35" s="151"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12" t="e" cm="1">
+      <c r="G35" s="151" t="s">
+        <v>3831</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>3832</v>
+      </c>
+      <c r="I35" s="12" t="str" cm="1">
         <f t="array" ref="I35">_xlfn.IFS(LEFT(G35,1)-RIGHT(G35,1) &gt; 0, "W1",LEFT(G35,1)-RIGHT(G35,1) = 0, "D",LEFT(G35,1)-RIGHT(G35,1) &lt; 0, "W2", ISBLANK(G35), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J35" s="13" t="e">
+        <v>W2</v>
+      </c>
+      <c r="J35" s="13">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">

--- a/FIFAScheduleResults.xlsx
+++ b/FIFAScheduleResults.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="428" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{914DF451-E662-43F0-BBC4-F95EEF690379}"/>
+  <xr:revisionPtr revIDLastSave="435" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66200827-B86D-4607-BC41-C80CAA1AE6C4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8201" uniqueCount="3833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8208" uniqueCount="3837">
   <si>
     <t>Match</t>
   </si>
@@ -11625,6 +11625,18 @@
   </si>
   <si>
     <t>JPN15, JPN18, JPN14, JPN18</t>
+  </si>
+  <si>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>ESP19, ESP21, ESP21, OG</t>
+  </si>
+  <si>
+    <t>CPV6, URY20, URY14, CPV26</t>
+  </si>
+  <si>
+    <t>NZL16, EGY11, EGY10, EGY7</t>
   </si>
 </sst>
 </file>
@@ -14054,15 +14066,17 @@
       <c r="F40" s="132" t="s">
         <v>2362</v>
       </c>
-      <c r="G40" s="152"/>
+      <c r="G40" s="152" t="s">
+        <v>2484</v>
+      </c>
       <c r="H40" s="14"/>
-      <c r="I40" s="14" t="e" cm="1">
+      <c r="I40" s="14" t="str" cm="1">
         <f t="array" ref="I40">_xlfn.IFS(LEFT(G40,1)-RIGHT(G40,1) &gt; 0, "W1",LEFT(G40,1)-RIGHT(G40,1) = 0, "D",LEFT(G40,1)-RIGHT(G40,1) &lt; 0, "W2", ISBLANK(G40), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J40" s="15" t="e">
+        <v>D</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -14084,15 +14098,19 @@
       <c r="F41" s="132" t="s">
         <v>2363</v>
       </c>
-      <c r="G41" s="152"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14" t="e" cm="1">
+      <c r="G41" s="152" t="s">
+        <v>3818</v>
+      </c>
+      <c r="H41" s="14" t="s">
+        <v>3836</v>
+      </c>
+      <c r="I41" s="14" t="str" cm="1">
         <f t="array" ref="I41">_xlfn.IFS(LEFT(G41,1)-RIGHT(G41,1) &gt; 0, "W1",LEFT(G41,1)-RIGHT(G41,1) = 0, "D",LEFT(G41,1)-RIGHT(G41,1) &lt; 0, "W2", ISBLANK(G41), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J41" s="15" t="e">
+        <v>W2</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -14240,15 +14258,19 @@
       <c r="F46" s="133" t="s">
         <v>2368</v>
       </c>
-      <c r="G46" s="153"/>
-      <c r="H46" s="16"/>
-      <c r="I46" s="16" t="e" cm="1">
+      <c r="G46" s="153" t="s">
+        <v>3833</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>3834</v>
+      </c>
+      <c r="I46" s="16" t="str" cm="1">
         <f t="array" ref="I46">_xlfn.IFS(LEFT(G46,1)-RIGHT(G46,1) &gt; 0, "W1",LEFT(G46,1)-RIGHT(G46,1) = 0, "D",LEFT(G46,1)-RIGHT(G46,1) &lt; 0, "W2", ISBLANK(G46), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J46" s="17" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J46" s="17">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -14270,15 +14292,19 @@
       <c r="F47" s="133" t="s">
         <v>2369</v>
       </c>
-      <c r="G47" s="153"/>
-      <c r="H47" s="16"/>
-      <c r="I47" s="16" t="e" cm="1">
+      <c r="G47" s="153" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H47" s="16" t="s">
+        <v>3835</v>
+      </c>
+      <c r="I47" s="16" t="str" cm="1">
         <f t="array" ref="I47">_xlfn.IFS(LEFT(G47,1)-RIGHT(G47,1) &gt; 0, "W1",LEFT(G47,1)-RIGHT(G47,1) = 0, "D",LEFT(G47,1)-RIGHT(G47,1) &lt; 0, "W2", ISBLANK(G47), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J47" s="17" t="e">
+        <v>D</v>
+      </c>
+      <c r="J47" s="17">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">

--- a/FIFAScheduleResults.xlsx
+++ b/FIFAScheduleResults.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="435" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66200827-B86D-4607-BC41-C80CAA1AE6C4}"/>
+  <xr:revisionPtr revIDLastSave="450" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{549EB84A-1893-47BD-BE4C-5B84FAE236D2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8208" uniqueCount="3837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8216" uniqueCount="3843">
   <si>
     <t>Match</t>
   </si>
@@ -11637,6 +11637,24 @@
   </si>
   <si>
     <t>NZL16, EGY11, EGY10, EGY7</t>
+  </si>
+  <si>
+    <t>ARG10, ARG10</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>FRA10, FRA10, FRA7</t>
+  </si>
+  <si>
+    <t>NOR16, NOR9, SEN18, NOR9, SEN18</t>
+  </si>
+  <si>
+    <t>JOR21, DZA12, DZA9</t>
+  </si>
+  <si>
+    <t>1-2</t>
   </si>
 </sst>
 </file>
@@ -14454,15 +14472,19 @@
       <c r="F52" s="134" t="s">
         <v>2374</v>
       </c>
-      <c r="G52" s="154"/>
-      <c r="H52" s="18"/>
-      <c r="I52" s="18" t="e" cm="1">
+      <c r="G52" s="154" t="s">
+        <v>3807</v>
+      </c>
+      <c r="H52" s="18" t="s">
+        <v>3839</v>
+      </c>
+      <c r="I52" s="18" t="str" cm="1">
         <f t="array" ref="I52">_xlfn.IFS(LEFT(G52,1)-RIGHT(G52,1) &gt; 0, "W1",LEFT(G52,1)-RIGHT(G52,1) = 0, "D",LEFT(G52,1)-RIGHT(G52,1) &lt; 0, "W2", ISBLANK(G52), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J52" s="19" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J52" s="19">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -14484,15 +14506,19 @@
       <c r="F53" s="134" t="s">
         <v>2375</v>
       </c>
-      <c r="G53" s="154"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="18" t="e" cm="1">
+      <c r="G53" s="154" t="s">
+        <v>3838</v>
+      </c>
+      <c r="H53" s="18" t="s">
+        <v>3840</v>
+      </c>
+      <c r="I53" s="18" t="str" cm="1">
         <f t="array" ref="I53">_xlfn.IFS(LEFT(G53,1)-RIGHT(G53,1) &gt; 0, "W1",LEFT(G53,1)-RIGHT(G53,1) = 0, "D",LEFT(G53,1)-RIGHT(G53,1) &lt; 0, "W2", ISBLANK(G53), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J53" s="19" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J53" s="19">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -14642,15 +14668,19 @@
       <c r="F58" s="135" t="s">
         <v>2380</v>
       </c>
-      <c r="G58" s="155"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="20" t="e" cm="1">
+      <c r="G58" s="155" t="s">
+        <v>2454</v>
+      </c>
+      <c r="H58" s="20" t="s">
+        <v>3837</v>
+      </c>
+      <c r="I58" s="20" t="str" cm="1">
         <f t="array" ref="I58">_xlfn.IFS(LEFT(G58,1)-RIGHT(G58,1) &gt; 0, "W1",LEFT(G58,1)-RIGHT(G58,1) = 0, "D",LEFT(G58,1)-RIGHT(G58,1) &lt; 0, "W2", ISBLANK(G58), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J58" s="21" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J58" s="21">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -14672,15 +14702,19 @@
       <c r="F59" s="135" t="s">
         <v>2381</v>
       </c>
-      <c r="G59" s="155"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="20" t="e" cm="1">
+      <c r="G59" s="155" t="s">
+        <v>3842</v>
+      </c>
+      <c r="H59" s="20" t="s">
+        <v>3841</v>
+      </c>
+      <c r="I59" s="20" t="str" cm="1">
         <f t="array" ref="I59">_xlfn.IFS(LEFT(G59,1)-RIGHT(G59,1) &gt; 0, "W1",LEFT(G59,1)-RIGHT(G59,1) = 0, "D",LEFT(G59,1)-RIGHT(G59,1) &lt; 0, "W2", ISBLANK(G59), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J59" s="21" t="e">
+        <v>W2</v>
+      </c>
+      <c r="J59" s="21">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">

--- a/FIFAScheduleResults.xlsx
+++ b/FIFAScheduleResults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="450" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{549EB84A-1893-47BD-BE4C-5B84FAE236D2}"/>
+  <xr:revisionPtr revIDLastSave="460" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{577A8126-5436-4E83-AAE9-8E2303267153}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA World Cup 2026" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8216" uniqueCount="3843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8223" uniqueCount="3847">
   <si>
     <t>Match</t>
   </si>
@@ -11655,6 +11655,18 @@
   </si>
   <si>
     <t>1-2</t>
+  </si>
+  <si>
+    <t>5-0</t>
+  </si>
+  <si>
+    <t>COL2</t>
+  </si>
+  <si>
+    <t>HRV11</t>
+  </si>
+  <si>
+    <t>POR7, POR25, POR7,OG, POR17</t>
   </si>
 </sst>
 </file>
@@ -14864,15 +14876,19 @@
       <c r="F64" s="136" t="s">
         <v>2386</v>
       </c>
-      <c r="G64" s="156"/>
-      <c r="H64" s="22"/>
-      <c r="I64" s="22" t="e" cm="1">
+      <c r="G64" s="156" t="s">
+        <v>3843</v>
+      </c>
+      <c r="H64" s="22" t="s">
+        <v>3846</v>
+      </c>
+      <c r="I64" s="22" t="str" cm="1">
         <f t="array" ref="I64">_xlfn.IFS(LEFT(G64,1)-RIGHT(G64,1) &gt; 0, "W1",LEFT(G64,1)-RIGHT(G64,1) = 0, "D",LEFT(G64,1)-RIGHT(G64,1) &lt; 0, "W2", ISBLANK(G64), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J64" s="23" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J64" s="23">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -14894,15 +14910,19 @@
       <c r="F65" s="136" t="s">
         <v>2387</v>
       </c>
-      <c r="G65" s="156"/>
-      <c r="H65" s="22"/>
-      <c r="I65" s="22" t="e" cm="1">
+      <c r="G65" s="156" t="s">
+        <v>2478</v>
+      </c>
+      <c r="H65" s="22" t="s">
+        <v>3844</v>
+      </c>
+      <c r="I65" s="22" t="str" cm="1">
         <f t="array" ref="I65">_xlfn.IFS(LEFT(G65,1)-RIGHT(G65,1) &gt; 0, "W1",LEFT(G65,1)-RIGHT(G65,1) = 0, "D",LEFT(G65,1)-RIGHT(G65,1) &lt; 0, "W2", ISBLANK(G65), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J65" s="23" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J65" s="23">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -15052,15 +15072,17 @@
       <c r="F70" s="137" t="s">
         <v>2392</v>
       </c>
-      <c r="G70" s="157"/>
+      <c r="G70" s="157" t="s">
+        <v>2484</v>
+      </c>
       <c r="H70" s="24"/>
-      <c r="I70" s="24" t="e" cm="1">
+      <c r="I70" s="24" t="str" cm="1">
         <f t="array" ref="I70">_xlfn.IFS(LEFT(G70,1)-RIGHT(G70,1) &gt; 0, "W1",LEFT(G70,1)-RIGHT(G70,1) = 0, "D",LEFT(G70,1)-RIGHT(G70,1) &lt; 0, "W2", ISBLANK(G70), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J70" s="25" t="e">
+        <v>D</v>
+      </c>
+      <c r="J70" s="25">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -15082,15 +15104,19 @@
       <c r="F71" s="137" t="s">
         <v>2393</v>
       </c>
-      <c r="G71" s="157"/>
-      <c r="H71" s="24"/>
-      <c r="I71" s="24" t="e" cm="1">
+      <c r="G71" s="157" t="s">
+        <v>2471</v>
+      </c>
+      <c r="H71" s="24" t="s">
+        <v>3845</v>
+      </c>
+      <c r="I71" s="24" t="str" cm="1">
         <f t="array" ref="I71">_xlfn.IFS(LEFT(G71,1)-RIGHT(G71,1) &gt; 0, "W1",LEFT(G71,1)-RIGHT(G71,1) = 0, "D",LEFT(G71,1)-RIGHT(G71,1) &lt; 0, "W2", ISBLANK(G71), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J71" s="25" t="e">
+        <v>W2</v>
+      </c>
+      <c r="J71" s="25">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">

--- a/FIFAScheduleResults.xlsx
+++ b/FIFAScheduleResults.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="460" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{577A8126-5436-4E83-AAE9-8E2303267153}"/>
+  <xr:revisionPtr revIDLastSave="461" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C678DBE-6D0D-40B0-8B81-AD5097D14663}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12798,7 +12798,7 @@
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="15.81640625" customWidth="1"/>
     <col min="7" max="7" width="30" style="143" customWidth="1"/>
-    <col min="8" max="8" width="38.08984375" style="163" customWidth="1"/>
+    <col min="8" max="8" width="47.81640625" style="163" customWidth="1"/>
     <col min="9" max="9" width="12.26953125" style="163" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.36328125" bestFit="1" customWidth="1"/>
   </cols>

--- a/FIFAScheduleResults.xlsx
+++ b/FIFAScheduleResults.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="461" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C678DBE-6D0D-40B0-8B81-AD5097D14663}"/>
+  <xr:revisionPtr revIDLastSave="473" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C623C239-2044-4349-9470-CEB37CEA9D32}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8223" uniqueCount="3847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8235" uniqueCount="3854">
   <si>
     <t>Match</t>
   </si>
@@ -11667,6 +11667,27 @@
   </si>
   <si>
     <t>POR7, POR25, POR7,OG, POR17</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>BRA7, BRA7, BRA9</t>
+  </si>
+  <si>
+    <t>OG, MAR2, HTI18, MAR11, MAR9, MAR16</t>
+  </si>
+  <si>
+    <t>MEX20, MEX16, MEX8</t>
+  </si>
+  <si>
+    <t>ZAF12</t>
+  </si>
+  <si>
+    <t>CHE17, CHE9, CAN24</t>
+  </si>
+  <si>
+    <t>BIH19, OG, QAT10, BIH26</t>
   </si>
 </sst>
 </file>
@@ -12990,15 +13011,19 @@
       <c r="F6" s="126" t="s">
         <v>2335</v>
       </c>
-      <c r="G6" s="146"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2" t="e" cm="1">
+      <c r="G6" s="146" t="s">
+        <v>3847</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>3850</v>
+      </c>
+      <c r="I6" s="2" t="str" cm="1">
         <f t="array" ref="I6">_xlfn.IFS(LEFT(G6,1)-RIGHT(G6,1) &gt; 0, "W1",LEFT(G6,1)-RIGHT(G6,1) = 0, "D",LEFT(G6,1)-RIGHT(G6,1) &lt; 0, "W2", ISBLANK(G6), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J6" s="3" t="e">
+        <v>W2</v>
+      </c>
+      <c r="J6" s="3">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -13020,15 +13045,19 @@
       <c r="F7" s="126" t="s">
         <v>2336</v>
       </c>
-      <c r="G7" s="146"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2" t="e" cm="1">
+      <c r="G7" s="146" t="s">
+        <v>2478</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>3851</v>
+      </c>
+      <c r="I7" s="2" t="str" cm="1">
         <f t="array" ref="I7">_xlfn.IFS(LEFT(G7,1)-RIGHT(G7,1) &gt; 0, "W1",LEFT(G7,1)-RIGHT(G7,1) = 0, "D",LEFT(G7,1)-RIGHT(G7,1) &lt; 0, "W2", ISBLANK(G7), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J7" s="3" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J7" s="3">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -13186,15 +13215,19 @@
       <c r="F12" s="127" t="s">
         <v>2339</v>
       </c>
-      <c r="G12" s="147"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4" t="e" cm="1">
+      <c r="G12" s="147" t="s">
+        <v>2455</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>3852</v>
+      </c>
+      <c r="I12" s="4" t="str" cm="1">
         <f t="array" ref="I12">_xlfn.IFS(LEFT(G12,1)-RIGHT(G12,1) &gt; 0, "W1",LEFT(G12,1)-RIGHT(G12,1) = 0, "D",LEFT(G12,1)-RIGHT(G12,1) &lt; 0, "W2", ISBLANK(G12), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J12" s="5" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J12" s="5">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -13216,15 +13249,19 @@
       <c r="F13" s="127" t="s">
         <v>2340</v>
       </c>
-      <c r="G13" s="147"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4" t="e" cm="1">
+      <c r="G13" s="147" t="s">
+        <v>3809</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>3853</v>
+      </c>
+      <c r="I13" s="4" t="str" cm="1">
         <f t="array" ref="I13">_xlfn.IFS(LEFT(G13,1)-RIGHT(G13,1) &gt; 0, "W1",LEFT(G13,1)-RIGHT(G13,1) = 0, "D",LEFT(G13,1)-RIGHT(G13,1) &lt; 0, "W2", ISBLANK(G13), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J13" s="5" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J13" s="5">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -13382,15 +13419,19 @@
       <c r="F18" s="128" t="s">
         <v>2343</v>
       </c>
-      <c r="G18" s="148"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6" t="e" cm="1">
+      <c r="G18" s="148" t="s">
+        <v>3847</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>3848</v>
+      </c>
+      <c r="I18" s="6" t="str" cm="1">
         <f t="array" ref="I18">_xlfn.IFS(LEFT(G18,1)-RIGHT(G18,1) &gt; 0, "W1",LEFT(G18,1)-RIGHT(G18,1) = 0, "D",LEFT(G18,1)-RIGHT(G18,1) &lt; 0, "W2", ISBLANK(G18), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J18" s="7" t="e">
+        <v>W2</v>
+      </c>
+      <c r="J18" s="7">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -13412,15 +13453,19 @@
       <c r="F19" s="128" t="s">
         <v>2344</v>
       </c>
-      <c r="G19" s="148"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6" t="e" cm="1">
+      <c r="G19" s="148" t="s">
+        <v>3815</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>3849</v>
+      </c>
+      <c r="I19" s="6" t="str" cm="1">
         <f t="array" ref="I19">_xlfn.IFS(LEFT(G19,1)-RIGHT(G19,1) &gt; 0, "W1",LEFT(G19,1)-RIGHT(G19,1) = 0, "D",LEFT(G19,1)-RIGHT(G19,1) &lt; 0, "W2", ISBLANK(G19), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J19" s="7" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J19" s="7">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">

--- a/FIFAScheduleResults.xlsx
+++ b/FIFAScheduleResults.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="576" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D89F3810-F572-46BE-B782-34AA7A8B3ED2}"/>
+  <xr:revisionPtr revIDLastSave="577" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FC64F6B-197A-4523-9610-A8CE0FC84C9C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11573,9 +11573,6 @@
     <t>HRV11</t>
   </si>
   <si>
-    <t>POR7, POR25, POR7,OG, POR17</t>
-  </si>
-  <si>
     <t>0-3</t>
   </si>
   <si>
@@ -11763,6 +11760,9 @@
   </si>
   <si>
     <t>AUT7, DZA17, AUT9, DZA7, DZA7, AUT14</t>
+  </si>
+  <si>
+    <t>POR7, POR25, POR7, OG, POR17</t>
   </si>
 </sst>
 </file>
@@ -12932,7 +12932,7 @@
         <v>2429</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>3830</v>
+        <v>3829</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -13095,10 +13095,10 @@
         <v>2304</v>
       </c>
       <c r="G6" s="146" t="s">
-        <v>3816</v>
+        <v>3815</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>3819</v>
+        <v>3818</v>
       </c>
       <c r="I6" s="2" t="str" cm="1">
         <f t="array" ref="I6">_xlfn.IFS(LEFT(G6,1)-RIGHT(G6,1) &gt; 0, "W1",LEFT(G6,1)-RIGHT(G6,1) = 0, "D",LEFT(G6,1)-RIGHT(G6,1) &lt; 0, "W2", ISBLANK(G6), "")</f>
@@ -13133,7 +13133,7 @@
         <v>2447</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>3820</v>
+        <v>3819</v>
       </c>
       <c r="I7" s="2" t="str" cm="1">
         <f t="array" ref="I7">_xlfn.IFS(LEFT(G7,1)-RIGHT(G7,1) &gt; 0, "W1",LEFT(G7,1)-RIGHT(G7,1) = 0, "D",LEFT(G7,1)-RIGHT(G7,1) &lt; 0, "W2", ISBLANK(G7), "")</f>
@@ -13308,7 +13308,7 @@
         <v>2424</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>3821</v>
+        <v>3820</v>
       </c>
       <c r="I12" s="4" t="str" cm="1">
         <f t="array" ref="I12">_xlfn.IFS(LEFT(G12,1)-RIGHT(G12,1) &gt; 0, "W1",LEFT(G12,1)-RIGHT(G12,1) = 0, "D",LEFT(G12,1)-RIGHT(G12,1) &lt; 0, "W2", ISBLANK(G12), "")</f>
@@ -13343,7 +13343,7 @@
         <v>3778</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>3822</v>
+        <v>3821</v>
       </c>
       <c r="I13" s="4" t="str" cm="1">
         <f t="array" ref="I13">_xlfn.IFS(LEFT(G13,1)-RIGHT(G13,1) &gt; 0, "W1",LEFT(G13,1)-RIGHT(G13,1) = 0, "D",LEFT(G13,1)-RIGHT(G13,1) &lt; 0, "W2", ISBLANK(G13), "")</f>
@@ -13515,10 +13515,10 @@
         <v>2312</v>
       </c>
       <c r="G18" s="148" t="s">
+        <v>3815</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>3816</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>3817</v>
       </c>
       <c r="I18" s="6" t="str" cm="1">
         <f t="array" ref="I18">_xlfn.IFS(LEFT(G18,1)-RIGHT(G18,1) &gt; 0, "W1",LEFT(G18,1)-RIGHT(G18,1) = 0, "D",LEFT(G18,1)-RIGHT(G18,1) &lt; 0, "W2", ISBLANK(G18), "")</f>
@@ -13553,7 +13553,7 @@
         <v>3784</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>3818</v>
+        <v>3817</v>
       </c>
       <c r="I19" s="6" t="str" cm="1">
         <f t="array" ref="I19">_xlfn.IFS(LEFT(G19,1)-RIGHT(G19,1) &gt; 0, "W1",LEFT(G19,1)-RIGHT(G19,1) = 0, "D",LEFT(G19,1)-RIGHT(G19,1) &lt; 0, "W2", ISBLANK(G19), "")</f>
@@ -13728,7 +13728,7 @@
         <v>3807</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>3836</v>
+        <v>3835</v>
       </c>
       <c r="I24" s="8" t="str" cm="1">
         <f t="array" ref="I24">_xlfn.IFS(LEFT(G24,1)-RIGHT(G24,1) &gt; 0, "W1",LEFT(G24,1)-RIGHT(G24,1) = 0, "D",LEFT(G24,1)-RIGHT(G24,1) &lt; 0, "W2", ISBLANK(G24), "")</f>
@@ -13934,7 +13934,7 @@
         <v>2424</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>3831</v>
+        <v>3830</v>
       </c>
       <c r="I30" s="10" t="str" cm="1">
         <f t="array" ref="I30">_xlfn.IFS(LEFT(G30,1)-RIGHT(G30,1) &gt; 0, "W1",LEFT(G30,1)-RIGHT(G30,1) = 0, "D",LEFT(G30,1)-RIGHT(G30,1) &lt; 0, "W2", ISBLANK(G30), "")</f>
@@ -13966,10 +13966,10 @@
         <v>2322</v>
       </c>
       <c r="G31" s="150" t="s">
+        <v>3831</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>3832</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>3833</v>
       </c>
       <c r="I31" s="10" t="str" cm="1">
         <f t="array" ref="I31">_xlfn.IFS(LEFT(G31,1)-RIGHT(G31,1) &gt; 0, "W1",LEFT(G31,1)-RIGHT(G31,1) = 0, "D",LEFT(G31,1)-RIGHT(G31,1) &lt; 0, "W2", ISBLANK(G31), "")</f>
@@ -14144,7 +14144,7 @@
         <v>3787</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>3834</v>
+        <v>3833</v>
       </c>
       <c r="I36" s="12" t="str" cm="1">
         <f t="array" ref="I36">_xlfn.IFS(LEFT(G36,1)-RIGHT(G36,1) &gt; 0, "W1",LEFT(G36,1)-RIGHT(G36,1) = 0, "D",LEFT(G36,1)-RIGHT(G36,1) &lt; 0, "W2", ISBLANK(G36), "")</f>
@@ -14179,7 +14179,7 @@
         <v>2430</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>3835</v>
+        <v>3834</v>
       </c>
       <c r="I37" s="12" t="str" cm="1">
         <f t="array" ref="I37">_xlfn.IFS(LEFT(G37,1)-RIGHT(G37,1) &gt; 0, "W1",LEFT(G37,1)-RIGHT(G37,1) = 0, "D",LEFT(G37,1)-RIGHT(G37,1) &lt; 0, "W2", ISBLANK(G37), "")</f>
@@ -14349,10 +14349,10 @@
         <v>2333</v>
       </c>
       <c r="G42" s="152" t="s">
+        <v>3845</v>
+      </c>
+      <c r="H42" s="14" t="s">
         <v>3846</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>3847</v>
       </c>
       <c r="I42" s="14" t="str" cm="1">
         <f t="array" ref="I42">_xlfn.IFS(LEFT(G42,1)-RIGHT(G42,1) &gt; 0, "W1",LEFT(G42,1)-RIGHT(G42,1) = 0, "D",LEFT(G42,1)-RIGHT(G42,1) &lt; 0, "W2", ISBLANK(G42), "")</f>
@@ -14387,7 +14387,7 @@
         <v>2430</v>
       </c>
       <c r="H43" s="14" t="s">
-        <v>3848</v>
+        <v>3847</v>
       </c>
       <c r="I43" s="14" t="str" cm="1">
         <f t="array" ref="I43">_xlfn.IFS(LEFT(G43,1)-RIGHT(G43,1) &gt; 0, "W1",LEFT(G43,1)-RIGHT(G43,1) = 0, "D",LEFT(G43,1)-RIGHT(G43,1) &lt; 0, "W2", ISBLANK(G43), "")</f>
@@ -14560,7 +14560,7 @@
         <v>2440</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>3845</v>
+        <v>3844</v>
       </c>
       <c r="I48" s="16" t="str" cm="1">
         <f t="array" ref="I48">_xlfn.IFS(LEFT(G48,1)-RIGHT(G48,1) &gt; 0, "W1",LEFT(G48,1)-RIGHT(G48,1) = 0, "D",LEFT(G48,1)-RIGHT(G48,1) &lt; 0, "W2", ISBLANK(G48), "")</f>
@@ -14768,7 +14768,7 @@
         <v>3779</v>
       </c>
       <c r="H54" s="18" t="s">
-        <v>3843</v>
+        <v>3842</v>
       </c>
       <c r="I54" s="18" t="str" cm="1">
         <f t="array" ref="I54">_xlfn.IFS(LEFT(G54,1)-RIGHT(G54,1) &gt; 0, "W1",LEFT(G54,1)-RIGHT(G54,1) = 0, "D",LEFT(G54,1)-RIGHT(G54,1) &lt; 0, "W2", ISBLANK(G54), "")</f>
@@ -14803,7 +14803,7 @@
         <v>3812</v>
       </c>
       <c r="H55" s="18" t="s">
-        <v>3844</v>
+        <v>3843</v>
       </c>
       <c r="I55" s="18" t="str" cm="1">
         <f t="array" ref="I55">_xlfn.IFS(LEFT(G55,1)-RIGHT(G55,1) &gt; 0, "W1",LEFT(G55,1)-RIGHT(G55,1) = 0, "D",LEFT(G55,1)-RIGHT(G55,1) &lt; 0, "W2", ISBLANK(G55), "")</f>
@@ -14978,7 +14978,7 @@
         <v>3787</v>
       </c>
       <c r="H60" s="20" t="s">
-        <v>3876</v>
+        <v>3875</v>
       </c>
       <c r="I60" s="20" t="str" cm="1">
         <f t="array" ref="I60">_xlfn.IFS(LEFT(G60,1)-RIGHT(G60,1) &gt; 0, "W1",LEFT(G60,1)-RIGHT(G60,1) = 0, "D",LEFT(G60,1)-RIGHT(G60,1) &lt; 0, "W2", ISBLANK(G60), "")</f>
@@ -15010,10 +15010,10 @@
         <v>2352</v>
       </c>
       <c r="G61" s="155" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>3878</v>
+        <v>3877</v>
       </c>
       <c r="I61" s="20" t="str" cm="1">
         <f t="array" ref="I61">_xlfn.IFS(LEFT(G61,1)-RIGHT(G61,1) &gt; 0, "W1",LEFT(G61,1)-RIGHT(G61,1) = 0, "D",LEFT(G61,1)-RIGHT(G61,1) &lt; 0, "W2", ISBLANK(G61), "")</f>
@@ -15118,7 +15118,7 @@
         <v>3812</v>
       </c>
       <c r="H64" s="22" t="s">
-        <v>3815</v>
+        <v>3878</v>
       </c>
       <c r="I64" s="22" t="str" cm="1">
         <f t="array" ref="I64">_xlfn.IFS(LEFT(G64,1)-RIGHT(G64,1) &gt; 0, "W1",LEFT(G64,1)-RIGHT(G64,1) = 0, "D",LEFT(G64,1)-RIGHT(G64,1) &lt; 0, "W2", ISBLANK(G64), "")</f>
@@ -15221,7 +15221,7 @@
         <v>3778</v>
       </c>
       <c r="H67" s="22" t="s">
-        <v>3874</v>
+        <v>3873</v>
       </c>
       <c r="I67" s="22" t="str" cm="1">
         <f t="array" ref="I67">_xlfn.IFS(LEFT(G67,1)-RIGHT(G67,1) &gt; 0, "W1",LEFT(G67,1)-RIGHT(G67,1) = 0, "D",LEFT(G67,1)-RIGHT(G67,1) &lt; 0, "W2", ISBLANK(G67), "")</f>
@@ -15391,10 +15391,10 @@
         <v>2363</v>
       </c>
       <c r="G72" s="157" t="s">
-        <v>3832</v>
+        <v>3831</v>
       </c>
       <c r="H72" s="24" t="s">
-        <v>3875</v>
+        <v>3874</v>
       </c>
       <c r="I72" s="24" t="str" cm="1">
         <f t="array" ref="I72">_xlfn.IFS(LEFT(G72,1)-RIGHT(G72,1) &gt; 0, "W1",LEFT(G72,1)-RIGHT(G72,1) = 0, "D",LEFT(G72,1)-RIGHT(G72,1) &lt; 0, "W2", ISBLANK(G72), "")</f>
@@ -15429,7 +15429,7 @@
         <v>2424</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>3877</v>
+        <v>3876</v>
       </c>
       <c r="I73" s="24" t="str" cm="1">
         <f t="array" ref="I73">_xlfn.IFS(LEFT(G73,1)-RIGHT(G73,1) &gt; 0, "W1",LEFT(G73,1)-RIGHT(G73,1) = 0, "D",LEFT(G73,1)-RIGHT(G73,1) &lt; 0, "W2", ISBLANK(G73), "")</f>
@@ -15443,10 +15443,10 @@
     </row>
     <row r="74" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="26" t="s">
+        <v>3822</v>
+      </c>
+      <c r="B74" s="27" t="s">
         <v>3823</v>
-      </c>
-      <c r="B74" s="27" t="s">
-        <v>3824</v>
       </c>
       <c r="C74" s="27" t="s">
         <v>199</v>
@@ -15455,7 +15455,7 @@
         <v>2410</v>
       </c>
       <c r="E74" s="27" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="F74" s="138" t="s">
         <v>2365</v>
@@ -15474,10 +15474,10 @@
     </row>
     <row r="75" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="26" t="s">
+        <v>3848</v>
+      </c>
+      <c r="B75" s="27" t="s">
         <v>3849</v>
-      </c>
-      <c r="B75" s="27" t="s">
-        <v>3850</v>
       </c>
       <c r="C75" s="27" t="s">
         <v>200</v>
@@ -15486,7 +15486,7 @@
         <v>2437</v>
       </c>
       <c r="E75" s="27" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="F75" s="138" t="s">
         <v>2366</v>
@@ -15505,10 +15505,10 @@
     </row>
     <row r="76" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="26" t="s">
+        <v>3836</v>
+      </c>
+      <c r="B76" s="27" t="s">
         <v>3837</v>
-      </c>
-      <c r="B76" s="27" t="s">
-        <v>3838</v>
       </c>
       <c r="C76" s="27" t="s">
         <v>201</v>
@@ -15517,7 +15517,7 @@
         <v>2413</v>
       </c>
       <c r="E76" s="27" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="F76" s="138" t="s">
         <v>2367</v>
@@ -15536,10 +15536,10 @@
     </row>
     <row r="77" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="26" t="s">
+        <v>3838</v>
+      </c>
+      <c r="B77" s="27" t="s">
         <v>3839</v>
-      </c>
-      <c r="B77" s="27" t="s">
-        <v>3840</v>
       </c>
       <c r="C77" s="27" t="s">
         <v>200</v>
@@ -15548,7 +15548,7 @@
         <v>2415</v>
       </c>
       <c r="E77" s="27" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="F77" s="138" t="s">
         <v>2368</v>
@@ -15567,10 +15567,10 @@
     </row>
     <row r="78" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="26" t="s">
+        <v>3850</v>
+      </c>
+      <c r="B78" s="27" t="s">
         <v>3851</v>
-      </c>
-      <c r="B78" s="27" t="s">
-        <v>3852</v>
       </c>
       <c r="C78" s="27" t="s">
         <v>202</v>
@@ -15579,7 +15579,7 @@
         <v>2419</v>
       </c>
       <c r="E78" s="27" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="F78" s="138" t="s">
         <v>2369</v>
@@ -15598,10 +15598,10 @@
     </row>
     <row r="79" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="26" t="s">
-        <v>3853</v>
+        <v>3852</v>
       </c>
       <c r="B79" s="27" t="s">
-        <v>3857</v>
+        <v>3856</v>
       </c>
       <c r="C79" s="27" t="s">
         <v>201</v>
@@ -15610,7 +15610,7 @@
         <v>2415</v>
       </c>
       <c r="E79" s="27" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="F79" s="138" t="s">
         <v>2370</v>
@@ -15629,10 +15629,10 @@
     </row>
     <row r="80" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="26" t="s">
+        <v>3858</v>
+      </c>
+      <c r="B80" s="27" t="s">
         <v>3859</v>
-      </c>
-      <c r="B80" s="27" t="s">
-        <v>3860</v>
       </c>
       <c r="C80" s="27" t="s">
         <v>202</v>
@@ -15641,7 +15641,7 @@
         <v>2413</v>
       </c>
       <c r="E80" s="27" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="F80" s="138" t="s">
         <v>2371</v>
@@ -15660,10 +15660,10 @@
     </row>
     <row r="81" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="26" t="s">
-        <v>3862</v>
+        <v>3861</v>
       </c>
       <c r="B81" s="27" t="s">
-        <v>3867</v>
+        <v>3866</v>
       </c>
       <c r="C81" s="27" t="s">
         <v>202</v>
@@ -15672,7 +15672,7 @@
         <v>2434</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="F81" s="138" t="s">
         <v>2372</v>
@@ -15691,10 +15691,10 @@
     </row>
     <row r="82" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="26" t="s">
-        <v>3842</v>
+        <v>3841</v>
       </c>
       <c r="B82" s="27" t="s">
-        <v>3841</v>
+        <v>3840</v>
       </c>
       <c r="C82" s="27" t="s">
         <v>203</v>
@@ -15703,7 +15703,7 @@
         <v>2411</v>
       </c>
       <c r="E82" s="27" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="F82" s="138" t="s">
         <v>2373</v>
@@ -15722,10 +15722,10 @@
     </row>
     <row r="83" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="26" t="s">
-        <v>3861</v>
+        <v>3860</v>
       </c>
       <c r="B83" s="27" t="s">
-        <v>3868</v>
+        <v>3867</v>
       </c>
       <c r="C83" s="27" t="s">
         <v>202</v>
@@ -15734,7 +15734,7 @@
         <v>2416</v>
       </c>
       <c r="E83" s="27" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="F83" s="138" t="s">
         <v>2374</v>
@@ -15753,10 +15753,10 @@
     </row>
     <row r="84" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="26" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
       <c r="B84" s="27" t="s">
-        <v>3869</v>
+        <v>3868</v>
       </c>
       <c r="C84" s="27" t="s">
         <v>204</v>
@@ -15765,7 +15765,7 @@
         <v>2417</v>
       </c>
       <c r="E84" s="27" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="F84" s="138" t="s">
         <v>2375</v>
@@ -15784,10 +15784,10 @@
     </row>
     <row r="85" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="26" t="s">
-        <v>3864</v>
+        <v>3863</v>
       </c>
       <c r="B85" s="27" t="s">
-        <v>3870</v>
+        <v>3869</v>
       </c>
       <c r="C85" s="27" t="s">
         <v>203</v>
@@ -15796,7 +15796,7 @@
         <v>2410</v>
       </c>
       <c r="E85" s="27" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="F85" s="138" t="s">
         <v>2376</v>
@@ -15815,10 +15815,10 @@
     </row>
     <row r="86" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="26" t="s">
-        <v>3865</v>
+        <v>3864</v>
       </c>
       <c r="B86" s="27" t="s">
-        <v>3871</v>
+        <v>3870</v>
       </c>
       <c r="C86" s="27" t="s">
         <v>204</v>
@@ -15827,7 +15827,7 @@
         <v>2420</v>
       </c>
       <c r="E86" s="27" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="F86" s="138" t="s">
         <v>2377</v>
@@ -15846,10 +15846,10 @@
     </row>
     <row r="87" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="26" t="s">
-        <v>3855</v>
+        <v>3854</v>
       </c>
       <c r="B87" s="27" t="s">
-        <v>3858</v>
+        <v>3857</v>
       </c>
       <c r="C87" s="27" t="s">
         <v>206</v>
@@ -15858,7 +15858,7 @@
         <v>2414</v>
       </c>
       <c r="E87" s="27" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="F87" s="138" t="s">
         <v>2378</v>
@@ -15877,10 +15877,10 @@
     </row>
     <row r="88" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="26" t="s">
-        <v>3866</v>
+        <v>3865</v>
       </c>
       <c r="B88" s="27" t="s">
-        <v>3872</v>
+        <v>3871</v>
       </c>
       <c r="C88" s="27" t="s">
         <v>206</v>
@@ -15889,7 +15889,7 @@
         <v>2438</v>
       </c>
       <c r="E88" s="27" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="F88" s="138" t="s">
         <v>2379</v>
@@ -15908,10 +15908,10 @@
     </row>
     <row r="89" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="26" t="s">
-        <v>3854</v>
+        <v>3853</v>
       </c>
       <c r="B89" s="27" t="s">
-        <v>3856</v>
+        <v>3855</v>
       </c>
       <c r="C89" s="27" t="s">
         <v>204</v>
@@ -15920,7 +15920,7 @@
         <v>2412</v>
       </c>
       <c r="E89" s="27" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="F89" s="138" t="s">
         <v>2380</v>
@@ -15951,7 +15951,7 @@
         <v>2419</v>
       </c>
       <c r="E90" s="29" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
       <c r="F90" s="139" t="s">
         <v>2381</v>
@@ -15982,7 +15982,7 @@
         <v>2415</v>
       </c>
       <c r="E91" s="29" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
       <c r="F91" s="139" t="s">
         <v>2382</v>
@@ -16013,7 +16013,7 @@
         <v>2416</v>
       </c>
       <c r="E92" s="29" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
       <c r="F92" s="139" t="s">
         <v>2383</v>
@@ -16044,7 +16044,7 @@
         <v>2411</v>
       </c>
       <c r="E93" s="29" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
       <c r="F93" s="139" t="s">
         <v>2384</v>
@@ -16075,7 +16075,7 @@
         <v>2410</v>
       </c>
       <c r="E94" s="29" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
       <c r="F94" s="139" t="s">
         <v>2385</v>
@@ -16106,7 +16106,7 @@
         <v>2411</v>
       </c>
       <c r="E95" s="29" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
       <c r="F95" s="139" t="s">
         <v>2386</v>
@@ -16137,7 +16137,7 @@
         <v>2434</v>
       </c>
       <c r="E96" s="29" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
       <c r="F96" s="139" t="s">
         <v>2387</v>
@@ -16168,7 +16168,7 @@
         <v>2416</v>
       </c>
       <c r="E97" s="29" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
       <c r="F97" s="139" t="s">
         <v>2388</v>
@@ -16199,7 +16199,7 @@
         <v>2416</v>
       </c>
       <c r="E98" s="31" t="s">
-        <v>3827</v>
+        <v>3826</v>
       </c>
       <c r="F98" s="140" t="s">
         <v>2389</v>
@@ -16230,7 +16230,7 @@
         <v>2410</v>
       </c>
       <c r="E99" s="31" t="s">
-        <v>3827</v>
+        <v>3826</v>
       </c>
       <c r="F99" s="140" t="s">
         <v>2390</v>
@@ -16261,7 +16261,7 @@
         <v>2419</v>
       </c>
       <c r="E100" s="31" t="s">
-        <v>3827</v>
+        <v>3826</v>
       </c>
       <c r="F100" s="140" t="s">
         <v>2391</v>
@@ -16292,7 +16292,7 @@
         <v>2413</v>
       </c>
       <c r="E101" s="31" t="s">
-        <v>3827</v>
+        <v>3826</v>
       </c>
       <c r="F101" s="140" t="s">
         <v>2392</v>
@@ -16323,7 +16323,7 @@
         <v>2410</v>
       </c>
       <c r="E102" s="33" t="s">
-        <v>3828</v>
+        <v>3827</v>
       </c>
       <c r="F102" s="141" t="s">
         <v>2393</v>
@@ -16354,7 +16354,7 @@
         <v>2410</v>
       </c>
       <c r="E103" s="33" t="s">
-        <v>3828</v>
+        <v>3827</v>
       </c>
       <c r="F103" s="141" t="s">
         <v>2394</v>
@@ -16385,7 +16385,7 @@
         <v>2419</v>
       </c>
       <c r="E104" s="35" t="s">
-        <v>3829</v>
+        <v>3828</v>
       </c>
       <c r="F104" s="142" t="s">
         <v>2395</v>

--- a/FIFAScheduleResults.xlsx
+++ b/FIFAScheduleResults.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="694" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F9CAB77-6EFD-439D-A24C-652F2532E859}"/>
+  <xr:revisionPtr revIDLastSave="698" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{357D453D-67E7-40D3-91C3-7AC03907457B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8327" uniqueCount="3919">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8329" uniqueCount="3920">
   <si>
     <t>Match</t>
   </si>
@@ -11876,13 +11876,16 @@
     <t>W1</t>
   </si>
   <si>
-    <t>FRA TBD</t>
-  </si>
-  <si>
-    <t>France vs</t>
-  </si>
-  <si>
     <t>FRA10, FRA7</t>
+  </si>
+  <si>
+    <t>ESP8, BEL17, ESP6</t>
+  </si>
+  <si>
+    <t>France vs Spain</t>
+  </si>
+  <si>
+    <t>FRA ESP</t>
   </si>
 </sst>
 </file>
@@ -16537,7 +16540,7 @@
         <v>2410</v>
       </c>
       <c r="H98" s="30" t="s">
-        <v>3918</v>
+        <v>3916</v>
       </c>
       <c r="I98" s="30" t="str" cm="1">
         <f t="array" ref="I98">_xlfn.IFS(LEFT(G98,1)-RIGHT(G98,1) &gt; 0, "W1",LEFT(G98,1)-RIGHT(G98,1) = 0, "D",LEFT(G98,1)-RIGHT(G98,1) &lt; 0, "W2", ISBLANK(G98), "")</f>
@@ -16569,15 +16572,19 @@
       <c r="F99" s="140" t="s">
         <v>2377</v>
       </c>
-      <c r="G99" s="160"/>
-      <c r="H99" s="30"/>
-      <c r="I99" s="30" t="e" cm="1">
+      <c r="G99" s="160" t="s">
+        <v>2411</v>
+      </c>
+      <c r="H99" s="30" t="s">
+        <v>3917</v>
+      </c>
+      <c r="I99" s="30" t="str" cm="1">
         <f t="array" ref="I99">_xlfn.IFS(LEFT(G99,1)-RIGHT(G99,1) &gt; 0, "W1",LEFT(G99,1)-RIGHT(G99,1) = 0, "D",LEFT(G99,1)-RIGHT(G99,1) &lt; 0, "W2", ISBLANK(G99), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J99" s="31" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J99" s="31">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
       <c r="K99" s="30"/>
       <c r="L99" s="30"/>
@@ -16648,10 +16655,10 @@
     </row>
     <row r="102" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="32" t="s">
-        <v>3917</v>
+        <v>3918</v>
       </c>
       <c r="B102" s="33" t="s">
-        <v>3916</v>
+        <v>3919</v>
       </c>
       <c r="C102" s="33" t="s">
         <v>211</v>

--- a/FIFAScheduleResults.xlsx
+++ b/FIFAScheduleResults.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="704" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{009D3017-7CC1-4B58-847E-631E9DE7DA39}"/>
+  <xr:revisionPtr revIDLastSave="705" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71FC843D-DCF8-4C9E-8689-4AC97D8DE95F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16618,18 +16618,18 @@
         <v>2377</v>
       </c>
       <c r="G100" s="160" t="s">
-        <v>2410</v>
+        <v>3797</v>
       </c>
       <c r="H100" s="30" t="s">
         <v>3922</v>
       </c>
       <c r="I100" s="30" t="str" cm="1">
         <f t="array" ref="I100">_xlfn.IFS(LEFT(G100,1)-RIGHT(G100,1) &gt; 0, "W1",LEFT(G100,1)-RIGHT(G100,1) = 0, "D",LEFT(G100,1)-RIGHT(G100,1) &lt; 0, "W2", ISBLANK(G100), "")</f>
-        <v>W1</v>
+        <v>W2</v>
       </c>
       <c r="J100" s="31">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K100" s="30"/>
       <c r="L100" s="30"/>

--- a/FIFAScheduleResults.xlsx
+++ b/FIFAScheduleResults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="715" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2E5E4CA-3DC6-4CBB-A19D-03E8EC5F2A27}"/>
+  <xr:revisionPtr revIDLastSave="717" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04777157-E4ED-47DD-93B6-7C419BD9717D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA World Cup 2026" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8337" uniqueCount="3926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8339" uniqueCount="3928">
   <si>
     <t>Match</t>
   </si>
@@ -11904,6 +11904,12 @@
   </si>
   <si>
     <t>ENG18, ARG24, ARG22</t>
+  </si>
+  <si>
+    <t>4-6</t>
+  </si>
+  <si>
+    <t>FRA10, FRA10, FRA12, FRA7, ENG4, ENG2, ENG7, ENG7, ENG7, ENG10</t>
   </si>
 </sst>
 </file>
@@ -16770,15 +16776,19 @@
       <c r="F104" s="142" t="s">
         <v>2378</v>
       </c>
-      <c r="G104" s="162"/>
-      <c r="H104" s="34"/>
-      <c r="I104" s="34" t="e" cm="1">
+      <c r="G104" s="162" t="s">
+        <v>3926</v>
+      </c>
+      <c r="H104" s="34" t="s">
+        <v>3927</v>
+      </c>
+      <c r="I104" s="34" t="str" cm="1">
         <f t="array" ref="I104">_xlfn.IFS(LEFT(G104,1)-RIGHT(G104,1) &gt; 0, "W1",LEFT(G104,1)-RIGHT(G104,1) = 0, "D",LEFT(G104,1)-RIGHT(G104,1) &lt; 0, "W2", ISBLANK(G104), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J104" s="35" t="e">
+        <v>W2</v>
+      </c>
+      <c r="J104" s="35">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v>-2</v>
       </c>
       <c r="K104" s="34"/>
       <c r="L104" s="34"/>

--- a/FIFAScheduleResults.xlsx
+++ b/FIFAScheduleResults.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="717" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04777157-E4ED-47DD-93B6-7C419BD9717D}"/>
+  <xr:revisionPtr revIDLastSave="719" documentId="13_ncr:1_{AD0E7F59-3B0E-407E-93E9-FE21F83F93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E38B04C-2003-43D4-AFE3-408761B7E275}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8339" uniqueCount="3928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8341" uniqueCount="3929">
   <si>
     <t>Match</t>
   </si>
@@ -11910,6 +11910,9 @@
   </si>
   <si>
     <t>FRA10, FRA10, FRA12, FRA7, ENG4, ENG2, ENG7, ENG7, ENG7, ENG10</t>
+  </si>
+  <si>
+    <t>ESP7</t>
   </si>
 </sst>
 </file>
@@ -16812,15 +16815,19 @@
       <c r="F105" s="138" t="s">
         <v>2379</v>
       </c>
-      <c r="G105" s="158"/>
-      <c r="H105" s="26"/>
-      <c r="I105" s="26" t="e" cm="1">
+      <c r="G105" s="158" t="s">
+        <v>2430</v>
+      </c>
+      <c r="H105" s="26" t="s">
+        <v>3928</v>
+      </c>
+      <c r="I105" s="26" t="str" cm="1">
         <f t="array" ref="I105">_xlfn.IFS(LEFT(G105,1)-RIGHT(G105,1) &gt; 0, "W1",LEFT(G105,1)-RIGHT(G105,1) = 0, "D",LEFT(G105,1)-RIGHT(G105,1) &lt; 0, "W2", ISBLANK(G105), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J105" s="27" t="e">
+        <v>W1</v>
+      </c>
+      <c r="J105" s="27">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
       <c r="K105" s="26"/>
       <c r="L105" s="26"/>
